--- a/database/event/6976/event_6976_evp_summary.xlsx
+++ b/database/event/6976/event_6976_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -508,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.9794</v>
+        <v>7.672</v>
       </c>
       <c r="C2" t="n">
-        <v>7.901872</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3.466333879191322</v>
+        <v>2.678</v>
       </c>
       <c r="E2" t="n">
-        <v>137.5863</v>
+        <v>7.672</v>
       </c>
       <c r="F2" t="n">
-        <v>14.19458728144559</v>
+        <v>1.7407</v>
       </c>
       <c r="G2" t="n">
-        <v>123.3917300723482</v>
+        <v>5.9313</v>
       </c>
       <c r="H2" t="n">
-        <v>14.19458728144559</v>
+        <v>1.7407</v>
       </c>
       <c r="I2" t="n">
-        <v>12.0956382849411</v>
+        <v>1.4109</v>
       </c>
       <c r="J2" t="n">
-        <v>123.3917300723482</v>
+        <v>5.9313</v>
       </c>
       <c r="K2" t="n">
         <v>85</v>
@@ -541,7 +529,7 @@
         <v>78</v>
       </c>
       <c r="M2" t="n">
-        <v>135.4874</v>
+        <v>7.3422</v>
       </c>
       <c r="N2" t="n">
         <v>163</v>
@@ -550,81 +538,81 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4037</v>
+        <v>4.6741</v>
       </c>
       <c r="C3" t="n">
-        <v>4.755256</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.461124447793647</v>
+        <v>1.4669</v>
       </c>
       <c r="E3" t="n">
-        <v>50.3361</v>
+        <v>4.6741</v>
       </c>
       <c r="F3" t="n">
-        <v>37.78873385852687</v>
+        <v>4.2088</v>
       </c>
       <c r="G3" t="n">
-        <v>12.54732266259654</v>
+        <v>0.4653</v>
       </c>
       <c r="H3" t="n">
-        <v>39.90190256132576</v>
+        <v>4.3723</v>
       </c>
       <c r="I3" t="n">
-        <v>34.0016212302024</v>
+        <v>3.5439</v>
       </c>
       <c r="J3" t="n">
-        <v>12.54732266259654</v>
+        <v>0.4653</v>
       </c>
       <c r="K3" t="n">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="L3" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M3" t="n">
-        <v>46.5489</v>
+        <v>4.0092</v>
       </c>
       <c r="N3" t="n">
-        <v>163</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.175</v>
+        <v>4.6313</v>
       </c>
       <c r="C4" t="n">
-        <v>4.554</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1.369077179471527</v>
+        <v>1.4496</v>
       </c>
       <c r="E4" t="n">
-        <v>46.3309</v>
+        <v>4.6313</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6225648108384947</v>
+        <v>4.1941</v>
       </c>
       <c r="G4" t="n">
-        <v>46.95347950274064</v>
+        <v>0.4372</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6225648108384947</v>
+        <v>4.3132</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5305063551004716</v>
+        <v>3.496</v>
       </c>
       <c r="J4" t="n">
-        <v>46.95347950274064</v>
+        <v>0.4372</v>
       </c>
       <c r="K4" t="n">
         <v>85</v>
@@ -633,7 +621,7 @@
         <v>78</v>
       </c>
       <c r="M4" t="n">
-        <v>46.423</v>
+        <v>3.9332</v>
       </c>
       <c r="N4" t="n">
         <v>163</v>
@@ -642,265 +630,265 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8359</v>
+        <v>3.588</v>
       </c>
       <c r="C5" t="n">
-        <v>4.255592</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.238890931463799</v>
+        <v>1.0281</v>
       </c>
       <c r="E5" t="n">
-        <v>40.6663</v>
+        <v>3.588</v>
       </c>
       <c r="F5" t="n">
-        <v>23.23787271208449</v>
+        <v>0.5859</v>
       </c>
       <c r="G5" t="n">
-        <v>17.42840470171368</v>
+        <v>3.0021</v>
       </c>
       <c r="H5" t="n">
-        <v>23.23787271208449</v>
+        <v>0.5859</v>
       </c>
       <c r="I5" t="n">
-        <v>19.80169604538528</v>
+        <v>0.5859</v>
       </c>
       <c r="J5" t="n">
-        <v>17.42840470171368</v>
+        <v>3.0021</v>
       </c>
       <c r="K5" t="n">
         <v>85</v>
       </c>
       <c r="L5" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="M5" t="n">
-        <v>37.2301</v>
+        <v>3.588</v>
       </c>
       <c r="N5" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1153</v>
+        <v>3.4116</v>
       </c>
       <c r="C6" t="n">
-        <v>3.621464</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9855279484200025</v>
+        <v>0.9568</v>
       </c>
       <c r="E6" t="n">
-        <v>29.642</v>
+        <v>3.4116</v>
       </c>
       <c r="F6" t="n">
-        <v>13.23044392957322</v>
+        <v>0.9599</v>
       </c>
       <c r="G6" t="n">
-        <v>16.41155541641916</v>
+        <v>2.4517</v>
       </c>
       <c r="H6" t="n">
-        <v>13.23044392957322</v>
+        <v>0.9599</v>
       </c>
       <c r="I6" t="n">
-        <v>11.27406249637818</v>
+        <v>0.9599</v>
       </c>
       <c r="J6" t="n">
-        <v>16.41155541641916</v>
+        <v>2.4517</v>
       </c>
       <c r="K6" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="L6" t="n">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="M6" t="n">
-        <v>27.6856</v>
+        <v>3.4116</v>
       </c>
       <c r="N6" t="n">
-        <v>163</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8116</v>
+        <v>3.1774</v>
       </c>
       <c r="C7" t="n">
-        <v>3.354208</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8875120805330727</v>
+        <v>0.8622</v>
       </c>
       <c r="E7" t="n">
-        <v>25.3772</v>
+        <v>3.1774</v>
       </c>
       <c r="F7" t="n">
-        <v>16.25470792980022</v>
+        <v>2.1623</v>
       </c>
       <c r="G7" t="n">
-        <v>9.122445108884348</v>
+        <v>1.0151</v>
       </c>
       <c r="H7" t="n">
-        <v>16.25470792980022</v>
+        <v>2.1623</v>
       </c>
       <c r="I7" t="n">
-        <v>19.3915813899371</v>
+        <v>2.1623</v>
       </c>
       <c r="J7" t="n">
-        <v>9.122445108884348</v>
+        <v>1.0151</v>
       </c>
       <c r="K7" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="L7" t="n">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="M7" t="n">
-        <v>28.514</v>
+        <v>3.1774</v>
       </c>
       <c r="N7" t="n">
-        <v>191</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6438</v>
+        <v>2.8854</v>
       </c>
       <c r="C8" t="n">
-        <v>3.206544</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8354583618277777</v>
+        <v>0.7443</v>
       </c>
       <c r="E8" t="n">
-        <v>23.1122</v>
+        <v>2.8854</v>
       </c>
       <c r="F8" t="n">
-        <v>22.86658412816974</v>
+        <v>2.6479</v>
       </c>
       <c r="G8" t="n">
-        <v>0.245618196024231</v>
+        <v>0.2375</v>
       </c>
       <c r="H8" t="n">
-        <v>22.86658412816974</v>
+        <v>2.6479</v>
       </c>
       <c r="I8" t="n">
-        <v>27.05019475813563</v>
+        <v>2.1462</v>
       </c>
       <c r="J8" t="n">
-        <v>0.245618196024231</v>
+        <v>0.2375</v>
       </c>
       <c r="K8" t="n">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="L8" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="M8" t="n">
-        <v>27.2958</v>
+        <v>2.3837</v>
       </c>
       <c r="N8" t="n">
-        <v>204</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6166</v>
+        <v>2.8566</v>
       </c>
       <c r="C9" t="n">
-        <v>3.182608</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.827169723842774</v>
+        <v>0.7326</v>
       </c>
       <c r="E9" t="n">
-        <v>22.7515</v>
+        <v>2.8566</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.119656966192278</v>
+        <v>1.1277</v>
       </c>
       <c r="G9" t="n">
-        <v>23.87120577718435</v>
+        <v>1.7289</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.119656966192278</v>
+        <v>1.1277</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.178586280202397</v>
+        <v>1.1277</v>
       </c>
       <c r="J9" t="n">
-        <v>23.87120577718435</v>
+        <v>1.7289</v>
       </c>
       <c r="K9" t="n">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="L9" t="n">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="M9" t="n">
-        <v>22.6926</v>
+        <v>2.8566</v>
       </c>
       <c r="N9" t="n">
-        <v>217</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6007</v>
+        <v>2.4301</v>
       </c>
       <c r="C10" t="n">
-        <v>3.168616</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8223278487940459</v>
+        <v>0.5603</v>
       </c>
       <c r="E10" t="n">
-        <v>22.5409</v>
+        <v>2.4301</v>
       </c>
       <c r="F10" t="n">
-        <v>-11.33551598168281</v>
+        <v>2.7083</v>
       </c>
       <c r="G10" t="n">
-        <v>33.87638612025997</v>
+        <v>-0.2782</v>
       </c>
       <c r="H10" t="n">
-        <v>-11.33551598168281</v>
+        <v>2.7083</v>
       </c>
       <c r="I10" t="n">
-        <v>-9.659336926747253</v>
+        <v>2.7083</v>
       </c>
       <c r="J10" t="n">
-        <v>33.87638612025997</v>
+        <v>-0.2782</v>
       </c>
       <c r="K10" t="n">
         <v>85</v>
@@ -909,7 +897,7 @@
         <v>82</v>
       </c>
       <c r="M10" t="n">
-        <v>24.217</v>
+        <v>2.4301</v>
       </c>
       <c r="N10" t="n">
         <v>167</v>
@@ -918,587 +906,587 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3316</v>
+        <v>2.4043</v>
       </c>
       <c r="C11" t="n">
-        <v>2.931808</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7424127640335657</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>19.0636</v>
+        <v>2.4043</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.224349205903309</v>
+        <v>2.3336</v>
       </c>
       <c r="G11" t="n">
-        <v>28.28797059398123</v>
+        <v>0.0707</v>
       </c>
       <c r="H11" t="n">
-        <v>-9.224349205903309</v>
+        <v>2.3336</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.860347694253445</v>
+        <v>1.8915</v>
       </c>
       <c r="J11" t="n">
-        <v>28.28797059398123</v>
+        <v>0.0707</v>
       </c>
       <c r="K11" t="n">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="L11" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="M11" t="n">
-        <v>20.4276</v>
+        <v>1.9622</v>
       </c>
       <c r="N11" t="n">
-        <v>167</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.149</v>
+        <v>2.0518</v>
       </c>
       <c r="C12" t="n">
-        <v>2.77112</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.69019092801399</v>
+        <v>0.4075</v>
       </c>
       <c r="E12" t="n">
-        <v>16.7914</v>
+        <v>2.0518</v>
       </c>
       <c r="F12" t="n">
-        <v>19.81451364329774</v>
+        <v>1.3472</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.023158055751706</v>
+        <v>0.7046</v>
       </c>
       <c r="H12" t="n">
-        <v>19.81451364329774</v>
+        <v>1.3472</v>
       </c>
       <c r="I12" t="n">
-        <v>23.63836715340782</v>
+        <v>1.092</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.023158055751706</v>
+        <v>0.7046</v>
       </c>
       <c r="K12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L12" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="M12" t="n">
-        <v>20.6152</v>
+        <v>1.7966</v>
       </c>
       <c r="N12" t="n">
-        <v>191</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Zyphon</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7516</v>
+        <v>1.9723</v>
       </c>
       <c r="C13" t="n">
-        <v>2.421408</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5818548380762543</v>
+        <v>0.3754</v>
       </c>
       <c r="E13" t="n">
-        <v>12.0775</v>
+        <v>1.9723</v>
       </c>
       <c r="F13" t="n">
-        <v>12.07745789852978</v>
+        <v>1.507</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.4653</v>
       </c>
       <c r="H13" t="n">
-        <v>12.07745789852978</v>
+        <v>1.507</v>
       </c>
       <c r="I13" t="n">
-        <v>10.17049086191981</v>
+        <v>1.514</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.4653</v>
       </c>
       <c r="K13" t="n">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M13" t="n">
-        <v>10.1705</v>
+        <v>1.9793</v>
       </c>
       <c r="N13" t="n">
-        <v>84</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5922</v>
+        <v>1.8727</v>
       </c>
       <c r="C14" t="n">
-        <v>2.281136</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5403821045822521</v>
+        <v>0.3352</v>
       </c>
       <c r="E14" t="n">
-        <v>10.2729</v>
+        <v>1.8727</v>
       </c>
       <c r="F14" t="n">
-        <v>19.97426655221206</v>
+        <v>-0.4829</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.701361713396015</v>
+        <v>2.3556</v>
       </c>
       <c r="H14" t="n">
-        <v>19.97426655221206</v>
+        <v>-0.4829</v>
       </c>
       <c r="I14" t="n">
-        <v>21.02554373917059</v>
+        <v>-0.4829</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.701361713396015</v>
+        <v>2.3556</v>
       </c>
       <c r="K14" t="n">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="L14" t="n">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="M14" t="n">
-        <v>11.3242</v>
+        <v>1.8727</v>
       </c>
       <c r="N14" t="n">
-        <v>217</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5769</v>
+        <v>1.7682</v>
       </c>
       <c r="C15" t="n">
-        <v>2.267672</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5364508196961106</v>
+        <v>0.293</v>
       </c>
       <c r="E15" t="n">
-        <v>10.1018</v>
+        <v>1.7682</v>
       </c>
       <c r="F15" t="n">
-        <v>31.32872469088161</v>
+        <v>0.7651</v>
       </c>
       <c r="G15" t="n">
-        <v>-21.22687711239587</v>
+        <v>1.0031</v>
       </c>
       <c r="H15" t="n">
-        <v>31.49585103926523</v>
+        <v>0.7651</v>
       </c>
       <c r="I15" t="n">
-        <v>26.83856980789518</v>
+        <v>0.6201</v>
       </c>
       <c r="J15" t="n">
-        <v>-21.22687711239587</v>
+        <v>1.0031</v>
       </c>
       <c r="K15" t="n">
         <v>85</v>
       </c>
       <c r="L15" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M15" t="n">
-        <v>5.6117</v>
+        <v>1.6232</v>
       </c>
       <c r="N15" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>Zyphon</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4853</v>
+        <v>1.6937</v>
       </c>
       <c r="C16" t="n">
-        <v>2.187064</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5131819699951685</v>
+        <v>0.2629</v>
       </c>
       <c r="E16" t="n">
-        <v>9.089399999999999</v>
+        <v>1.6937</v>
       </c>
       <c r="F16" t="n">
-        <v>22.41638331378955</v>
+        <v>1.6937</v>
       </c>
       <c r="G16" t="n">
-        <v>-13.32700514318421</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>22.41638331378955</v>
+        <v>1.6937</v>
       </c>
       <c r="I16" t="n">
-        <v>20.45003390029923</v>
+        <v>1.6937</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.32700514318421</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L16" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>7.123</v>
+        <v>1.6937</v>
       </c>
       <c r="N16" t="n">
-        <v>125</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.196</v>
+        <v>1.5667</v>
       </c>
       <c r="C17" t="n">
-        <v>1.93248</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4419490652144421</v>
+        <v>0.2115</v>
       </c>
       <c r="E17" t="n">
-        <v>5.9899</v>
+        <v>1.5667</v>
       </c>
       <c r="F17" t="n">
-        <v>30.09092905040821</v>
+        <v>0.6481</v>
       </c>
       <c r="G17" t="n">
-        <v>-24.10102239867315</v>
+        <v>0.9186</v>
       </c>
       <c r="H17" t="n">
-        <v>30.10006227635755</v>
+        <v>0.6481</v>
       </c>
       <c r="I17" t="n">
-        <v>27.45970593632618</v>
+        <v>0.5253</v>
       </c>
       <c r="J17" t="n">
-        <v>-24.10102239867315</v>
+        <v>0.9186</v>
       </c>
       <c r="K17" t="n">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="L17" t="n">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3587</v>
+        <v>1.4439</v>
       </c>
       <c r="N17" t="n">
-        <v>125</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.186</v>
+        <v>1.2885</v>
       </c>
       <c r="C18" t="n">
-        <v>1.92368</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4395493909427444</v>
+        <v>0.0992</v>
       </c>
       <c r="E18" t="n">
-        <v>5.8855</v>
+        <v>1.2885</v>
       </c>
       <c r="F18" t="n">
-        <v>2.783254228232252</v>
+        <v>1.2885</v>
       </c>
       <c r="G18" t="n">
-        <v>3.102238289577087</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.783254228232252</v>
+        <v>1.2885</v>
       </c>
       <c r="I18" t="n">
-        <v>3.320373465259529</v>
+        <v>1.2885</v>
       </c>
       <c r="J18" t="n">
-        <v>3.102238289577087</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L18" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>6.4226</v>
+        <v>1.2885</v>
       </c>
       <c r="N18" t="n">
-        <v>191</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5485</v>
+        <v>1.0167</v>
       </c>
       <c r="C19" t="n">
-        <v>1.36268</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2944476960248361</v>
+        <v>-0.0106</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4281</v>
+        <v>1.0167</v>
       </c>
       <c r="F19" t="n">
-        <v>2.050721757717893</v>
+        <v>-0.5706</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.478864379768064</v>
+        <v>1.5873</v>
       </c>
       <c r="H19" t="n">
-        <v>2.050721757717893</v>
+        <v>-0.5706</v>
       </c>
       <c r="I19" t="n">
-        <v>1.747482199559107</v>
+        <v>-0.4625</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.478864379768064</v>
+        <v>1.5873</v>
       </c>
       <c r="K19" t="n">
         <v>85</v>
       </c>
       <c r="L19" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7314000000000001</v>
+        <v>1.1248</v>
       </c>
       <c r="N19" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5298</v>
+        <v>1.0124</v>
       </c>
       <c r="C20" t="n">
-        <v>1.346224</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2904206193283018</v>
+        <v>-0.0124</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6034</v>
+        <v>1.0124</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6033679559550066</v>
+        <v>2.0124</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6033679559550066</v>
+        <v>2.0124</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6714169735439171</v>
+        <v>2.0218</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K20" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6714</v>
+        <v>1.0218</v>
       </c>
       <c r="N20" t="n">
-        <v>111</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4554</v>
+        <v>0.9228</v>
       </c>
       <c r="C21" t="n">
-        <v>1.280752</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2745253126636562</v>
+        <v>-0.0486</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.295</v>
+        <v>0.9228</v>
       </c>
       <c r="F21" t="n">
-        <v>9.512660754852929</v>
+        <v>1.2595</v>
       </c>
       <c r="G21" t="n">
-        <v>-10.80766202889927</v>
+        <v>-0.3367</v>
       </c>
       <c r="H21" t="n">
-        <v>9.512660754852929</v>
+        <v>1.2595</v>
       </c>
       <c r="I21" t="n">
-        <v>11.25307237165559</v>
+        <v>1.2595</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.80766202889927</v>
+        <v>-0.3367</v>
       </c>
       <c r="K21" t="n">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="L21" t="n">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4454</v>
+        <v>0.9228000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>204</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3957</v>
+        <v>0.888</v>
       </c>
       <c r="C22" t="n">
-        <v>1.228216</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2618964450464194</v>
+        <v>-0.0626</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8445</v>
+        <v>0.888</v>
       </c>
       <c r="F22" t="n">
-        <v>-15.24702154397108</v>
+        <v>2.5026</v>
       </c>
       <c r="G22" t="n">
-        <v>13.40251557661341</v>
+        <v>-1.6146</v>
       </c>
       <c r="H22" t="n">
-        <v>-15.24702154397108</v>
+        <v>2.5026</v>
       </c>
       <c r="I22" t="n">
-        <v>-12.99244943596533</v>
+        <v>2.0284</v>
       </c>
       <c r="J22" t="n">
-        <v>13.40251557661341</v>
+        <v>-1.6146</v>
       </c>
       <c r="K22" t="n">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="L22" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4101</v>
+        <v>0.4137999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>167</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1149</v>
+        <v>0.6307</v>
       </c>
       <c r="C23" t="n">
-        <v>0.981112</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2042080675003039</v>
+        <v>-0.1666</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3546</v>
+        <v>0.6307</v>
       </c>
       <c r="F23" t="n">
-        <v>25.18255007246313</v>
+        <v>0.6087</v>
       </c>
       <c r="G23" t="n">
-        <v>-29.53718087221988</v>
+        <v>0.022</v>
       </c>
       <c r="H23" t="n">
-        <v>25.18255007246313</v>
+        <v>0.6087</v>
       </c>
       <c r="I23" t="n">
-        <v>30.04234043732443</v>
+        <v>0.6115</v>
       </c>
       <c r="J23" t="n">
-        <v>-29.53718087221988</v>
+        <v>0.022</v>
       </c>
       <c r="K23" t="n">
         <v>119</v>
@@ -1507,7 +1495,7 @@
         <v>72</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5052</v>
+        <v>0.6335000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>191</v>
@@ -1516,127 +1504,127 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3639</v>
+        <v>0.3456</v>
       </c>
       <c r="C24" t="n">
-        <v>0.320232</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.06252924472291904</v>
+        <v>-0.2817</v>
       </c>
       <c r="E24" t="n">
-        <v>-10.5193</v>
+        <v>0.3456</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.51933063022597</v>
+        <v>1.547</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-1.2014</v>
       </c>
       <c r="H24" t="n">
-        <v>-10.51933063022597</v>
+        <v>1.547</v>
       </c>
       <c r="I24" t="n">
-        <v>-11.70572130280785</v>
+        <v>1.547</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-1.2014</v>
       </c>
       <c r="K24" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="M24" t="n">
-        <v>-11.7057</v>
+        <v>0.3455999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>111</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.0818</v>
+        <v>0.3308</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.07198399999999999</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.01372874232063515</v>
+        <v>-0.2877</v>
       </c>
       <c r="E25" t="n">
-        <v>-13.8375</v>
+        <v>0.3308</v>
       </c>
       <c r="F25" t="n">
-        <v>1.254338266398305</v>
+        <v>-0.4416</v>
       </c>
       <c r="G25" t="n">
-        <v>-15.09179076257164</v>
+        <v>0.7724</v>
       </c>
       <c r="H25" t="n">
-        <v>1.254338266398305</v>
+        <v>-0.4416</v>
       </c>
       <c r="I25" t="n">
-        <v>1.483828726165413</v>
+        <v>-0.4416</v>
       </c>
       <c r="J25" t="n">
-        <v>-15.09179076257164</v>
+        <v>0.7724</v>
       </c>
       <c r="K25" t="n">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="L25" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M25" t="n">
-        <v>-13.608</v>
+        <v>0.3308</v>
       </c>
       <c r="N25" t="n">
-        <v>204</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.4883</v>
+        <v>0.2058</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.429704</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.08478554711743284</v>
+        <v>-0.3382</v>
       </c>
       <c r="E26" t="n">
-        <v>-16.9293</v>
+        <v>0.2058</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.23197092446972</v>
+        <v>1.2058</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.697290664250824</v>
+        <v>-1</v>
       </c>
       <c r="H26" t="n">
-        <v>-10.23197092446972</v>
+        <v>1.2058</v>
       </c>
       <c r="I26" t="n">
-        <v>-9.334429615305705</v>
+        <v>1.2058</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.697290664250824</v>
+        <v>-1</v>
       </c>
       <c r="K26" t="n">
         <v>91</v>
@@ -1645,7 +1633,7 @@
         <v>34</v>
       </c>
       <c r="M26" t="n">
-        <v>-16.0317</v>
+        <v>0.2058</v>
       </c>
       <c r="N26" t="n">
         <v>125</v>
@@ -1654,216 +1642,216 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.6723</v>
+        <v>-0.1048</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.591624</v>
+        <v>-0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1185721313626422</v>
+        <v>-0.4637</v>
       </c>
       <c r="E27" t="n">
-        <v>-18.3994</v>
+        <v>-0.1048</v>
       </c>
       <c r="F27" t="n">
-        <v>10.1704496475222</v>
+        <v>-0.1048</v>
       </c>
       <c r="G27" t="n">
-        <v>-28.56982614887047</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>10.1704496475222</v>
+        <v>-0.1048</v>
       </c>
       <c r="I27" t="n">
-        <v>10.70573647107599</v>
+        <v>-0.1048</v>
       </c>
       <c r="J27" t="n">
-        <v>-28.56982614887047</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L27" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-17.8641</v>
+        <v>-0.1048</v>
       </c>
       <c r="N27" t="n">
-        <v>217</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.7398</v>
+        <v>-0.1139</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.651024</v>
+        <v>-0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1312284892433106</v>
+        <v>-0.4674</v>
       </c>
       <c r="E28" t="n">
-        <v>-18.9501</v>
+        <v>-0.1139</v>
       </c>
       <c r="F28" t="n">
-        <v>-6.227638866787584</v>
+        <v>-0.6938</v>
       </c>
       <c r="G28" t="n">
-        <v>-12.72243847856692</v>
+        <v>0.5799</v>
       </c>
       <c r="H28" t="n">
-        <v>-6.227638866787584</v>
+        <v>-0.6938</v>
       </c>
       <c r="I28" t="n">
-        <v>-7.36703144141288</v>
+        <v>-0.697</v>
       </c>
       <c r="J28" t="n">
-        <v>-12.72243847856692</v>
+        <v>0.5799</v>
       </c>
       <c r="K28" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L28" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="M28" t="n">
-        <v>-20.0895</v>
+        <v>-0.1171</v>
       </c>
       <c r="N28" t="n">
-        <v>204</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.0885</v>
+        <v>-0.1531</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.9578800000000001</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1989216934433408</v>
+        <v>-0.4832</v>
       </c>
       <c r="E29" t="n">
-        <v>-21.8955</v>
+        <v>-0.1531</v>
       </c>
       <c r="F29" t="n">
-        <v>-21.89553013974669</v>
+        <v>-0.1458</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.0073</v>
       </c>
       <c r="H29" t="n">
-        <v>-21.89553013974669</v>
+        <v>-0.1458</v>
       </c>
       <c r="I29" t="n">
-        <v>-18.438341170313</v>
+        <v>-0.1458</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.0073</v>
       </c>
       <c r="K29" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M29" t="n">
-        <v>-18.4383</v>
+        <v>-0.1531</v>
       </c>
       <c r="N29" t="n">
-        <v>84</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.1544</v>
+        <v>-0.2782</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.015872</v>
+        <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.2121577022664346</v>
+        <v>-0.5337</v>
       </c>
       <c r="E30" t="n">
-        <v>-22.4715</v>
+        <v>-0.2782</v>
       </c>
       <c r="F30" t="n">
-        <v>-22.47145263647737</v>
+        <v>-0.013</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.2652</v>
       </c>
       <c r="H30" t="n">
-        <v>-22.47145263647737</v>
+        <v>-0.013</v>
       </c>
       <c r="I30" t="n">
-        <v>-25.00582699397482</v>
+        <v>-0.0131</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.2652</v>
       </c>
       <c r="K30" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M30" t="n">
-        <v>-25.0058</v>
+        <v>-0.2783</v>
       </c>
       <c r="N30" t="n">
-        <v>111</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dycha</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.4548</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.280224</v>
+        <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.274386859339731</v>
+        <v>-0.7624</v>
       </c>
       <c r="E31" t="n">
-        <v>-25.1792</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>-25.17915493481428</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-25.17915493481428</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-28.01890925077078</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1875,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-28.0189</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="N31" t="n">
         <v>111</v>
@@ -1884,185 +1872,185 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.7373</v>
+        <v>-0.8928</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.528824</v>
+        <v>-0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.3358268114966584</v>
+        <v>-0.782</v>
       </c>
       <c r="E32" t="n">
-        <v>-27.8525</v>
+        <v>-0.8928</v>
       </c>
       <c r="F32" t="n">
-        <v>-27.85251751096286</v>
+        <v>0.5503</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-1.4431</v>
       </c>
       <c r="H32" t="n">
-        <v>-27.85251751096286</v>
+        <v>0.5503</v>
       </c>
       <c r="I32" t="n">
-        <v>-30.99377888437972</v>
+        <v>0.5503</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-1.4431</v>
       </c>
       <c r="K32" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="M32" t="n">
-        <v>-30.9938</v>
+        <v>-0.8928</v>
       </c>
       <c r="N32" t="n">
-        <v>111</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.836</v>
+        <v>-0.9284</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.61568</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3579916600469261</v>
+        <v>-0.7964</v>
       </c>
       <c r="E33" t="n">
-        <v>-28.8169</v>
+        <v>-0.9284</v>
       </c>
       <c r="F33" t="n">
-        <v>-16.97464204520751</v>
+        <v>0.0716</v>
       </c>
       <c r="G33" t="n">
-        <v>-11.84230780237144</v>
+        <v>-1</v>
       </c>
       <c r="H33" t="n">
-        <v>-16.97464204520751</v>
+        <v>0.0716</v>
       </c>
       <c r="I33" t="n">
-        <v>-20.25045015919492</v>
+        <v>0.0716</v>
       </c>
       <c r="J33" t="n">
-        <v>-11.84230780237144</v>
+        <v>-1</v>
       </c>
       <c r="K33" t="n">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="L33" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="M33" t="n">
-        <v>-32.0928</v>
+        <v>-0.9284</v>
       </c>
       <c r="N33" t="n">
-        <v>191</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-2.1027</v>
+        <v>-0.9552</v>
       </c>
       <c r="C34" t="n">
-        <v>-1.850376</v>
+        <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.4196946323507854</v>
+        <v>-0.8072</v>
       </c>
       <c r="E34" t="n">
-        <v>-31.5018</v>
+        <v>-0.9552</v>
       </c>
       <c r="F34" t="n">
-        <v>-9.282136307386756</v>
+        <v>-0.9552</v>
       </c>
       <c r="G34" t="n">
-        <v>-22.21962059493973</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-9.282136307386756</v>
+        <v>-0.9552</v>
       </c>
       <c r="I34" t="n">
-        <v>-8.467913824282654</v>
+        <v>-0.9552</v>
       </c>
       <c r="J34" t="n">
-        <v>-22.21962059493973</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L34" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-30.6875</v>
+        <v>-0.9552</v>
       </c>
       <c r="N34" t="n">
-        <v>125</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-2.321</v>
+        <v>-1.0554</v>
       </c>
       <c r="C35" t="n">
-        <v>-2.04248</v>
+        <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.4723211700394103</v>
+        <v>-0.8477</v>
       </c>
       <c r="E35" t="n">
-        <v>-33.7916</v>
+        <v>-1.0554</v>
       </c>
       <c r="F35" t="n">
-        <v>-9.527661861845486</v>
+        <v>-1.0554</v>
       </c>
       <c r="G35" t="n">
-        <v>-24.26397013689543</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-9.527661861845486</v>
+        <v>-1.0554</v>
       </c>
       <c r="I35" t="n">
-        <v>-8.691902049402898</v>
+        <v>-1.0554</v>
       </c>
       <c r="J35" t="n">
-        <v>-24.26397013689543</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L35" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-32.9559</v>
+        <v>-1.0554</v>
       </c>
       <c r="N35" t="n">
-        <v>125</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36">
@@ -2072,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-2.6081</v>
+        <v>-1.0718</v>
       </c>
       <c r="C36" t="n">
-        <v>-2.295128</v>
+        <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.5444619445185108</v>
+        <v>-0.8542999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>-36.9306</v>
+        <v>-1.0718</v>
       </c>
       <c r="F36" t="n">
-        <v>-36.93060655741587</v>
+        <v>-1.0718</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-36.93060655741587</v>
+        <v>-1.0718</v>
       </c>
       <c r="I36" t="n">
-        <v>-31.09945815361337</v>
+        <v>-1.0718</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2105,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-31.0995</v>
+        <v>-1.0718</v>
       </c>
       <c r="N36" t="n">
         <v>84</v>
@@ -2114,32 +2102,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-2.6412</v>
+        <v>-1.1718</v>
       </c>
       <c r="C37" t="n">
-        <v>-2.324256</v>
+        <v>-0</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.5530083649986456</v>
+        <v>-0.8947000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>-37.3025</v>
+        <v>-1.1718</v>
       </c>
       <c r="F37" t="n">
-        <v>-37.30247664958758</v>
+        <v>-1.1718</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-37.30247664958758</v>
+        <v>-1.1718</v>
       </c>
       <c r="I37" t="n">
-        <v>-31.41261191544217</v>
+        <v>-1.1718</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2151,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-31.4126</v>
+        <v>-1.1718</v>
       </c>
       <c r="N37" t="n">
         <v>84</v>
@@ -2160,173 +2148,173 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.7923</v>
+        <v>-1.193</v>
       </c>
       <c r="C38" t="n">
-        <v>-2.457224</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.5926221880506466</v>
+        <v>-0.9033</v>
       </c>
       <c r="E38" t="n">
-        <v>-39.0261</v>
+        <v>-1.193</v>
       </c>
       <c r="F38" t="n">
-        <v>-20.97892937061761</v>
+        <v>-1.193</v>
       </c>
       <c r="G38" t="n">
-        <v>-18.04721580942228</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-20.97892937061761</v>
+        <v>-1.193</v>
       </c>
       <c r="I38" t="n">
-        <v>-22.08308354801854</v>
+        <v>-1.193</v>
       </c>
       <c r="J38" t="n">
-        <v>-18.04721580942228</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L38" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-40.1303</v>
+        <v>-1.193</v>
       </c>
       <c r="N38" t="n">
-        <v>217</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>dycha</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-3.0291</v>
+        <v>-1.2688</v>
       </c>
       <c r="C39" t="n">
-        <v>-2.665608</v>
+        <v>-0</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.6567451864885939</v>
+        <v>-0.9339</v>
       </c>
       <c r="E39" t="n">
-        <v>-41.8163</v>
+        <v>-1.2688</v>
       </c>
       <c r="F39" t="n">
-        <v>-41.81625191476842</v>
+        <v>-1.2688</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-41.81625191476842</v>
+        <v>-1.2688</v>
       </c>
       <c r="I39" t="n">
-        <v>-35.21368582296288</v>
+        <v>-1.2688</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-35.2137</v>
+        <v>-1.2688</v>
       </c>
       <c r="N39" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.6866</v>
+        <v>-1.4141</v>
       </c>
       <c r="C40" t="n">
-        <v>-3.244208</v>
+        <v>-0</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.8486216754650827</v>
+        <v>-0.9926</v>
       </c>
       <c r="E40" t="n">
-        <v>-50.1651</v>
+        <v>-1.4141</v>
       </c>
       <c r="F40" t="n">
-        <v>9.892331703661133</v>
+        <v>-0.4141</v>
       </c>
       <c r="G40" t="n">
-        <v>-60.05747398804378</v>
+        <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>9.892331703661133</v>
+        <v>-0.4141</v>
       </c>
       <c r="I40" t="n">
-        <v>11.70220692763924</v>
+        <v>-0.4141</v>
       </c>
       <c r="J40" t="n">
-        <v>-60.05747398804378</v>
+        <v>-1</v>
       </c>
       <c r="K40" t="n">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="L40" t="n">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="M40" t="n">
-        <v>-48.3553</v>
+        <v>-1.4141</v>
       </c>
       <c r="N40" t="n">
-        <v>204</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.1594</v>
+        <v>-1.8356</v>
       </c>
       <c r="C41" t="n">
-        <v>-3.660272</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.000164451428045</v>
+        <v>-1.1629</v>
       </c>
       <c r="E41" t="n">
-        <v>-56.759</v>
+        <v>-1.8356</v>
       </c>
       <c r="F41" t="n">
-        <v>-6.485864144429096</v>
+        <v>-1.39</v>
       </c>
       <c r="G41" t="n">
-        <v>-50.27317627500234</v>
+        <v>-0.4456</v>
       </c>
       <c r="H41" t="n">
-        <v>-6.485864144429096</v>
+        <v>-1.39</v>
       </c>
       <c r="I41" t="n">
-        <v>-6.827225415188521</v>
+        <v>-1.39</v>
       </c>
       <c r="J41" t="n">
-        <v>-50.27317627500234</v>
+        <v>-0.4456</v>
       </c>
       <c r="K41" t="n">
         <v>105</v>
@@ -2335,7 +2323,7 @@
         <v>112</v>
       </c>
       <c r="M41" t="n">
-        <v>-57.1004</v>
+        <v>-1.8356</v>
       </c>
       <c r="N41" t="n">
         <v>217</v>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2441,10 +2429,10 @@
         <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5189257133580483</v>
+        <v>0.6737</v>
       </c>
       <c r="J2" t="n">
-        <v>9.340662840444869</v>
+        <v>12.1266</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2469,10 @@
         <v>0.76</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.167535631225212</v>
+        <v>-0.3896</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.01564136205381</v>
+        <v>-7.0128</v>
       </c>
     </row>
     <row r="4">
@@ -2521,10 +2509,10 @@
         <v>0.7</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.31295241197679</v>
+        <v>-0.4786</v>
       </c>
       <c r="J4" t="n">
-        <v>-23.63314341558222</v>
+        <v>-8.614800000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2561,10 +2549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.335073102388797</v>
+        <v>-0.4927</v>
       </c>
       <c r="J5" t="n">
-        <v>-24.03131584299835</v>
+        <v>-8.868600000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2601,10 +2589,10 @@
         <v>0.61</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.497272822287971</v>
+        <v>-0.601</v>
       </c>
       <c r="J6" t="n">
-        <v>-26.95091080118348</v>
+        <v>-10.818</v>
       </c>
     </row>
     <row r="7">
@@ -2641,10 +2629,10 @@
         <v>1.67</v>
       </c>
       <c r="I7" t="n">
-        <v>2.046772735471317</v>
+        <v>1.4891</v>
       </c>
       <c r="J7" t="n">
-        <v>36.84190923848369</v>
+        <v>26.8038</v>
       </c>
     </row>
     <row r="8">
@@ -2681,10 +2669,10 @@
         <v>1.65</v>
       </c>
       <c r="I8" t="n">
-        <v>2.008314240435828</v>
+        <v>1.4519</v>
       </c>
       <c r="J8" t="n">
-        <v>36.14965632784489</v>
+        <v>26.1342</v>
       </c>
     </row>
     <row r="9">
@@ -2721,10 +2709,10 @@
         <v>1.45</v>
       </c>
       <c r="I9" t="n">
-        <v>1.55602559959061</v>
+        <v>1.0561</v>
       </c>
       <c r="J9" t="n">
-        <v>28.00846079263098</v>
+        <v>19.0098</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2749,10 @@
         <v>1.1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3841017281597306</v>
+        <v>0.1851</v>
       </c>
       <c r="J10" t="n">
-        <v>6.913831106875151</v>
+        <v>3.3318</v>
       </c>
     </row>
     <row r="11">
@@ -2801,10 +2789,10 @@
         <v>0.77</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5091507405162743</v>
+        <v>-0.8257</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.164713329292937</v>
+        <v>-14.8626</v>
       </c>
     </row>
     <row r="12">
@@ -2841,10 +2829,10 @@
         <v>1.54</v>
       </c>
       <c r="I12" t="n">
-        <v>1.009602806398954</v>
+        <v>0.8224</v>
       </c>
       <c r="J12" t="n">
-        <v>20.19205612797907</v>
+        <v>16.448</v>
       </c>
     </row>
     <row r="13">
@@ -2881,10 +2869,10 @@
         <v>1.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1461180493296589</v>
+        <v>0.397</v>
       </c>
       <c r="J13" t="n">
-        <v>2.922360986593178</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="14">
@@ -2921,10 +2909,10 @@
         <v>0.77</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.189914784840347</v>
+        <v>-0.4174</v>
       </c>
       <c r="J14" t="n">
-        <v>-23.79829569680693</v>
+        <v>-8.348000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -2961,10 +2949,10 @@
         <v>0.75</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.231759399267925</v>
+        <v>-0.4454</v>
       </c>
       <c r="J15" t="n">
-        <v>-24.6351879853585</v>
+        <v>-8.907999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -3001,10 +2989,10 @@
         <v>0.55</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.590064395490312</v>
+        <v>-0.7005</v>
       </c>
       <c r="J16" t="n">
-        <v>-31.80128790980623</v>
+        <v>-14.01</v>
       </c>
     </row>
     <row r="17">
@@ -3041,10 +3029,10 @@
         <v>2.2</v>
       </c>
       <c r="I17" t="n">
-        <v>2.748912062566378</v>
+        <v>2.219</v>
       </c>
       <c r="J17" t="n">
-        <v>54.97824125132755</v>
+        <v>44.38</v>
       </c>
     </row>
     <row r="18">
@@ -3081,10 +3069,10 @@
         <v>1.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1827601460361046</v>
+        <v>0.113</v>
       </c>
       <c r="J18" t="n">
-        <v>3.655202920722092</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="19">
@@ -3121,10 +3109,10 @@
         <v>1.06</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1827601460361046</v>
+        <v>0.113</v>
       </c>
       <c r="J19" t="n">
-        <v>3.655202920722092</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="20">
@@ -3161,10 +3149,10 @@
         <v>0.9</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3681259012609412</v>
+        <v>-0.478</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.362518025218825</v>
+        <v>-9.56</v>
       </c>
     </row>
     <row r="21">
@@ -3201,10 +3189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.581992421169365</v>
+        <v>-0.7076</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.6398484233873</v>
+        <v>-14.152</v>
       </c>
     </row>
     <row r="22">
@@ -3241,10 +3229,10 @@
         <v>1.53</v>
       </c>
       <c r="I22" t="n">
-        <v>0.943380008384987</v>
+        <v>1.2672</v>
       </c>
       <c r="J22" t="n">
-        <v>16.98084015092977</v>
+        <v>22.8096</v>
       </c>
     </row>
     <row r="23">
@@ -3281,10 +3269,10 @@
         <v>1.46</v>
       </c>
       <c r="I23" t="n">
-        <v>0.867462974142289</v>
+        <v>1.1262</v>
       </c>
       <c r="J23" t="n">
-        <v>15.6143335345612</v>
+        <v>20.2716</v>
       </c>
     </row>
     <row r="24">
@@ -3321,10 +3309,10 @@
         <v>1.16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3595743140796611</v>
+        <v>0.3878</v>
       </c>
       <c r="J24" t="n">
-        <v>6.4723376534339</v>
+        <v>6.9804</v>
       </c>
     </row>
     <row r="25">
@@ -3361,10 +3349,10 @@
         <v>1.14</v>
       </c>
       <c r="I25" t="n">
-        <v>0.326423189092615</v>
+        <v>0.3336</v>
       </c>
       <c r="J25" t="n">
-        <v>5.875617403667071</v>
+        <v>6.0048</v>
       </c>
     </row>
     <row r="26">
@@ -3401,10 +3389,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1244228070875106</v>
+        <v>-0.5904</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.239610527575191</v>
+        <v>-10.6272</v>
       </c>
     </row>
     <row r="27">
@@ -3441,10 +3429,10 @@
         <v>1.03</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2192114746873489</v>
+        <v>0.155</v>
       </c>
       <c r="J27" t="n">
-        <v>-3.945806544372281</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="28">
@@ -3481,10 +3469,10 @@
         <v>0.97</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3224608216794144</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.804294790229459</v>
+        <v>-0.1728</v>
       </c>
     </row>
     <row r="29">
@@ -3521,10 +3509,10 @@
         <v>0.85</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5916715310753876</v>
+        <v>-0.2466</v>
       </c>
       <c r="J29" t="n">
-        <v>-10.65008755935698</v>
+        <v>-4.4388</v>
       </c>
     </row>
     <row r="30">
@@ -3561,10 +3549,10 @@
         <v>0.77</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7697875689562654</v>
+        <v>-0.3845</v>
       </c>
       <c r="J30" t="n">
-        <v>-13.85617624121278</v>
+        <v>-6.921</v>
       </c>
     </row>
     <row r="31">
@@ -3601,10 +3589,10 @@
         <v>0.64</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9678576258805002</v>
+        <v>-0.5679</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.421437265849</v>
+        <v>-10.2222</v>
       </c>
     </row>
     <row r="32">
@@ -3641,10 +3629,10 @@
         <v>1.38</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6632154287094185</v>
+        <v>0.9882</v>
       </c>
       <c r="J32" t="n">
-        <v>14.59073943160721</v>
+        <v>21.7404</v>
       </c>
     </row>
     <row r="33">
@@ -3681,10 +3669,10 @@
         <v>1.28</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5265679735333403</v>
+        <v>0.7621</v>
       </c>
       <c r="J33" t="n">
-        <v>11.58449541773349</v>
+        <v>16.7662</v>
       </c>
     </row>
     <row r="34">
@@ -3721,10 +3709,10 @@
         <v>1.22</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4267377628067657</v>
+        <v>0.6128</v>
       </c>
       <c r="J34" t="n">
-        <v>9.388230781748845</v>
+        <v>13.4816</v>
       </c>
     </row>
     <row r="35">
@@ -3761,10 +3749,10 @@
         <v>1.15</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2510563271986412</v>
+        <v>0.3994</v>
       </c>
       <c r="J35" t="n">
-        <v>5.523239198370106</v>
+        <v>8.786799999999999</v>
       </c>
     </row>
     <row r="36">
@@ -3801,10 +3789,10 @@
         <v>0.82</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4133252486075248</v>
+        <v>-0.6742</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.093155469365545</v>
+        <v>-14.8324</v>
       </c>
     </row>
     <row r="37">
@@ -3841,10 +3829,10 @@
         <v>1.32</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5375134136836347</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>11.82529510103996</v>
+        <v>12.408</v>
       </c>
     </row>
     <row r="38">
@@ -3881,10 +3869,10 @@
         <v>1.2</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2872211152664285</v>
+        <v>0.402</v>
       </c>
       <c r="J38" t="n">
-        <v>6.318864535861426</v>
+        <v>8.843999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -3921,10 +3909,10 @@
         <v>0.88</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5245385727317987</v>
+        <v>-0.244</v>
       </c>
       <c r="J39" t="n">
-        <v>-11.53984860009957</v>
+        <v>-5.368</v>
       </c>
     </row>
     <row r="40">
@@ -3961,10 +3949,10 @@
         <v>0.82</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6325357529214251</v>
+        <v>-0.3404</v>
       </c>
       <c r="J40" t="n">
-        <v>-13.91578656427135</v>
+        <v>-7.4888</v>
       </c>
     </row>
     <row r="41">
@@ -4001,10 +3989,10 @@
         <v>0.52</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.02454526975708</v>
+        <v>-0.7341</v>
       </c>
       <c r="J41" t="n">
-        <v>-22.53999593465576</v>
+        <v>-16.1502</v>
       </c>
     </row>
     <row r="42">
@@ -4041,10 +4029,10 @@
         <v>1.39</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8729517885805228</v>
+        <v>1.073</v>
       </c>
       <c r="J42" t="n">
-        <v>20.95084292593255</v>
+        <v>25.752</v>
       </c>
     </row>
     <row r="43">
@@ -4081,10 +4069,10 @@
         <v>1.27</v>
       </c>
       <c r="I43" t="n">
-        <v>0.687573516255459</v>
+        <v>0.8061</v>
       </c>
       <c r="J43" t="n">
-        <v>16.50176439013102</v>
+        <v>19.3464</v>
       </c>
     </row>
     <row r="44">
@@ -4121,10 +4109,10 @@
         <v>0.99</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.05221280376337322</v>
+        <v>-0.1124</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.253107290320957</v>
+        <v>-2.6976</v>
       </c>
     </row>
     <row r="45">
@@ -4161,10 +4149,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2133733379941209</v>
+        <v>-0.3322</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.120960111858901</v>
+        <v>-7.9728</v>
       </c>
     </row>
     <row r="46">
@@ -4201,10 +4189,10 @@
         <v>0.68</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6206301713679256</v>
+        <v>-0.9649</v>
       </c>
       <c r="J46" t="n">
-        <v>-14.89512411283022</v>
+        <v>-23.1576</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4229,10 @@
         <v>1.26</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6269440594510068</v>
+        <v>0.4706</v>
       </c>
       <c r="J47" t="n">
-        <v>15.04665742682417</v>
+        <v>11.2944</v>
       </c>
     </row>
     <row r="48">
@@ -4281,10 +4269,10 @@
         <v>1.08</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1815828118258184</v>
+        <v>0.1967</v>
       </c>
       <c r="J48" t="n">
-        <v>4.357987483819642</v>
+        <v>4.7208</v>
       </c>
     </row>
     <row r="49">
@@ -4321,10 +4309,10 @@
         <v>0.92</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3510091404881059</v>
+        <v>-0.1892</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.424219371714543</v>
+        <v>-4.5408</v>
       </c>
     </row>
     <row r="50">
@@ -4361,10 +4349,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3723298941961096</v>
+        <v>-0.2072</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.93591746070663</v>
+        <v>-4.9728</v>
       </c>
     </row>
     <row r="51">
@@ -4401,10 +4389,10 @@
         <v>0.78</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6029126924395304</v>
+        <v>-0.4098</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.46990461854873</v>
+        <v>-9.8352</v>
       </c>
     </row>
     <row r="52">
@@ -4441,10 +4429,10 @@
         <v>1.29</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7114968788954561</v>
+        <v>0.8456</v>
       </c>
       <c r="J52" t="n">
-        <v>17.07592509349094</v>
+        <v>20.2944</v>
       </c>
     </row>
     <row r="53">
@@ -4481,10 +4469,10 @@
         <v>1.28</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6947823436765862</v>
+        <v>0.8225</v>
       </c>
       <c r="J53" t="n">
-        <v>16.67477624823807</v>
+        <v>19.74</v>
       </c>
     </row>
     <row r="54">
@@ -4521,10 +4509,10 @@
         <v>1.1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3189408081936034</v>
+        <v>0.3503</v>
       </c>
       <c r="J54" t="n">
-        <v>7.654579396646481</v>
+        <v>8.4072</v>
       </c>
     </row>
     <row r="55">
@@ -4561,10 +4549,10 @@
         <v>1.07</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2224160500568527</v>
+        <v>0.248</v>
       </c>
       <c r="J55" t="n">
-        <v>5.337985201364466</v>
+        <v>5.952</v>
       </c>
     </row>
     <row r="56">
@@ -4601,10 +4589,10 @@
         <v>0.58</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7479052393366007</v>
+        <v>-1.1799</v>
       </c>
       <c r="J56" t="n">
-        <v>-17.94972574407842</v>
+        <v>-28.3176</v>
       </c>
     </row>
     <row r="57">
@@ -4641,10 +4629,10 @@
         <v>1.45</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9511695197275176</v>
+        <v>0.7103</v>
       </c>
       <c r="J57" t="n">
-        <v>22.82806847346042</v>
+        <v>17.0472</v>
       </c>
     </row>
     <row r="58">
@@ -4681,10 +4669,10 @@
         <v>1.13</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3200086379694909</v>
+        <v>0.2827</v>
       </c>
       <c r="J58" t="n">
-        <v>7.680207311267782</v>
+        <v>6.7848</v>
       </c>
     </row>
     <row r="59">
@@ -4721,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3549927179862689</v>
+        <v>-0.1877</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.519825231670454</v>
+        <v>-4.5048</v>
       </c>
     </row>
     <row r="60">
@@ -4761,10 +4749,10 @@
         <v>0.76</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.6365430546414942</v>
+        <v>-0.4369</v>
       </c>
       <c r="J60" t="n">
-        <v>-15.27703331139586</v>
+        <v>-10.4856</v>
       </c>
     </row>
     <row r="61">
@@ -4801,10 +4789,10 @@
         <v>0.67</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7609805696972219</v>
+        <v>-0.5565</v>
       </c>
       <c r="J61" t="n">
-        <v>-18.26353367273333</v>
+        <v>-13.356</v>
       </c>
     </row>
     <row r="62">
@@ -4841,10 +4829,10 @@
         <v>1.18</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2292420030547515</v>
+        <v>0.3708</v>
       </c>
       <c r="J62" t="n">
-        <v>6.648018088587794</v>
+        <v>10.7532</v>
       </c>
     </row>
     <row r="63">
@@ -4881,10 +4869,10 @@
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1109506626704353</v>
+        <v>0.029</v>
       </c>
       <c r="J63" t="n">
-        <v>-3.217569217442624</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="64">
@@ -4921,10 +4909,10 @@
         <v>0.98</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1500230287942961</v>
+        <v>-0.0334</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.350667835034588</v>
+        <v>-0.9686</v>
       </c>
     </row>
     <row r="65">
@@ -4961,10 +4949,10 @@
         <v>0.91</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3143300694149517</v>
+        <v>-0.1932</v>
       </c>
       <c r="J65" t="n">
-        <v>-9.115572013033599</v>
+        <v>-5.6028</v>
       </c>
     </row>
     <row r="66">
@@ -5001,10 +4989,10 @@
         <v>0.7</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5919965405451826</v>
+        <v>-0.5114</v>
       </c>
       <c r="J66" t="n">
-        <v>-17.16789967581029</v>
+        <v>-14.8306</v>
       </c>
     </row>
     <row r="67">
@@ -5041,10 +5029,10 @@
         <v>1.41</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5903641362878856</v>
+        <v>0.6216</v>
       </c>
       <c r="J67" t="n">
-        <v>17.12055995234869</v>
+        <v>18.0264</v>
       </c>
     </row>
     <row r="68">
@@ -5081,10 +5069,10 @@
         <v>1.23</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3953564041500712</v>
+        <v>0.3873</v>
       </c>
       <c r="J68" t="n">
-        <v>11.46533572035206</v>
+        <v>11.2317</v>
       </c>
     </row>
     <row r="69">
@@ -5121,10 +5109,10 @@
         <v>1.15</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2785939138803005</v>
+        <v>0.2651</v>
       </c>
       <c r="J69" t="n">
-        <v>8.079223502528714</v>
+        <v>7.6879</v>
       </c>
     </row>
     <row r="70">
@@ -5161,10 +5149,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1590286158200973</v>
+        <v>-0.2068</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.611829858782823</v>
+        <v>-5.9972</v>
       </c>
     </row>
     <row r="71">
@@ -5201,10 +5189,10 @@
         <v>0.85</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2817602978747783</v>
+        <v>-0.3346</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.171048638368571</v>
+        <v>-9.7034</v>
       </c>
     </row>
     <row r="72">
@@ -5241,10 +5229,10 @@
         <v>1.85</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9785629482056087</v>
+        <v>1.8475</v>
       </c>
       <c r="J72" t="n">
-        <v>23.48551075693461</v>
+        <v>44.34</v>
       </c>
     </row>
     <row r="73">
@@ -5281,10 +5269,10 @@
         <v>0.98</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.07010557626588521</v>
+        <v>-0.1554</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.682533830381245</v>
+        <v>-3.7296</v>
       </c>
     </row>
     <row r="74">
@@ -5321,10 +5309,10 @@
         <v>0.85</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2882294214669627</v>
+        <v>-0.5591</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.917506115207104</v>
+        <v>-13.4184</v>
       </c>
     </row>
     <row r="75">
@@ -5361,10 +5349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3404471982215506</v>
+        <v>-0.6615</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.170732757317214</v>
+        <v>-15.876</v>
       </c>
     </row>
     <row r="76">
@@ -5401,10 +5389,10 @@
         <v>0.76</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4003826606489705</v>
+        <v>-0.7825</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.609183855575292</v>
+        <v>-18.78</v>
       </c>
     </row>
     <row r="77">
@@ -5441,10 +5429,10 @@
         <v>1.28</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3698228554901686</v>
+        <v>0.4967</v>
       </c>
       <c r="J77" t="n">
-        <v>8.875748531764046</v>
+        <v>11.9208</v>
       </c>
     </row>
     <row r="78">
@@ -5481,10 +5469,10 @@
         <v>1.16</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2257463187814533</v>
+        <v>0.3273</v>
       </c>
       <c r="J78" t="n">
-        <v>5.417911650754879</v>
+        <v>7.8552</v>
       </c>
     </row>
     <row r="79">
@@ -5521,10 +5509,10 @@
         <v>0.96</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2020550594914226</v>
+        <v>-0.1109</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.849321427794143</v>
+        <v>-2.6616</v>
       </c>
     </row>
     <row r="80">
@@ -5561,10 +5549,10 @@
         <v>0.8</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4490212082550642</v>
+        <v>-0.3817</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.77650899812154</v>
+        <v>-9.1608</v>
       </c>
     </row>
     <row r="81">
@@ -5601,10 +5589,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.497312038014579</v>
+        <v>-0.4382</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.9354889123499</v>
+        <v>-10.5168</v>
       </c>
     </row>
     <row r="82">
@@ -5641,10 +5629,10 @@
         <v>2.32</v>
       </c>
       <c r="I82" t="n">
-        <v>1.316314475705912</v>
+        <v>2.2006</v>
       </c>
       <c r="J82" t="n">
-        <v>25.00997503841234</v>
+        <v>41.8114</v>
       </c>
     </row>
     <row r="83">
@@ -5681,10 +5669,10 @@
         <v>1.1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1425719690080419</v>
+        <v>0.199</v>
       </c>
       <c r="J83" t="n">
-        <v>2.708867411152797</v>
+        <v>3.781</v>
       </c>
     </row>
     <row r="84">
@@ -5721,10 +5709,10 @@
         <v>1.04</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0647476971685905</v>
+        <v>0.0182</v>
       </c>
       <c r="J84" t="n">
-        <v>1.23020624620322</v>
+        <v>0.3458</v>
       </c>
     </row>
     <row r="85">
@@ -5761,10 +5749,10 @@
         <v>1.01</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0255980404693296</v>
+        <v>-0.0945</v>
       </c>
       <c r="J85" t="n">
-        <v>0.4863627689172624</v>
+        <v>-1.7955</v>
       </c>
     </row>
     <row r="86">
@@ -5801,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.02780922719826501</v>
+        <v>-0.2882</v>
       </c>
       <c r="J86" t="n">
-        <v>-0.5283753167670352</v>
+        <v>-5.4758</v>
       </c>
     </row>
     <row r="87">
@@ -5841,10 +5829,10 @@
         <v>1.41</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3052380939563112</v>
+        <v>0.6965</v>
       </c>
       <c r="J87" t="n">
-        <v>5.799523785169914</v>
+        <v>13.2335</v>
       </c>
     </row>
     <row r="88">
@@ -5881,10 +5869,10 @@
         <v>0.86</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.5073248604373488</v>
+        <v>-0.2544</v>
       </c>
       <c r="J88" t="n">
-        <v>-9.639172348309627</v>
+        <v>-4.8336</v>
       </c>
     </row>
     <row r="89">
@@ -5921,10 +5909,10 @@
         <v>0.75</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.6603688260929955</v>
+        <v>-0.4273</v>
       </c>
       <c r="J89" t="n">
-        <v>-12.54700769576691</v>
+        <v>-8.1187</v>
       </c>
     </row>
     <row r="90">
@@ -5961,10 +5949,10 @@
         <v>0.73</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6836769526887982</v>
+        <v>-0.4558</v>
       </c>
       <c r="J90" t="n">
-        <v>-12.98986210108717</v>
+        <v>-8.6602</v>
       </c>
     </row>
     <row r="91">
@@ -6001,10 +5989,10 @@
         <v>0.71</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7061066575904851</v>
+        <v>-0.4836</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.41602649421922</v>
+        <v>-9.1884</v>
       </c>
     </row>
     <row r="92">
@@ -6041,10 +6029,10 @@
         <v>0.83</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.4715090091269372</v>
+        <v>-0.1441</v>
       </c>
       <c r="J92" t="n">
-        <v>-6.601126127777121</v>
+        <v>-2.0174</v>
       </c>
     </row>
     <row r="93">
@@ -6081,10 +6069,10 @@
         <v>0.66</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.6655872442253485</v>
+        <v>-0.4107</v>
       </c>
       <c r="J93" t="n">
-        <v>-9.318221419154879</v>
+        <v>-5.7498</v>
       </c>
     </row>
     <row r="94">
@@ -6121,10 +6109,10 @@
         <v>0.63</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.7124169411326321</v>
+        <v>-0.4613</v>
       </c>
       <c r="J94" t="n">
-        <v>-9.973837175856849</v>
+        <v>-6.4582</v>
       </c>
     </row>
     <row r="95">
@@ -6161,10 +6149,10 @@
         <v>0.62</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.7313322699006864</v>
+        <v>-0.4798</v>
       </c>
       <c r="J95" t="n">
-        <v>-10.23865177860961</v>
+        <v>-6.7172</v>
       </c>
     </row>
     <row r="96">
@@ -6201,10 +6189,10 @@
         <v>0.31</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.106695827109474</v>
+        <v>-0.9304</v>
       </c>
       <c r="J96" t="n">
-        <v>-15.49374157953264</v>
+        <v>-13.0256</v>
       </c>
     </row>
     <row r="97">
@@ -6241,10 +6229,10 @@
         <v>2.01</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9865072915983855</v>
+        <v>1.8521</v>
       </c>
       <c r="J97" t="n">
-        <v>13.8111020823774</v>
+        <v>25.9294</v>
       </c>
     </row>
     <row r="98">
@@ -6281,10 +6269,10 @@
         <v>1.72</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7580769328004323</v>
+        <v>1.4476</v>
       </c>
       <c r="J98" t="n">
-        <v>10.61307705920605</v>
+        <v>20.2664</v>
       </c>
     </row>
     <row r="99">
@@ -6321,10 +6309,10 @@
         <v>1.61</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5947708206383407</v>
+        <v>1.2068</v>
       </c>
       <c r="J99" t="n">
-        <v>8.32679148893677</v>
+        <v>16.8952</v>
       </c>
     </row>
     <row r="100">
@@ -6361,10 +6349,10 @@
         <v>1.46</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4371464129231094</v>
+        <v>0.9022</v>
       </c>
       <c r="J100" t="n">
-        <v>6.120049780923532</v>
+        <v>12.6308</v>
       </c>
     </row>
     <row r="101">
@@ -6401,10 +6389,10 @@
         <v>1.38</v>
       </c>
       <c r="I101" t="n">
-        <v>0.3698880570413586</v>
+        <v>0.7403</v>
       </c>
       <c r="J101" t="n">
-        <v>5.17843279857902</v>
+        <v>10.3642</v>
       </c>
     </row>
     <row r="102">
@@ -6441,10 +6429,10 @@
         <v>1.22</v>
       </c>
       <c r="I102" t="n">
-        <v>0.1770680557179393</v>
+        <v>0.4725</v>
       </c>
       <c r="J102" t="n">
-        <v>3.541361114358785</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="103">
@@ -6481,10 +6469,10 @@
         <v>0.87</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.3362939507703544</v>
+        <v>-0.1926</v>
       </c>
       <c r="J103" t="n">
-        <v>-6.725879015407088</v>
+        <v>-3.852</v>
       </c>
     </row>
     <row r="104">
@@ -6521,10 +6509,10 @@
         <v>0.87</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3362939507703544</v>
+        <v>-0.1926</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.725879015407088</v>
+        <v>-3.852</v>
       </c>
     </row>
     <row r="105">
@@ -6561,10 +6549,10 @@
         <v>0.63</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7063592611408152</v>
+        <v>-0.5772</v>
       </c>
       <c r="J105" t="n">
-        <v>-14.1271852228163</v>
+        <v>-11.544</v>
       </c>
     </row>
     <row r="106">
@@ -6601,10 +6589,10 @@
         <v>0.59</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7472874358870277</v>
+        <v>-0.6292</v>
       </c>
       <c r="J106" t="n">
-        <v>-14.94574871774056</v>
+        <v>-12.584</v>
       </c>
     </row>
     <row r="107">
@@ -6641,10 +6629,10 @@
         <v>1.77</v>
       </c>
       <c r="I107" t="n">
-        <v>0.83682384329501</v>
+        <v>1.7036</v>
       </c>
       <c r="J107" t="n">
-        <v>16.7364768659002</v>
+        <v>34.072</v>
       </c>
     </row>
     <row r="108">
@@ -6681,10 +6669,10 @@
         <v>1.26</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3961492154978516</v>
+        <v>0.6694</v>
       </c>
       <c r="J108" t="n">
-        <v>7.922984309957032</v>
+        <v>13.388</v>
       </c>
     </row>
     <row r="109">
@@ -6721,10 +6709,10 @@
         <v>1.26</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3961492154978516</v>
+        <v>0.6694</v>
       </c>
       <c r="J109" t="n">
-        <v>7.922984309957032</v>
+        <v>13.388</v>
       </c>
     </row>
     <row r="110">
@@ -6761,10 +6749,10 @@
         <v>0.97</v>
       </c>
       <c r="I110" t="n">
-        <v>0.01412215667364918</v>
+        <v>-0.2728</v>
       </c>
       <c r="J110" t="n">
-        <v>0.2824431334729837</v>
+        <v>-5.456</v>
       </c>
     </row>
     <row r="111">
@@ -6801,10 +6789,10 @@
         <v>0.92</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.05378490296109092</v>
+        <v>-0.4303</v>
       </c>
       <c r="J111" t="n">
-        <v>-1.075698059221819</v>
+        <v>-8.606</v>
       </c>
     </row>
     <row r="112">
@@ -6841,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.04427153580308898</v>
+        <v>0.2988</v>
       </c>
       <c r="J112" t="n">
-        <v>0.8854307160617797</v>
+        <v>5.976</v>
       </c>
     </row>
     <row r="113">
@@ -6881,10 +6869,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.006149125623482105</v>
+        <v>0.2304</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.1229825124696421</v>
+        <v>4.608</v>
       </c>
     </row>
     <row r="114">
@@ -6921,10 +6909,10 @@
         <v>0.78</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3760170159871974</v>
+        <v>-0.3714</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.520340319743949</v>
+        <v>-7.428</v>
       </c>
     </row>
     <row r="115">
@@ -6961,10 +6949,10 @@
         <v>0.72</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4358515208550559</v>
+        <v>-0.4601</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.717030417101117</v>
+        <v>-9.202</v>
       </c>
     </row>
     <row r="116">
@@ -7001,10 +6989,10 @@
         <v>0.61</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5279622304217491</v>
+        <v>-0.6083</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.55924460843498</v>
+        <v>-12.166</v>
       </c>
     </row>
     <row r="117">
@@ -7041,10 +7029,10 @@
         <v>1.47</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8827256973957027</v>
+        <v>0.6857</v>
       </c>
       <c r="J117" t="n">
-        <v>17.65451394791405</v>
+        <v>13.714</v>
       </c>
     </row>
     <row r="118">
@@ -7081,10 +7069,10 @@
         <v>1.44</v>
       </c>
       <c r="I118" t="n">
-        <v>0.8514719583141858</v>
+        <v>0.6503</v>
       </c>
       <c r="J118" t="n">
-        <v>17.02943916628372</v>
+        <v>13.006</v>
       </c>
     </row>
     <row r="119">
@@ -7121,10 +7109,10 @@
         <v>1.08</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2680973793443151</v>
+        <v>0.1207</v>
       </c>
       <c r="J119" t="n">
-        <v>5.361947586886302</v>
+        <v>2.414</v>
       </c>
     </row>
     <row r="120">
@@ -7161,10 +7149,10 @@
         <v>0.98</v>
       </c>
       <c r="I120" t="n">
-        <v>0.09828467039319697</v>
+        <v>-0.1148</v>
       </c>
       <c r="J120" t="n">
-        <v>1.965693407863939</v>
+        <v>-2.296</v>
       </c>
     </row>
     <row r="121">
@@ -7201,10 +7189,10 @@
         <v>0.72</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2340462754466197</v>
+        <v>-0.5162</v>
       </c>
       <c r="J121" t="n">
-        <v>-4.680925508932394</v>
+        <v>-10.324</v>
       </c>
     </row>
     <row r="122">
@@ -7241,10 +7229,10 @@
         <v>1.81</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7229350867605375</v>
+        <v>1.8082</v>
       </c>
       <c r="J122" t="n">
-        <v>16.62750699549236</v>
+        <v>41.5886</v>
       </c>
     </row>
     <row r="123">
@@ -7281,10 +7269,10 @@
         <v>1.24</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2493489877886731</v>
+        <v>0.655</v>
       </c>
       <c r="J123" t="n">
-        <v>5.735026719139481</v>
+        <v>15.065</v>
       </c>
     </row>
     <row r="124">
@@ -7321,10 +7309,10 @@
         <v>1.24</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2493489877886731</v>
+        <v>0.655</v>
       </c>
       <c r="J124" t="n">
-        <v>5.735026719139481</v>
+        <v>15.065</v>
       </c>
     </row>
     <row r="125">
@@ -7361,10 +7349,10 @@
         <v>0.85</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2931953489128579</v>
+        <v>-0.6035</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.743493024995731</v>
+        <v>-13.8805</v>
       </c>
     </row>
     <row r="126">
@@ -7401,10 +7389,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3484193458984483</v>
+        <v>-0.7729</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.013644955664311</v>
+        <v>-17.7767</v>
       </c>
     </row>
     <row r="127">
@@ -7441,10 +7429,10 @@
         <v>2.08</v>
       </c>
       <c r="I127" t="n">
-        <v>1.025124734550833</v>
+        <v>1.3376</v>
       </c>
       <c r="J127" t="n">
-        <v>23.57786889466917</v>
+        <v>30.7648</v>
       </c>
     </row>
     <row r="128">
@@ -7481,10 +7469,10 @@
         <v>1.1</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.08222048982092611</v>
+        <v>0.1985</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.891071265881301</v>
+        <v>4.5655</v>
       </c>
     </row>
     <row r="129">
@@ -7521,10 +7509,10 @@
         <v>0.92</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3340110283646811</v>
+        <v>-0.2135</v>
       </c>
       <c r="J129" t="n">
-        <v>-7.682253652387664</v>
+        <v>-4.9105</v>
       </c>
     </row>
     <row r="130">
@@ -7561,10 +7549,10 @@
         <v>0.89</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3624328250982637</v>
+        <v>-0.2636</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.335954977260064</v>
+        <v>-6.0628</v>
       </c>
     </row>
     <row r="131">
@@ -7601,10 +7589,10 @@
         <v>0.36</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7102775943764896</v>
+        <v>-0.9244</v>
       </c>
       <c r="J131" t="n">
-        <v>-16.33638467065926</v>
+        <v>-21.2612</v>
       </c>
     </row>
     <row r="132">
@@ -7641,10 +7629,10 @@
         <v>1.43</v>
       </c>
       <c r="I132" t="n">
-        <v>0.4979943202170059</v>
+        <v>1.1077</v>
       </c>
       <c r="J132" t="n">
-        <v>14.44183528629317</v>
+        <v>32.1233</v>
       </c>
     </row>
     <row r="133">
@@ -7681,10 +7669,10 @@
         <v>1.12</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1148456741365507</v>
+        <v>0.3296</v>
       </c>
       <c r="J133" t="n">
-        <v>3.330524549959971</v>
+        <v>9.558400000000001</v>
       </c>
     </row>
     <row r="134">
@@ -7721,10 +7709,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.06720467468950315</v>
+        <v>0.2374</v>
       </c>
       <c r="J134" t="n">
-        <v>1.948935565995592</v>
+        <v>6.8846</v>
       </c>
     </row>
     <row r="135">
@@ -7761,10 +7749,10 @@
         <v>1.07</v>
       </c>
       <c r="I135" t="n">
-        <v>0.03732474764271904</v>
+        <v>0.1748</v>
       </c>
       <c r="J135" t="n">
-        <v>1.082417681638852</v>
+        <v>5.0692</v>
       </c>
     </row>
     <row r="136">
@@ -7801,10 +7789,10 @@
         <v>1.01</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.05127784049670832</v>
+        <v>-0.0416</v>
       </c>
       <c r="J136" t="n">
-        <v>-1.487057374404541</v>
+        <v>-1.2064</v>
       </c>
     </row>
     <row r="137">
@@ -7841,10 +7829,10 @@
         <v>1.23</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2724100146900831</v>
+        <v>0.4254</v>
       </c>
       <c r="J137" t="n">
-        <v>7.899890426012409</v>
+        <v>12.3366</v>
       </c>
     </row>
     <row r="138">
@@ -7881,10 +7869,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.222126561055684</v>
+        <v>0.3829</v>
       </c>
       <c r="J138" t="n">
-        <v>6.441670270614837</v>
+        <v>11.1041</v>
       </c>
     </row>
     <row r="139">
@@ -7921,10 +7909,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.08486961248517605</v>
+        <v>0.1135</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.461218762070105</v>
+        <v>3.2915</v>
       </c>
     </row>
     <row r="140">
@@ -7961,10 +7949,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3457382162326094</v>
+        <v>-0.3096</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.02640827074567</v>
+        <v>-8.978400000000001</v>
       </c>
     </row>
     <row r="141">
@@ -8001,10 +7989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4791744677836863</v>
+        <v>-0.5336</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.8960595657269</v>
+        <v>-15.4744</v>
       </c>
     </row>
     <row r="142">
@@ -8041,10 +8029,10 @@
         <v>1.43</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3917717420226838</v>
+        <v>0.7175</v>
       </c>
       <c r="J142" t="n">
-        <v>7.835434840453677</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="143">
@@ -8081,10 +8069,10 @@
         <v>0.83</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.3795205482518881</v>
+        <v>-0.3086</v>
       </c>
       <c r="J143" t="n">
-        <v>-7.590410965037762</v>
+        <v>-6.172</v>
       </c>
     </row>
     <row r="144">
@@ -8121,10 +8109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.4007377819649303</v>
+        <v>-0.3403</v>
       </c>
       <c r="J144" t="n">
-        <v>-8.014755639298606</v>
+        <v>-6.806</v>
       </c>
     </row>
     <row r="145">
@@ -8161,10 +8149,10 @@
         <v>0.79</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4207467239468949</v>
+        <v>-0.3709</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.414934478937898</v>
+        <v>-7.418</v>
       </c>
     </row>
     <row r="146">
@@ -8201,10 +8189,10 @@
         <v>0.64</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5469366218851739</v>
+        <v>-0.5786</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.93873243770348</v>
+        <v>-11.572</v>
       </c>
     </row>
     <row r="147">
@@ -8241,10 +8229,10 @@
         <v>1.5</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4211525197871134</v>
+        <v>1.2124</v>
       </c>
       <c r="J147" t="n">
-        <v>8.423050395742267</v>
+        <v>24.248</v>
       </c>
     </row>
     <row r="148">
@@ -8281,10 +8269,10 @@
         <v>1.36</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3367221392875938</v>
+        <v>0.9179</v>
       </c>
       <c r="J148" t="n">
-        <v>6.734442785751876</v>
+        <v>18.358</v>
       </c>
     </row>
     <row r="149">
@@ -8321,10 +8309,10 @@
         <v>1.25</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2487319879813262</v>
+        <v>0.6554</v>
       </c>
       <c r="J149" t="n">
-        <v>4.974639759626525</v>
+        <v>13.108</v>
       </c>
     </row>
     <row r="150">
@@ -8361,10 +8349,10 @@
         <v>1.08</v>
       </c>
       <c r="I150" t="n">
-        <v>0.07700498070483426</v>
+        <v>0.1683</v>
       </c>
       <c r="J150" t="n">
-        <v>1.540099614096685</v>
+        <v>3.366</v>
       </c>
     </row>
     <row r="151">
@@ -8401,10 +8389,10 @@
         <v>0.91</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.1120397741720316</v>
+        <v>-0.4542</v>
       </c>
       <c r="J151" t="n">
-        <v>-2.240795483440632</v>
+        <v>-9.084</v>
       </c>
     </row>
     <row r="152">
@@ -8441,10 +8429,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.02962233954947172</v>
+        <v>0.4157</v>
       </c>
       <c r="J152" t="n">
-        <v>-0.5332021118904908</v>
+        <v>7.4826</v>
       </c>
     </row>
     <row r="153">
@@ -8481,10 +8469,10 @@
         <v>0.92</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2894640518474185</v>
+        <v>-0.119</v>
       </c>
       <c r="J153" t="n">
-        <v>-5.210352933253533</v>
+        <v>-2.142</v>
       </c>
     </row>
     <row r="154">
@@ -8521,10 +8509,10 @@
         <v>0.83</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4258665376757966</v>
+        <v>-0.2966</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.665597678164339</v>
+        <v>-5.3388</v>
       </c>
     </row>
     <row r="155">
@@ -8561,10 +8549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4485507022044321</v>
+        <v>-0.3296</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.073912639679778</v>
+        <v>-5.9328</v>
       </c>
     </row>
     <row r="156">
@@ -8601,10 +8589,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6193209687891561</v>
+        <v>-0.6113</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.14777743820481</v>
+        <v>-11.0034</v>
       </c>
     </row>
     <row r="157">
@@ -8641,10 +8629,10 @@
         <v>2.06</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6597410177351866</v>
+        <v>2.0572</v>
       </c>
       <c r="J157" t="n">
-        <v>11.87533831923336</v>
+        <v>37.0296</v>
       </c>
     </row>
     <row r="158">
@@ -8681,10 +8669,10 @@
         <v>1.86</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5873398998223391</v>
+        <v>1.8277</v>
       </c>
       <c r="J158" t="n">
-        <v>10.5721181968021</v>
+        <v>32.8986</v>
       </c>
     </row>
     <row r="159">
@@ -8721,10 +8709,10 @@
         <v>1.4</v>
       </c>
       <c r="I159" t="n">
-        <v>0.344400202613539</v>
+        <v>0.9472</v>
       </c>
       <c r="J159" t="n">
-        <v>6.199203647043702</v>
+        <v>17.0496</v>
       </c>
     </row>
     <row r="160">
@@ -8761,10 +8749,10 @@
         <v>0.74</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3373689477696746</v>
+        <v>-0.8922</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.072641059854142</v>
+        <v>-16.0596</v>
       </c>
     </row>
     <row r="161">
@@ -8801,10 +8789,10 @@
         <v>0.58</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4879176446332167</v>
+        <v>-1.222</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.782517603397901</v>
+        <v>-21.996</v>
       </c>
     </row>
     <row r="162">
@@ -8841,10 +8829,10 @@
         <v>1.32</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4357861058392587</v>
+        <v>0.5647</v>
       </c>
       <c r="J162" t="n">
-        <v>10.45886654014221</v>
+        <v>13.5528</v>
       </c>
     </row>
     <row r="163">
@@ -8881,10 +8869,10 @@
         <v>1.09</v>
       </c>
       <c r="I163" t="n">
-        <v>0.06756365699383975</v>
+        <v>0.2314</v>
       </c>
       <c r="J163" t="n">
-        <v>1.621527767852154</v>
+        <v>5.5536</v>
       </c>
     </row>
     <row r="164">
@@ -8921,10 +8909,10 @@
         <v>1.02</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.03899773166843198</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="J164" t="n">
-        <v>-0.9359455600423674</v>
+        <v>2.2512</v>
       </c>
     </row>
     <row r="165">
@@ -8961,10 +8949,10 @@
         <v>0.71</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4136690550039434</v>
+        <v>-0.4963</v>
       </c>
       <c r="J165" t="n">
-        <v>-9.928057320094641</v>
+        <v>-11.9112</v>
       </c>
     </row>
     <row r="166">
@@ -9001,10 +8989,10 @@
         <v>0.59</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5024955825656082</v>
+        <v>-0.6498</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.0598939815746</v>
+        <v>-15.5952</v>
       </c>
     </row>
     <row r="167">
@@ -9041,10 +9029,10 @@
         <v>1.8</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6225187748028101</v>
+        <v>1.816</v>
       </c>
       <c r="J167" t="n">
-        <v>14.94045059526744</v>
+        <v>43.584</v>
       </c>
     </row>
     <row r="168">
@@ -9081,10 +9069,10 @@
         <v>1.12</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1121259238686944</v>
+        <v>0.3384</v>
       </c>
       <c r="J168" t="n">
-        <v>2.691022172848665</v>
+        <v>8.121600000000001</v>
       </c>
     </row>
     <row r="169">
@@ -9121,10 +9109,10 @@
         <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.01231633440369229</v>
+        <v>0.0058</v>
       </c>
       <c r="J169" t="n">
-        <v>-0.2955920256886149</v>
+        <v>0.1392</v>
       </c>
     </row>
     <row r="170">
@@ -9161,10 +9149,10 @@
         <v>0.93</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1566432017989104</v>
+        <v>-0.3675</v>
       </c>
       <c r="J170" t="n">
-        <v>-3.759436843173849</v>
+        <v>-8.82</v>
       </c>
     </row>
     <row r="171">
@@ -9201,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3096537586569955</v>
+        <v>-0.7126</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.431690207767892</v>
+        <v>-17.1024</v>
       </c>
     </row>
     <row r="172">
@@ -9241,10 +9229,10 @@
         <v>1.15</v>
       </c>
       <c r="I172" t="n">
-        <v>0.09340116301311679</v>
+        <v>0.3745</v>
       </c>
       <c r="J172" t="n">
-        <v>1.961424423275453</v>
+        <v>7.8645</v>
       </c>
     </row>
     <row r="173">
@@ -9281,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.06835627643735021</v>
+        <v>0.1184</v>
       </c>
       <c r="J173" t="n">
-        <v>-1.435481805184354</v>
+        <v>2.4864</v>
       </c>
     </row>
     <row r="174">
@@ -9321,10 +9309,10 @@
         <v>0.82</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2980258613611986</v>
+        <v>-0.2869</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.25854308858517</v>
+        <v>-6.0249</v>
       </c>
     </row>
     <row r="175">
@@ -9361,10 +9349,10 @@
         <v>0.58</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5340187362978398</v>
+        <v>-0.6398</v>
       </c>
       <c r="J175" t="n">
-        <v>-11.21439346225464</v>
+        <v>-13.4358</v>
       </c>
     </row>
     <row r="176">
@@ -9401,10 +9389,10 @@
         <v>0.57</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5413534182848544</v>
+        <v>-0.6525</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.36842178398194</v>
+        <v>-13.7025</v>
       </c>
     </row>
     <row r="177">
@@ -9441,10 +9429,10 @@
         <v>1.64</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5917562525553772</v>
+        <v>1.4831</v>
       </c>
       <c r="J177" t="n">
-        <v>12.42688130366292</v>
+        <v>31.1451</v>
       </c>
     </row>
     <row r="178">
@@ -9481,10 +9469,10 @@
         <v>1.47</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4895860875427421</v>
+        <v>1.1516</v>
       </c>
       <c r="J178" t="n">
-        <v>10.28130783839758</v>
+        <v>24.1836</v>
       </c>
     </row>
     <row r="179">
@@ -9521,10 +9509,10 @@
         <v>1.05</v>
       </c>
       <c r="I179" t="n">
-        <v>0.07471412684899696</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>1.568996663828936</v>
+        <v>1.5813</v>
       </c>
     </row>
     <row r="180">
@@ -9561,10 +9549,10 @@
         <v>0.98</v>
       </c>
       <c r="I180" t="n">
-        <v>0.01330053204127693</v>
+        <v>-0.2305</v>
       </c>
       <c r="J180" t="n">
-        <v>0.2793111728668155</v>
+        <v>-4.8405</v>
       </c>
     </row>
     <row r="181">
@@ -9601,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.005084738646350216</v>
+        <v>-0.3022</v>
       </c>
       <c r="J181" t="n">
-        <v>-0.1067795115733545</v>
+        <v>-6.3462</v>
       </c>
     </row>
     <row r="182">
@@ -9641,10 +9629,10 @@
         <v>1.19</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.02974875917264375</v>
+        <v>0.4629</v>
       </c>
       <c r="J182" t="n">
-        <v>-0.5057289059349437</v>
+        <v>7.8693</v>
       </c>
     </row>
     <row r="183">
@@ -9681,10 +9669,10 @@
         <v>0.74</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.4592421216418061</v>
+        <v>-0.3871</v>
       </c>
       <c r="J183" t="n">
-        <v>-7.807116067910703</v>
+        <v>-6.5807</v>
       </c>
     </row>
     <row r="184">
@@ -9721,10 +9709,10 @@
         <v>0.73</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.4724716351276018</v>
+        <v>-0.4043</v>
       </c>
       <c r="J184" t="n">
-        <v>-8.03201779716923</v>
+        <v>-6.8731</v>
       </c>
     </row>
     <row r="185">
@@ -9761,10 +9749,10 @@
         <v>0.66</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.5464587341720648</v>
+        <v>-0.5122</v>
       </c>
       <c r="J185" t="n">
-        <v>-9.289798480925102</v>
+        <v>-8.7074</v>
       </c>
     </row>
     <row r="186">
@@ -9801,10 +9789,10 @@
         <v>0.47</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6925463765719699</v>
+        <v>-0.7633</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.77328840172349</v>
+        <v>-12.9761</v>
       </c>
     </row>
     <row r="187">
@@ -9841,10 +9829,10 @@
         <v>1.64</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7969184415827884</v>
+        <v>1.4038</v>
       </c>
       <c r="J187" t="n">
-        <v>13.5476135069074</v>
+        <v>23.8646</v>
       </c>
     </row>
     <row r="188">
@@ -9881,10 +9869,10 @@
         <v>1.53</v>
       </c>
       <c r="I188" t="n">
-        <v>0.6960596615145107</v>
+        <v>1.1889</v>
       </c>
       <c r="J188" t="n">
-        <v>11.83301424574668</v>
+        <v>20.2113</v>
       </c>
     </row>
     <row r="189">
@@ -9921,10 +9909,10 @@
         <v>1.49</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6535185705573854</v>
+        <v>1.1063</v>
       </c>
       <c r="J189" t="n">
-        <v>11.10981569947555</v>
+        <v>18.8071</v>
       </c>
     </row>
     <row r="190">
@@ -9961,10 +9949,10 @@
         <v>1.47</v>
       </c>
       <c r="I190" t="n">
-        <v>0.6304535019693432</v>
+        <v>1.0638</v>
       </c>
       <c r="J190" t="n">
-        <v>10.71770953347884</v>
+        <v>18.0846</v>
       </c>
     </row>
     <row r="191">
@@ -10001,10 +9989,10 @@
         <v>0.84</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.07131291937131584</v>
+        <v>-0.6751</v>
       </c>
       <c r="J191" t="n">
-        <v>-1.212319629312369</v>
+        <v>-11.4767</v>
       </c>
     </row>
     <row r="192">
@@ -10041,10 +10029,10 @@
         <v>1.35</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3968359404615782</v>
+        <v>0.5481</v>
       </c>
       <c r="J192" t="n">
-        <v>9.524062571077877</v>
+        <v>13.1544</v>
       </c>
     </row>
     <row r="193">
@@ -10081,10 +10069,10 @@
         <v>1.16</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2048977802269404</v>
+        <v>0.2824</v>
       </c>
       <c r="J193" t="n">
-        <v>4.91754672544657</v>
+        <v>6.7776</v>
       </c>
     </row>
     <row r="194">
@@ -10121,10 +10109,10 @@
         <v>1.14</v>
       </c>
       <c r="I194" t="n">
-        <v>0.1770783150754017</v>
+        <v>0.2491</v>
       </c>
       <c r="J194" t="n">
-        <v>4.249879561809641</v>
+        <v>5.9784</v>
       </c>
     </row>
     <row r="195">
@@ -10161,10 +10149,10 @@
         <v>1.12</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1441602419234248</v>
+        <v>0.2128</v>
       </c>
       <c r="J195" t="n">
-        <v>3.459845806162195</v>
+        <v>5.1072</v>
       </c>
     </row>
     <row r="196">
@@ -10201,10 +10189,10 @@
         <v>0.79</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.298314852235092</v>
+        <v>-0.4197</v>
       </c>
       <c r="J196" t="n">
-        <v>-7.159556453642207</v>
+        <v>-10.0728</v>
       </c>
     </row>
     <row r="197">
@@ -10241,10 +10229,10 @@
         <v>1.15</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1640890971842323</v>
+        <v>0.3141</v>
       </c>
       <c r="J197" t="n">
-        <v>3.938138332421576</v>
+        <v>7.5384</v>
       </c>
     </row>
     <row r="198">
@@ -10281,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.07802010533775905</v>
+        <v>0.0488</v>
       </c>
       <c r="J198" t="n">
-        <v>-1.872482528106217</v>
+        <v>1.1712</v>
       </c>
     </row>
     <row r="199">
@@ -10321,10 +10309,10 @@
         <v>0.99</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1137913264605251</v>
+        <v>-0.0262</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.730991835052602</v>
+        <v>-0.6288</v>
       </c>
     </row>
     <row r="200">
@@ -10361,10 +10349,10 @@
         <v>0.91</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2396533741961132</v>
+        <v>-0.2057</v>
       </c>
       <c r="J200" t="n">
-        <v>-5.751680980706717</v>
+        <v>-4.9368</v>
       </c>
     </row>
     <row r="201">
@@ -10401,10 +10389,10 @@
         <v>0.87</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2840014240058678</v>
+        <v>-0.2734</v>
       </c>
       <c r="J201" t="n">
-        <v>-6.816034176140827</v>
+        <v>-6.5616</v>
       </c>
     </row>
     <row r="202">
@@ -10441,10 +10429,10 @@
         <v>1.27</v>
       </c>
       <c r="I202" t="n">
-        <v>0.2564745705562534</v>
+        <v>0.4686</v>
       </c>
       <c r="J202" t="n">
-        <v>6.155389693350081</v>
+        <v>11.2464</v>
       </c>
     </row>
     <row r="203">
@@ -10481,10 +10469,10 @@
         <v>1.21</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1975641311044681</v>
+        <v>0.3855</v>
       </c>
       <c r="J203" t="n">
-        <v>4.741539146507234</v>
+        <v>9.252000000000001</v>
       </c>
     </row>
     <row r="204">
@@ -10521,10 +10509,10 @@
         <v>0.97</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1867985382819319</v>
+        <v>-0.1071</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.483164918766366</v>
+        <v>-2.5704</v>
       </c>
     </row>
     <row r="205">
@@ -10561,10 +10549,10 @@
         <v>0.88</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2902097810743158</v>
+        <v>-0.2713</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.965034745783578</v>
+        <v>-6.5112</v>
       </c>
     </row>
     <row r="206">
@@ -10601,10 +10589,10 @@
         <v>0.85</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3197917713047686</v>
+        <v>-0.3181</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.675002511314446</v>
+        <v>-7.6344</v>
       </c>
     </row>
     <row r="207">
@@ -10641,10 +10629,10 @@
         <v>1.26</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3860398532799993</v>
+        <v>0.771</v>
       </c>
       <c r="J207" t="n">
-        <v>9.264956478719983</v>
+        <v>18.504</v>
       </c>
     </row>
     <row r="208">
@@ -10681,10 +10669,10 @@
         <v>1.11</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1766761465985442</v>
+        <v>0.375</v>
       </c>
       <c r="J208" t="n">
-        <v>4.24022751836506</v>
+        <v>9</v>
       </c>
     </row>
     <row r="209">
@@ -10721,10 +10709,10 @@
         <v>1.1</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1577971577443958</v>
+        <v>0.3436</v>
       </c>
       <c r="J209" t="n">
-        <v>3.787131785865499</v>
+        <v>8.2464</v>
       </c>
     </row>
     <row r="210">
@@ -10761,10 +10749,10 @@
         <v>1.08</v>
       </c>
       <c r="I210" t="n">
-        <v>0.1142032906528553</v>
+        <v>0.2758</v>
       </c>
       <c r="J210" t="n">
-        <v>2.740878975668528</v>
+        <v>6.6192</v>
       </c>
     </row>
     <row r="211">
@@ -10801,10 +10789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2816968565917323</v>
+        <v>-0.6691</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.760724558201575</v>
+        <v>-16.0584</v>
       </c>
     </row>
     <row r="212">
@@ -10841,10 +10829,10 @@
         <v>1.36</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3921118802230496</v>
+        <v>0.6313</v>
       </c>
       <c r="J212" t="n">
-        <v>9.01857324513014</v>
+        <v>14.5199</v>
       </c>
     </row>
     <row r="213">
@@ -10881,10 +10869,10 @@
         <v>0.97</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.06766073591110412</v>
+        <v>-0.0316</v>
       </c>
       <c r="J213" t="n">
-        <v>-1.556196925955395</v>
+        <v>-0.7268</v>
       </c>
     </row>
     <row r="214">
@@ -10921,10 +10909,10 @@
         <v>0.88</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2148132532176023</v>
+        <v>-0.2232</v>
       </c>
       <c r="J214" t="n">
-        <v>-4.940704824004852</v>
+        <v>-5.1336</v>
       </c>
     </row>
     <row r="215">
@@ -10961,10 +10949,10 @@
         <v>0.75</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.361571667995119</v>
+        <v>-0.4302</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.316148363887738</v>
+        <v>-9.894600000000001</v>
       </c>
     </row>
     <row r="216">
@@ -11001,10 +10989,10 @@
         <v>0.55</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5202604614896361</v>
+        <v>-0.6915</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.96599061426163</v>
+        <v>-15.9045</v>
       </c>
     </row>
     <row r="217">
@@ -11041,10 +11029,10 @@
         <v>1.52</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7284852092612253</v>
+        <v>1.3172</v>
       </c>
       <c r="J217" t="n">
-        <v>16.75515981300818</v>
+        <v>30.2956</v>
       </c>
     </row>
     <row r="218">
@@ -11081,10 +11069,10 @@
         <v>1.17</v>
       </c>
       <c r="I218" t="n">
-        <v>0.365539719100992</v>
+        <v>0.5327</v>
       </c>
       <c r="J218" t="n">
-        <v>8.407413539322818</v>
+        <v>12.2521</v>
       </c>
     </row>
     <row r="219">
@@ -11121,10 +11109,10 @@
         <v>1.17</v>
       </c>
       <c r="I219" t="n">
-        <v>0.365539719100992</v>
+        <v>0.5327</v>
       </c>
       <c r="J219" t="n">
-        <v>8.407413539322818</v>
+        <v>12.2521</v>
       </c>
     </row>
     <row r="220">
@@ -11161,10 +11149,10 @@
         <v>0.89</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1180960774619228</v>
+        <v>-0.4674</v>
       </c>
       <c r="J220" t="n">
-        <v>-2.716209781624224</v>
+        <v>-10.7502</v>
       </c>
     </row>
     <row r="221">
@@ -11201,10 +11189,10 @@
         <v>0.71</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3027557981553676</v>
+        <v>-0.909</v>
       </c>
       <c r="J221" t="n">
-        <v>-6.963383357573456</v>
+        <v>-20.907</v>
       </c>
     </row>
     <row r="222">
@@ -11241,10 +11229,10 @@
         <v>1.15</v>
       </c>
       <c r="I222" t="n">
-        <v>0.1835232762264584</v>
+        <v>0.3382</v>
       </c>
       <c r="J222" t="n">
-        <v>4.404558629435002</v>
+        <v>8.1168</v>
       </c>
     </row>
     <row r="223">
@@ -11281,10 +11269,10 @@
         <v>1</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.03631533552510698</v>
+        <v>0.0444</v>
       </c>
       <c r="J223" t="n">
-        <v>-0.8715680526025675</v>
+        <v>1.0656</v>
       </c>
     </row>
     <row r="224">
@@ -11321,10 +11309,10 @@
         <v>0.89</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2094851494936238</v>
+        <v>-0.2142</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.027643587846971</v>
+        <v>-5.1408</v>
       </c>
     </row>
     <row r="225">
@@ -11361,10 +11349,10 @@
         <v>0.82</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.292779600331905</v>
+        <v>-0.3316</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.026710407965719</v>
+        <v>-7.9584</v>
       </c>
     </row>
     <row r="226">
@@ -11401,10 +11389,10 @@
         <v>0.74</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3694662382981603</v>
+        <v>-0.4492</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.867189719155848</v>
+        <v>-10.7808</v>
       </c>
     </row>
     <row r="227">
@@ -11441,10 +11429,10 @@
         <v>1.67</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7984144523836713</v>
+        <v>1.5898</v>
       </c>
       <c r="J227" t="n">
-        <v>19.16194685720811</v>
+        <v>38.1552</v>
       </c>
     </row>
     <row r="228">
@@ -11481,10 +11469,10 @@
         <v>1.26</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4276733396243419</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="J228" t="n">
-        <v>10.26416015098421</v>
+        <v>17.868</v>
       </c>
     </row>
     <row r="229">
@@ -11521,10 +11509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.08717667612018934</v>
+        <v>-0.3303</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.092240226884544</v>
+        <v>-7.9272</v>
       </c>
     </row>
     <row r="230">
@@ -11561,10 +11549,10 @@
         <v>0.86</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2021415682002293</v>
+        <v>-0.5576</v>
       </c>
       <c r="J230" t="n">
-        <v>-4.851397636805504</v>
+        <v>-13.3824</v>
       </c>
     </row>
     <row r="231">
@@ -11601,10 +11589,10 @@
         <v>0.86</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2021415682002293</v>
+        <v>-0.5576</v>
       </c>
       <c r="J231" t="n">
-        <v>-4.851397636805504</v>
+        <v>-13.3824</v>
       </c>
     </row>
     <row r="232">
@@ -11641,10 +11629,10 @@
         <v>1.85</v>
       </c>
       <c r="I232" t="n">
-        <v>0.5628591223466048</v>
+        <v>1.7337</v>
       </c>
       <c r="J232" t="n">
-        <v>9.005745957545678</v>
+        <v>27.7392</v>
       </c>
     </row>
     <row r="233">
@@ -11681,10 +11669,10 @@
         <v>1.54</v>
       </c>
       <c r="I233" t="n">
-        <v>0.37438628962434</v>
+        <v>1.1448</v>
       </c>
       <c r="J233" t="n">
-        <v>5.99018063398944</v>
+        <v>18.3168</v>
       </c>
     </row>
     <row r="234">
@@ -11721,10 +11709,10 @@
         <v>1.49</v>
       </c>
       <c r="I234" t="n">
-        <v>0.3119082770767664</v>
+        <v>1.0183</v>
       </c>
       <c r="J234" t="n">
-        <v>4.990532433228263</v>
+        <v>16.2928</v>
       </c>
     </row>
     <row r="235">
@@ -11761,10 +11749,10 @@
         <v>1.41</v>
       </c>
       <c r="I235" t="n">
-        <v>0.2473731101175506</v>
+        <v>0.8439</v>
       </c>
       <c r="J235" t="n">
-        <v>3.95796976188081</v>
+        <v>13.5024</v>
       </c>
     </row>
     <row r="236">
@@ -11801,10 +11789,10 @@
         <v>1.28</v>
       </c>
       <c r="I236" t="n">
-        <v>0.1635853944558564</v>
+        <v>0.5636</v>
       </c>
       <c r="J236" t="n">
-        <v>2.617366311293702</v>
+        <v>9.0176</v>
       </c>
     </row>
     <row r="237">
@@ -11841,10 +11829,10 @@
         <v>1.65</v>
       </c>
       <c r="I237" t="n">
-        <v>0.424226073308595</v>
+        <v>0.9939</v>
       </c>
       <c r="J237" t="n">
-        <v>6.787617172937519</v>
+        <v>15.9024</v>
       </c>
     </row>
     <row r="238">
@@ -11881,10 +11869,10 @@
         <v>0.99</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2846054878048134</v>
+        <v>0.0451</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.553687804877014</v>
+        <v>0.7216</v>
       </c>
     </row>
     <row r="239">
@@ -11921,10 +11909,10 @@
         <v>0.83</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4700989948885688</v>
+        <v>-0.275</v>
       </c>
       <c r="J239" t="n">
-        <v>-7.521583918217101</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="240">
@@ -11961,10 +11949,10 @@
         <v>0.45</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.7803445172681664</v>
+        <v>-0.8007</v>
       </c>
       <c r="J240" t="n">
-        <v>-12.48551227629066</v>
+        <v>-12.8112</v>
       </c>
     </row>
     <row r="241">
@@ -12001,10 +11989,10 @@
         <v>0.26</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.8807613797728828</v>
+        <v>-1.0152</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.09218207636613</v>
+        <v>-16.2432</v>
       </c>
     </row>
     <row r="242">
@@ -12041,10 +12029,10 @@
         <v>1.31</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2475535029238953</v>
+        <v>0.8356</v>
       </c>
       <c r="J242" t="n">
-        <v>7.426605087716858</v>
+        <v>25.068</v>
       </c>
     </row>
     <row r="243">
@@ -12081,10 +12069,10 @@
         <v>1.31</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2475535029238953</v>
+        <v>0.8356</v>
       </c>
       <c r="J243" t="n">
-        <v>7.426605087716858</v>
+        <v>25.068</v>
       </c>
     </row>
     <row r="244">
@@ -12121,10 +12109,10 @@
         <v>1.25</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2014182338509337</v>
+        <v>0.6929</v>
       </c>
       <c r="J244" t="n">
-        <v>6.042547015528011</v>
+        <v>20.787</v>
       </c>
     </row>
     <row r="245">
@@ -12161,10 +12149,10 @@
         <v>1.03</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.06244600770797486</v>
+        <v>0.0301</v>
       </c>
       <c r="J245" t="n">
-        <v>-1.873380231239246</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="246">
@@ -12201,10 +12189,10 @@
         <v>0.92</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2694937245461266</v>
+        <v>-0.408</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.084811736383799</v>
+        <v>-12.24</v>
       </c>
     </row>
     <row r="247">
@@ -12241,10 +12229,10 @@
         <v>1.32</v>
       </c>
       <c r="I247" t="n">
-        <v>0.426178650307341</v>
+        <v>0.5488</v>
       </c>
       <c r="J247" t="n">
-        <v>12.78535950922023</v>
+        <v>16.464</v>
       </c>
     </row>
     <row r="248">
@@ -12281,10 +12269,10 @@
         <v>1.15</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1207117162736132</v>
+        <v>0.3119</v>
       </c>
       <c r="J248" t="n">
-        <v>3.621351488208396</v>
+        <v>9.356999999999999</v>
       </c>
     </row>
     <row r="249">
@@ -12321,10 +12309,10 @@
         <v>0.9</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.275153133156578</v>
+        <v>-0.2253</v>
       </c>
       <c r="J249" t="n">
-        <v>-8.254593994697341</v>
+        <v>-6.759</v>
       </c>
     </row>
     <row r="250">
@@ -12361,10 +12349,10 @@
         <v>0.83</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3450921887614708</v>
+        <v>-0.3375</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.35276566284412</v>
+        <v>-10.125</v>
       </c>
     </row>
     <row r="251">
@@ -12401,10 +12389,10 @@
         <v>0.76</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4057789051922788</v>
+        <v>-0.4382</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.17336715576836</v>
+        <v>-13.146</v>
       </c>
     </row>
     <row r="252">
@@ -12441,10 +12429,10 @@
         <v>1.39</v>
       </c>
       <c r="I252" t="n">
-        <v>0.4955457298622672</v>
+        <v>1.0641</v>
       </c>
       <c r="J252" t="n">
-        <v>10.40646032710761</v>
+        <v>22.3461</v>
       </c>
     </row>
     <row r="253">
@@ -12481,10 +12469,10 @@
         <v>1.21</v>
       </c>
       <c r="I253" t="n">
-        <v>0.3357278442089101</v>
+        <v>0.6516</v>
       </c>
       <c r="J253" t="n">
-        <v>7.050284728387112</v>
+        <v>13.6836</v>
       </c>
     </row>
     <row r="254">
@@ -12521,10 +12509,10 @@
         <v>1.18</v>
       </c>
       <c r="I254" t="n">
-        <v>0.3029758607717963</v>
+        <v>0.5747</v>
       </c>
       <c r="J254" t="n">
-        <v>6.362493076207722</v>
+        <v>12.0687</v>
       </c>
     </row>
     <row r="255">
@@ -12561,10 +12549,10 @@
         <v>0.89</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1417329994270769</v>
+        <v>-0.4578</v>
       </c>
       <c r="J255" t="n">
-        <v>-2.976392987968615</v>
+        <v>-9.613799999999999</v>
       </c>
     </row>
     <row r="256">
@@ -12601,10 +12589,10 @@
         <v>0.67</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3294672530809196</v>
+        <v>-0.9909</v>
       </c>
       <c r="J256" t="n">
-        <v>-6.918812314699312</v>
+        <v>-20.8089</v>
       </c>
     </row>
     <row r="257">
@@ -12641,10 +12629,10 @@
         <v>1.33</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3470509205082518</v>
+        <v>0.5483</v>
       </c>
       <c r="J257" t="n">
-        <v>7.288069330673287</v>
+        <v>11.5143</v>
       </c>
     </row>
     <row r="258">
@@ -12681,10 +12669,10 @@
         <v>1.05</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.09218975557763859</v>
+        <v>0.1196</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.93598486713041</v>
+        <v>2.5116</v>
       </c>
     </row>
     <row r="259">
@@ -12721,10 +12709,10 @@
         <v>1.03</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1411258216321322</v>
+        <v>0.0687</v>
       </c>
       <c r="J259" t="n">
-        <v>-2.963642254274776</v>
+        <v>1.4427</v>
       </c>
     </row>
     <row r="260">
@@ -12761,10 +12749,10 @@
         <v>0.95</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2673354760323773</v>
+        <v>-0.1472</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.614044996679923</v>
+        <v>-3.0912</v>
       </c>
     </row>
     <row r="261">
@@ -12801,10 +12789,10 @@
         <v>0.8</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4219117526748991</v>
+        <v>-0.3907</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.860146806172882</v>
+        <v>-8.204700000000001</v>
       </c>
     </row>
     <row r="262">
@@ -12841,10 +12829,10 @@
         <v>1.53</v>
       </c>
       <c r="I262" t="n">
-        <v>0.5573465967656773</v>
+        <v>1.2242</v>
       </c>
       <c r="J262" t="n">
-        <v>10.58958533854787</v>
+        <v>23.2598</v>
       </c>
     </row>
     <row r="263">
@@ -12881,10 +12869,10 @@
         <v>1.52</v>
       </c>
       <c r="I263" t="n">
-        <v>0.5495731180378376</v>
+        <v>1.2042</v>
       </c>
       <c r="J263" t="n">
-        <v>10.44188924271891</v>
+        <v>22.8798</v>
       </c>
     </row>
     <row r="264">
@@ -12921,10 +12909,10 @@
         <v>1.32</v>
       </c>
       <c r="I264" t="n">
-        <v>0.3370835164431916</v>
+        <v>0.7531</v>
       </c>
       <c r="J264" t="n">
-        <v>6.404586812420639</v>
+        <v>14.3089</v>
       </c>
     </row>
     <row r="265">
@@ -12961,10 +12949,10 @@
         <v>1.32</v>
       </c>
       <c r="I265" t="n">
-        <v>0.3370835164431916</v>
+        <v>0.7531</v>
       </c>
       <c r="J265" t="n">
-        <v>6.404586812420639</v>
+        <v>14.3089</v>
       </c>
     </row>
     <row r="266">
@@ -13001,10 +12989,10 @@
         <v>0.91</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.090349499579197</v>
+        <v>-0.4802</v>
       </c>
       <c r="J266" t="n">
-        <v>-1.716640492004743</v>
+        <v>-9.123799999999999</v>
       </c>
     </row>
     <row r="267">
@@ -13041,10 +13029,10 @@
         <v>1.17</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.0280941644919467</v>
+        <v>0.3834</v>
       </c>
       <c r="J267" t="n">
-        <v>-0.5337891253469872</v>
+        <v>7.2846</v>
       </c>
     </row>
     <row r="268">
@@ -13081,10 +13069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.2507797495574744</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="J268" t="n">
-        <v>-4.764815241592014</v>
+        <v>-1.596</v>
       </c>
     </row>
     <row r="269">
@@ -13121,10 +13109,10 @@
         <v>0.84</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3992057619363737</v>
+        <v>-0.2834</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.584909476791101</v>
+        <v>-5.3846</v>
       </c>
     </row>
     <row r="270">
@@ -13161,10 +13149,10 @@
         <v>0.77</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4727218274872609</v>
+        <v>-0.3944</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.981714722257957</v>
+        <v>-7.4936</v>
       </c>
     </row>
     <row r="271">
@@ -13201,10 +13189,10 @@
         <v>0.68</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5495731180378376</v>
+        <v>-0.5214</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.44188924271891</v>
+        <v>-9.906599999999999</v>
       </c>
     </row>
     <row r="272">
@@ -13241,10 +13229,10 @@
         <v>2.16</v>
       </c>
       <c r="I272" t="n">
-        <v>1.108200023511818</v>
+        <v>2.0593</v>
       </c>
       <c r="J272" t="n">
-        <v>18.8394003997009</v>
+        <v>35.0081</v>
       </c>
     </row>
     <row r="273">
@@ -13281,10 +13269,10 @@
         <v>1.58</v>
       </c>
       <c r="I273" t="n">
-        <v>0.7065807519472461</v>
+        <v>1.2699</v>
       </c>
       <c r="J273" t="n">
-        <v>12.01187278310318</v>
+        <v>21.5883</v>
       </c>
     </row>
     <row r="274">
@@ -13321,10 +13309,10 @@
         <v>1.27</v>
       </c>
       <c r="I274" t="n">
-        <v>0.29444798077343</v>
+        <v>0.5678</v>
       </c>
       <c r="J274" t="n">
-        <v>5.005615673148311</v>
+        <v>9.6526</v>
       </c>
     </row>
     <row r="275">
@@ -13361,10 +13349,10 @@
         <v>1.14</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1663119326466588</v>
+        <v>0.2586</v>
       </c>
       <c r="J275" t="n">
-        <v>2.8273028549932</v>
+        <v>4.3962</v>
       </c>
     </row>
     <row r="276">
@@ -13401,10 +13389,10 @@
         <v>1.02</v>
       </c>
       <c r="I276" t="n">
-        <v>0.053652326747738</v>
+        <v>-0.0915</v>
       </c>
       <c r="J276" t="n">
-        <v>0.912089554711546</v>
+        <v>-1.5555</v>
       </c>
     </row>
     <row r="277">
@@ -13441,10 +13429,10 @@
         <v>1.16</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.09188620791906825</v>
+        <v>0.4021</v>
       </c>
       <c r="J277" t="n">
-        <v>-1.56206553462416</v>
+        <v>6.8357</v>
       </c>
     </row>
     <row r="278">
@@ -13481,10 +13469,10 @@
         <v>1.01</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2226955189510643</v>
+        <v>0.131</v>
       </c>
       <c r="J278" t="n">
-        <v>-3.785823822168094</v>
+        <v>2.227</v>
       </c>
     </row>
     <row r="279">
@@ -13521,10 +13509,10 @@
         <v>0.71</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.587390797740609</v>
+        <v>-0.4535</v>
       </c>
       <c r="J279" t="n">
-        <v>-9.985643561590352</v>
+        <v>-7.7095</v>
       </c>
     </row>
     <row r="280">
@@ -13561,10 +13549,10 @@
         <v>0.68</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.6176746443649214</v>
+        <v>-0.4971</v>
       </c>
       <c r="J280" t="n">
-        <v>-10.50046895420366</v>
+        <v>-8.450699999999999</v>
       </c>
     </row>
     <row r="281">
@@ -13601,10 +13589,10 @@
         <v>0.42</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.820120774526804</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="J281" t="n">
-        <v>-13.94205316695567</v>
+        <v>-14.1117</v>
       </c>
     </row>
     <row r="282">
@@ -13641,10 +13629,10 @@
         <v>1.62</v>
       </c>
       <c r="I282" t="n">
-        <v>0.7215404441603309</v>
+        <v>1.483</v>
       </c>
       <c r="J282" t="n">
-        <v>20.9246728806496</v>
+        <v>43.007</v>
       </c>
     </row>
     <row r="283">
@@ -13681,10 +13669,10 @@
         <v>1.59</v>
       </c>
       <c r="I283" t="n">
-        <v>0.6997748713000039</v>
+        <v>1.4261</v>
       </c>
       <c r="J283" t="n">
-        <v>20.29347126770011</v>
+        <v>41.3569</v>
       </c>
     </row>
     <row r="284">
@@ -13721,10 +13709,10 @@
         <v>0.85</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2197728410908561</v>
+        <v>-0.5918</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.373412391634827</v>
+        <v>-17.1622</v>
       </c>
     </row>
     <row r="285">
@@ -13761,10 +13749,10 @@
         <v>0.84</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2295931502945806</v>
+        <v>-0.6172</v>
       </c>
       <c r="J285" t="n">
-        <v>-6.658201358542837</v>
+        <v>-17.8988</v>
       </c>
     </row>
     <row r="286">
@@ -13801,10 +13789,10 @@
         <v>0.82</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.248565484336108</v>
+        <v>-0.6669</v>
       </c>
       <c r="J286" t="n">
-        <v>-7.208399045747131</v>
+        <v>-19.3401</v>
       </c>
     </row>
     <row r="287">
@@ -13841,10 +13829,10 @@
         <v>1.13</v>
       </c>
       <c r="I287" t="n">
-        <v>0.06911485728690712</v>
+        <v>0.2975</v>
       </c>
       <c r="J287" t="n">
-        <v>2.004330861320307</v>
+        <v>8.6275</v>
       </c>
     </row>
     <row r="288">
@@ -13881,10 +13869,10 @@
         <v>1.12</v>
       </c>
       <c r="I288" t="n">
-        <v>0.05619526979213488</v>
+        <v>0.2815</v>
       </c>
       <c r="J288" t="n">
-        <v>1.629662823971912</v>
+        <v>8.163500000000001</v>
       </c>
     </row>
     <row r="289">
@@ -13921,10 +13909,10 @@
         <v>0.95</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1815714915728373</v>
+        <v>-0.1005</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.265573255612281</v>
+        <v>-2.9145</v>
       </c>
     </row>
     <row r="290">
@@ -13961,10 +13949,10 @@
         <v>0.86</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3265837443447848</v>
+        <v>-0.2767</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.470928585998758</v>
+        <v>-8.0243</v>
       </c>
     </row>
     <row r="291">
@@ -14001,10 +13989,10 @@
         <v>0.67</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5129188079586159</v>
+        <v>-0.5491</v>
       </c>
       <c r="J291" t="n">
-        <v>-14.87464543079986</v>
+        <v>-15.9239</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6976/event_6976_evp_summary.xlsx
+++ b/database/event/6976/event_6976_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>7.672</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3.2772</v>
       </c>
       <c r="D2" t="n">
         <v>2.678</v>
@@ -545,7 +545,7 @@
         <v>4.6741</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1.9966</v>
       </c>
       <c r="D3" t="n">
         <v>1.4669</v>
@@ -591,7 +591,7 @@
         <v>4.6313</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1.9784</v>
       </c>
       <c r="D4" t="n">
         <v>1.4496</v>
@@ -637,7 +637,7 @@
         <v>3.588</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1.5327</v>
       </c>
       <c r="D5" t="n">
         <v>1.0281</v>
@@ -683,7 +683,7 @@
         <v>3.4116</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1.4573</v>
       </c>
       <c r="D6" t="n">
         <v>0.9568</v>
@@ -729,7 +729,7 @@
         <v>3.1774</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.3573</v>
       </c>
       <c r="D7" t="n">
         <v>0.8622</v>
@@ -775,7 +775,7 @@
         <v>2.8854</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1.2326</v>
       </c>
       <c r="D8" t="n">
         <v>0.7443</v>
@@ -821,7 +821,7 @@
         <v>2.8566</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1.2203</v>
       </c>
       <c r="D9" t="n">
         <v>0.7326</v>
@@ -867,7 +867,7 @@
         <v>2.4301</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1.0381</v>
       </c>
       <c r="D10" t="n">
         <v>0.5603</v>
@@ -913,7 +913,7 @@
         <v>2.4043</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.027</v>
       </c>
       <c r="D11" t="n">
         <v>0.5499000000000001</v>
@@ -959,7 +959,7 @@
         <v>2.0518</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="D12" t="n">
         <v>0.4075</v>
@@ -1005,7 +1005,7 @@
         <v>1.9723</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.8425</v>
       </c>
       <c r="D13" t="n">
         <v>0.3754</v>
@@ -1051,7 +1051,7 @@
         <v>1.8727</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D14" t="n">
         <v>0.3352</v>
@@ -1097,7 +1097,7 @@
         <v>1.7682</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.7553</v>
       </c>
       <c r="D15" t="n">
         <v>0.293</v>
@@ -1143,7 +1143,7 @@
         <v>1.6937</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.7235</v>
       </c>
       <c r="D16" t="n">
         <v>0.2629</v>
@@ -1189,7 +1189,7 @@
         <v>1.5667</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.6692</v>
       </c>
       <c r="D17" t="n">
         <v>0.2115</v>
@@ -1235,7 +1235,7 @@
         <v>1.2885</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.5504</v>
       </c>
       <c r="D18" t="n">
         <v>0.0992</v>
@@ -1281,7 +1281,7 @@
         <v>1.0167</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.4343</v>
       </c>
       <c r="D19" t="n">
         <v>-0.0106</v>
@@ -1327,7 +1327,7 @@
         <v>1.0124</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.4325</v>
       </c>
       <c r="D20" t="n">
         <v>-0.0124</v>
@@ -1373,7 +1373,7 @@
         <v>0.9228</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.3942</v>
       </c>
       <c r="D21" t="n">
         <v>-0.0486</v>
@@ -1419,7 +1419,7 @@
         <v>0.888</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.3793</v>
       </c>
       <c r="D22" t="n">
         <v>-0.0626</v>
@@ -1465,7 +1465,7 @@
         <v>0.6307</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.2694</v>
       </c>
       <c r="D23" t="n">
         <v>-0.1666</v>
@@ -1511,7 +1511,7 @@
         <v>0.3456</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.1476</v>
       </c>
       <c r="D24" t="n">
         <v>-0.2817</v>
@@ -1557,7 +1557,7 @@
         <v>0.3308</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.1413</v>
       </c>
       <c r="D25" t="n">
         <v>-0.2877</v>
@@ -1603,7 +1603,7 @@
         <v>0.2058</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="D26" t="n">
         <v>-0.3382</v>
@@ -1649,7 +1649,7 @@
         <v>-0.1048</v>
       </c>
       <c r="C27" t="n">
-        <v>-0</v>
+        <v>-0.0448</v>
       </c>
       <c r="D27" t="n">
         <v>-0.4637</v>
@@ -1695,7 +1695,7 @@
         <v>-0.1139</v>
       </c>
       <c r="C28" t="n">
-        <v>-0</v>
+        <v>-0.0487</v>
       </c>
       <c r="D28" t="n">
         <v>-0.4674</v>
@@ -1741,7 +1741,7 @@
         <v>-0.1531</v>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>-0.0654</v>
       </c>
       <c r="D29" t="n">
         <v>-0.4832</v>
@@ -1787,7 +1787,7 @@
         <v>-0.2782</v>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>-0.1188</v>
       </c>
       <c r="D30" t="n">
         <v>-0.5337</v>
@@ -1833,7 +1833,7 @@
         <v>-0.8443000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>-0.3607</v>
       </c>
       <c r="D31" t="n">
         <v>-0.7624</v>
@@ -1879,7 +1879,7 @@
         <v>-0.8928</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>-0.3814</v>
       </c>
       <c r="D32" t="n">
         <v>-0.782</v>
@@ -1925,7 +1925,7 @@
         <v>-0.9284</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>-0.3966</v>
       </c>
       <c r="D33" t="n">
         <v>-0.7964</v>
@@ -1971,7 +1971,7 @@
         <v>-0.9552</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>-0.408</v>
       </c>
       <c r="D34" t="n">
         <v>-0.8072</v>
@@ -2017,7 +2017,7 @@
         <v>-1.0554</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>-0.4508</v>
       </c>
       <c r="D35" t="n">
         <v>-0.8477</v>
@@ -2063,7 +2063,7 @@
         <v>-1.0718</v>
       </c>
       <c r="C36" t="n">
-        <v>-0</v>
+        <v>-0.4578</v>
       </c>
       <c r="D36" t="n">
         <v>-0.8542999999999999</v>
@@ -2109,7 +2109,7 @@
         <v>-1.1718</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>-0.5006</v>
       </c>
       <c r="D37" t="n">
         <v>-0.8947000000000001</v>
@@ -2155,7 +2155,7 @@
         <v>-1.193</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="D38" t="n">
         <v>-0.9033</v>
@@ -2201,7 +2201,7 @@
         <v>-1.2688</v>
       </c>
       <c r="C39" t="n">
-        <v>-0</v>
+        <v>-0.542</v>
       </c>
       <c r="D39" t="n">
         <v>-0.9339</v>
@@ -2247,7 +2247,7 @@
         <v>-1.4141</v>
       </c>
       <c r="C40" t="n">
-        <v>-0</v>
+        <v>-0.6041</v>
       </c>
       <c r="D40" t="n">
         <v>-0.9926</v>
@@ -2293,7 +2293,7 @@
         <v>-1.8356</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-0.7841</v>
       </c>
       <c r="D41" t="n">
         <v>-1.1629</v>

--- a/database/event/6976/event_6976_evp_summary.xlsx
+++ b/database/event/6976/event_6976_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.2772</v>
       </c>
       <c r="D2" t="n">
-        <v>2.678</v>
+        <v>2.6126</v>
       </c>
       <c r="E2" t="n">
         <v>7.672</v>
@@ -548,7 +548,7 @@
         <v>1.9966</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4669</v>
+        <v>1.4183</v>
       </c>
       <c r="E3" t="n">
         <v>4.6741</v>
@@ -594,7 +594,7 @@
         <v>1.9784</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4496</v>
+        <v>1.4012</v>
       </c>
       <c r="E4" t="n">
         <v>4.6313</v>
@@ -640,7 +640,7 @@
         <v>1.5327</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0281</v>
+        <v>0.9855</v>
       </c>
       <c r="E5" t="n">
         <v>3.588</v>
@@ -686,7 +686,7 @@
         <v>1.4573</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9568</v>
+        <v>0.9153</v>
       </c>
       <c r="E6" t="n">
         <v>3.4116</v>
@@ -732,7 +732,7 @@
         <v>1.3573</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8622</v>
+        <v>0.822</v>
       </c>
       <c r="E7" t="n">
         <v>3.1774</v>
@@ -778,7 +778,7 @@
         <v>1.2326</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7443</v>
+        <v>0.7056</v>
       </c>
       <c r="E8" t="n">
         <v>2.8854</v>
@@ -824,7 +824,7 @@
         <v>1.2203</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7326</v>
+        <v>0.6942</v>
       </c>
       <c r="E9" t="n">
         <v>2.8566</v>
@@ -870,7 +870,7 @@
         <v>1.0381</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5603</v>
+        <v>0.5242</v>
       </c>
       <c r="E10" t="n">
         <v>2.4301</v>
@@ -916,7 +916,7 @@
         <v>1.027</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.514</v>
       </c>
       <c r="E11" t="n">
         <v>2.4043</v>
@@ -962,7 +962,7 @@
         <v>0.8764999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4075</v>
+        <v>0.3735</v>
       </c>
       <c r="E12" t="n">
         <v>2.0518</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9723</v>
+        <v>1.9666</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8425</v>
+        <v>0.8401</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3754</v>
+        <v>0.3396</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9723</v>
+        <v>1.9666</v>
       </c>
       <c r="F13" t="n">
-        <v>1.507</v>
+        <v>1.5013</v>
       </c>
       <c r="G13" t="n">
         <v>0.4653</v>
       </c>
       <c r="H13" t="n">
-        <v>1.507</v>
+        <v>1.5013</v>
       </c>
       <c r="I13" t="n">
         <v>1.514</v>
@@ -1054,7 +1054,7 @@
         <v>0.8</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3352</v>
+        <v>0.3022</v>
       </c>
       <c r="E14" t="n">
         <v>1.8727</v>
@@ -1100,7 +1100,7 @@
         <v>0.7553</v>
       </c>
       <c r="D15" t="n">
-        <v>0.293</v>
+        <v>0.2605</v>
       </c>
       <c r="E15" t="n">
         <v>1.7682</v>
@@ -1146,7 +1146,7 @@
         <v>0.7235</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2629</v>
+        <v>0.2309</v>
       </c>
       <c r="E16" t="n">
         <v>1.6937</v>
@@ -1192,7 +1192,7 @@
         <v>0.6692</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2115</v>
+        <v>0.1803</v>
       </c>
       <c r="E17" t="n">
         <v>1.5667</v>
@@ -1238,7 +1238,7 @@
         <v>0.5504</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0992</v>
+        <v>0.0694</v>
       </c>
       <c r="E18" t="n">
         <v>1.2885</v>
@@ -1284,7 +1284,7 @@
         <v>0.4343</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0106</v>
+        <v>-0.0389</v>
       </c>
       <c r="E19" t="n">
         <v>1.0167</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0124</v>
+        <v>1.0049</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4325</v>
+        <v>0.4293</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0124</v>
+        <v>-0.0436</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0124</v>
+        <v>1.0049</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0124</v>
+        <v>2.0049</v>
       </c>
       <c r="G20" t="n">
         <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0124</v>
+        <v>2.0049</v>
       </c>
       <c r="I20" t="n">
         <v>2.0218</v>
@@ -1376,7 +1376,7 @@
         <v>0.3942</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0486</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="E21" t="n">
         <v>0.9228</v>
@@ -1422,7 +1422,7 @@
         <v>0.3793</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0626</v>
+        <v>-0.0901</v>
       </c>
       <c r="E22" t="n">
         <v>0.888</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6307</v>
+        <v>0.6284</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2694</v>
+        <v>0.2684</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1666</v>
+        <v>-0.1936</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6307</v>
+        <v>0.6284</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6087</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>0.022</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6087</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="I23" t="n">
         <v>0.6115</v>
@@ -1514,7 +1514,7 @@
         <v>0.1476</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2817</v>
+        <v>-0.3062</v>
       </c>
       <c r="E24" t="n">
         <v>0.3456</v>
@@ -1560,7 +1560,7 @@
         <v>0.1413</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2877</v>
+        <v>-0.3121</v>
       </c>
       <c r="E25" t="n">
         <v>0.3308</v>
@@ -1606,7 +1606,7 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3382</v>
+        <v>-0.3619</v>
       </c>
       <c r="E26" t="n">
         <v>0.2058</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0448</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4637</v>
+        <v>-0.4857</v>
       </c>
       <c r="E27" t="n">
         <v>-0.1048</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1139</v>
+        <v>-0.1113</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0487</v>
+        <v>-0.0475</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4674</v>
+        <v>-0.4883</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1139</v>
+        <v>-0.1113</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.6938</v>
+        <v>-0.6912</v>
       </c>
       <c r="G28" t="n">
         <v>0.5799</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6938</v>
+        <v>-0.6912</v>
       </c>
       <c r="I28" t="n">
         <v>-0.697</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0654</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4832</v>
+        <v>-0.5049</v>
       </c>
       <c r="E29" t="n">
         <v>-0.1531</v>
@@ -1790,7 +1790,7 @@
         <v>-0.1188</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5337</v>
+        <v>-0.5547</v>
       </c>
       <c r="E30" t="n">
         <v>-0.2782</v>
@@ -1836,7 +1836,7 @@
         <v>-0.3607</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7624</v>
+        <v>-0.7803</v>
       </c>
       <c r="E31" t="n">
         <v>-0.8443000000000001</v>
@@ -1882,7 +1882,7 @@
         <v>-0.3814</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.782</v>
+        <v>-0.7996</v>
       </c>
       <c r="E32" t="n">
         <v>-0.8928</v>
@@ -1928,7 +1928,7 @@
         <v>-0.3966</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7964</v>
+        <v>-0.8138</v>
       </c>
       <c r="E33" t="n">
         <v>-0.9284</v>
@@ -1974,7 +1974,7 @@
         <v>-0.408</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8072</v>
+        <v>-0.8245</v>
       </c>
       <c r="E34" t="n">
         <v>-0.9552</v>
@@ -2020,7 +2020,7 @@
         <v>-0.4508</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8477</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="E35" t="n">
         <v>-1.0554</v>
@@ -2066,7 +2066,7 @@
         <v>-0.4578</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.8709</v>
       </c>
       <c r="E36" t="n">
         <v>-1.0718</v>
@@ -2112,7 +2112,7 @@
         <v>-0.5006</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-0.9108000000000001</v>
       </c>
       <c r="E37" t="n">
         <v>-1.1718</v>
@@ -2158,7 +2158,7 @@
         <v>-0.5096000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9033</v>
+        <v>-0.9192</v>
       </c>
       <c r="E38" t="n">
         <v>-1.193</v>
@@ -2204,7 +2204,7 @@
         <v>-0.542</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9339</v>
+        <v>-0.9494</v>
       </c>
       <c r="E39" t="n">
         <v>-1.2688</v>
@@ -2250,7 +2250,7 @@
         <v>-0.6041</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9926</v>
+        <v>-1.0073</v>
       </c>
       <c r="E40" t="n">
         <v>-1.4141</v>
@@ -2296,7 +2296,7 @@
         <v>-0.7841</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1629</v>
+        <v>-1.1752</v>
       </c>
       <c r="E41" t="n">
         <v>-1.8356</v>

--- a/database/event/6976/event_6976_evp_summary.xlsx
+++ b/database/event/6976/event_6976_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.672</v>
+        <v>7.1454</v>
       </c>
       <c r="C2" t="n">
-        <v>3.2772</v>
+        <v>3.0523</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6126</v>
+        <v>2.5878</v>
       </c>
       <c r="E2" t="n">
-        <v>7.672</v>
+        <v>7.1454</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7407</v>
+        <v>2.3389</v>
       </c>
       <c r="G2" t="n">
-        <v>5.9313</v>
+        <v>4.8065</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7407</v>
+        <v>2.7545</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4109</v>
+        <v>1.4322</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9313</v>
+        <v>4.8065</v>
       </c>
       <c r="K2" t="n">
         <v>85</v>
@@ -529,7 +529,7 @@
         <v>78</v>
       </c>
       <c r="M2" t="n">
-        <v>7.3422</v>
+        <v>6.2387</v>
       </c>
       <c r="N2" t="n">
         <v>163</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.6741</v>
+        <v>4.3709</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9966</v>
+        <v>1.8671</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4183</v>
+        <v>1.3352</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6741</v>
+        <v>4.3709</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2088</v>
+        <v>3.4966</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4653</v>
+        <v>0.8743</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3723</v>
+        <v>6.8335</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5439</v>
+        <v>3.5531</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4653</v>
+        <v>0.8743</v>
       </c>
       <c r="K3" t="n">
         <v>118</v>
@@ -575,7 +575,7 @@
         <v>86</v>
       </c>
       <c r="M3" t="n">
-        <v>4.0092</v>
+        <v>4.4274</v>
       </c>
       <c r="N3" t="n">
         <v>204</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6313</v>
+        <v>3.831</v>
       </c>
       <c r="C4" t="n">
-        <v>1.9784</v>
+        <v>1.6365</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4012</v>
+        <v>1.0915</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6313</v>
+        <v>3.831</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1941</v>
+        <v>3.4388</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4372</v>
+        <v>0.3922</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3132</v>
+        <v>6.63</v>
       </c>
       <c r="I4" t="n">
-        <v>3.496</v>
+        <v>3.4473</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4372</v>
+        <v>0.3922</v>
       </c>
       <c r="K4" t="n">
         <v>85</v>
@@ -621,7 +621,7 @@
         <v>78</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9332</v>
+        <v>3.8395</v>
       </c>
       <c r="N4" t="n">
         <v>163</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.588</v>
+        <v>3.4328</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5327</v>
+        <v>1.4664</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9855</v>
+        <v>0.9117</v>
       </c>
       <c r="E5" t="n">
-        <v>3.588</v>
+        <v>3.4328</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5859</v>
+        <v>0.8971</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0021</v>
+        <v>2.5357</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5859</v>
+        <v>0.8971</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5859</v>
+        <v>0.8971</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0021</v>
+        <v>2.5357</v>
       </c>
       <c r="K5" t="n">
         <v>85</v>
@@ -667,7 +667,7 @@
         <v>82</v>
       </c>
       <c r="M5" t="n">
-        <v>3.588</v>
+        <v>3.4328</v>
       </c>
       <c r="N5" t="n">
         <v>167</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.4116</v>
+        <v>3.2955</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4573</v>
+        <v>1.4077</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9153</v>
+        <v>0.8497</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4116</v>
+        <v>3.2955</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9599</v>
+        <v>2.4451</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4517</v>
+        <v>0.8504</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9599</v>
+        <v>2.4451</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9599</v>
+        <v>2.4451</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4517</v>
+        <v>0.8504</v>
       </c>
       <c r="K6" t="n">
         <v>105</v>
@@ -713,7 +713,7 @@
         <v>112</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4116</v>
+        <v>3.2955</v>
       </c>
       <c r="N6" t="n">
         <v>217</v>
@@ -722,35 +722,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1774</v>
+        <v>3.1616</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3573</v>
+        <v>1.3505</v>
       </c>
       <c r="D7" t="n">
-        <v>0.822</v>
+        <v>0.7893</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1774</v>
+        <v>3.1616</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1623</v>
+        <v>1.1513</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0151</v>
+        <v>2.0103</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1623</v>
+        <v>1.1513</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1623</v>
+        <v>1.1513</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0151</v>
+        <v>2.0103</v>
       </c>
       <c r="K7" t="n">
         <v>105</v>
@@ -759,7 +759,7 @@
         <v>112</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1774</v>
+        <v>3.1616</v>
       </c>
       <c r="N7" t="n">
         <v>217</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8854</v>
+        <v>3.1303</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2326</v>
+        <v>1.3372</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7056</v>
+        <v>0.7752</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8854</v>
+        <v>3.1303</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6479</v>
+        <v>2.723</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2375</v>
+        <v>0.4073</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6479</v>
+        <v>4.1077</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1462</v>
+        <v>2.1358</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2375</v>
+        <v>0.4073</v>
       </c>
       <c r="K8" t="n">
         <v>85</v>
@@ -805,7 +805,7 @@
         <v>78</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3837</v>
+        <v>2.5431</v>
       </c>
       <c r="N8" t="n">
         <v>163</v>
@@ -814,173 +814,173 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8566</v>
+        <v>3.0034</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2203</v>
+        <v>1.283</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6942</v>
+        <v>0.7179</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8566</v>
+        <v>3.0034</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1277</v>
+        <v>2.7178</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7289</v>
+        <v>0.2856</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1277</v>
+        <v>4.0894</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1277</v>
+        <v>2.1263</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7289</v>
+        <v>0.2856</v>
       </c>
       <c r="K9" t="n">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="L9" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8566</v>
+        <v>2.4119</v>
       </c>
       <c r="N9" t="n">
-        <v>167</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4301</v>
+        <v>2.9755</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0381</v>
+        <v>1.271</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5242</v>
+        <v>0.7053</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4301</v>
+        <v>2.9755</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7083</v>
+        <v>2.375</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2782</v>
+        <v>0.6005</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7083</v>
+        <v>2.8818</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7083</v>
+        <v>1.4984</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2782</v>
+        <v>0.6005</v>
       </c>
       <c r="K10" t="n">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="L10" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4301</v>
+        <v>2.0989</v>
       </c>
       <c r="N10" t="n">
-        <v>167</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4043</v>
+        <v>2.9635</v>
       </c>
       <c r="C11" t="n">
-        <v>1.027</v>
+        <v>1.2659</v>
       </c>
       <c r="D11" t="n">
-        <v>0.514</v>
+        <v>0.6999</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4043</v>
+        <v>2.9635</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3336</v>
+        <v>2.9679</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0707</v>
+        <v>-0.0044</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3336</v>
+        <v>3.1572</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8915</v>
+        <v>3.1572</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0707</v>
+        <v>-0.0044</v>
       </c>
       <c r="K11" t="n">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="L11" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M11" t="n">
-        <v>1.9622</v>
+        <v>3.1528</v>
       </c>
       <c r="N11" t="n">
-        <v>204</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0518</v>
+        <v>2.524</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8764999999999999</v>
+        <v>1.0782</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3735</v>
+        <v>0.5014</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0518</v>
+        <v>2.524</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3472</v>
+        <v>1.8055</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7046</v>
+        <v>0.7185</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3472</v>
+        <v>1.8055</v>
       </c>
       <c r="I12" t="n">
-        <v>1.092</v>
+        <v>0.9388</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7046</v>
+        <v>0.7185</v>
       </c>
       <c r="K12" t="n">
         <v>118</v>
@@ -989,7 +989,7 @@
         <v>86</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7966</v>
+        <v>1.6573</v>
       </c>
       <c r="N12" t="n">
         <v>204</v>
@@ -998,139 +998,139 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9666</v>
+        <v>2.5092</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8401</v>
+        <v>1.0719</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3396</v>
+        <v>0.4948</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9666</v>
+        <v>2.5092</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5013</v>
+        <v>0.9902</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4653</v>
+        <v>1.519</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5013</v>
+        <v>0.9902</v>
       </c>
       <c r="I13" t="n">
-        <v>1.514</v>
+        <v>0.9902</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4653</v>
+        <v>1.519</v>
       </c>
       <c r="K13" t="n">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="L13" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9793</v>
+        <v>2.5092</v>
       </c>
       <c r="N13" t="n">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8727</v>
+        <v>2.3226</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8</v>
+        <v>0.9921</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3022</v>
+        <v>0.4105</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8727</v>
+        <v>2.3226</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4829</v>
+        <v>1.4928</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3556</v>
+        <v>0.8298</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4829</v>
+        <v>1.4928</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4829</v>
+        <v>0.7762</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3556</v>
+        <v>0.8298</v>
       </c>
       <c r="K14" t="n">
         <v>85</v>
       </c>
       <c r="L14" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8727</v>
+        <v>1.606</v>
       </c>
       <c r="N14" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7682</v>
+        <v>2.2625</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7553</v>
+        <v>0.9665</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2605</v>
+        <v>0.3834</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7682</v>
+        <v>2.2625</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7651</v>
+        <v>1.7666</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0031</v>
+        <v>0.4959</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7651</v>
+        <v>1.7666</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6201</v>
+        <v>1.8393</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0031</v>
+        <v>0.4959</v>
       </c>
       <c r="K15" t="n">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="L15" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6232</v>
+        <v>2.3352</v>
       </c>
       <c r="N15" t="n">
-        <v>163</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6937</v>
+        <v>2.2109</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7235</v>
+        <v>0.9444</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2309</v>
+        <v>0.3601</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6937</v>
+        <v>2.2109</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6937</v>
+        <v>2.2109</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6937</v>
+        <v>2.2109</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6937</v>
+        <v>2.2109</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6937</v>
+        <v>2.2109</v>
       </c>
       <c r="N16" t="n">
         <v>84</v>
@@ -1182,277 +1182,277 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5667</v>
+        <v>2.0542</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6692</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1803</v>
+        <v>0.2894</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5667</v>
+        <v>2.0542</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6481</v>
+        <v>2.7847</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9186</v>
+        <v>-0.7305</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6481</v>
+        <v>2.7847</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5253</v>
+        <v>2.7847</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9186</v>
+        <v>-0.7305</v>
       </c>
       <c r="K17" t="n">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="L17" t="n">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4439</v>
+        <v>2.0542</v>
       </c>
       <c r="N17" t="n">
-        <v>204</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2885</v>
+        <v>1.5612</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5504</v>
+        <v>0.6669</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0694</v>
+        <v>0.0668</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2885</v>
+        <v>1.5612</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2885</v>
+        <v>-0.4372</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.9984</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2885</v>
+        <v>-0.4372</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2885</v>
+        <v>-0.4372</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.9984</v>
       </c>
       <c r="K18" t="n">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2885</v>
+        <v>1.5612</v>
       </c>
       <c r="N18" t="n">
-        <v>111</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0167</v>
+        <v>1.519</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4343</v>
+        <v>0.6489</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0389</v>
+        <v>0.0477</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0167</v>
+        <v>1.519</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5706</v>
+        <v>2.8566</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5873</v>
+        <v>-1.3376</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5706</v>
+        <v>4.5787</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4625</v>
+        <v>2.3807</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5873</v>
+        <v>-1.3376</v>
       </c>
       <c r="K19" t="n">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="L19" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1248</v>
+        <v>1.0431</v>
       </c>
       <c r="N19" t="n">
-        <v>163</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0049</v>
+        <v>1.453</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4293</v>
+        <v>0.6207</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0436</v>
+        <v>0.0179</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0049</v>
+        <v>1.453</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0049</v>
+        <v>1.453</v>
       </c>
       <c r="G20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0049</v>
+        <v>1.453</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0218</v>
+        <v>1.453</v>
       </c>
       <c r="J20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L20" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0218</v>
+        <v>1.453</v>
       </c>
       <c r="N20" t="n">
-        <v>191</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9228</v>
+        <v>1.3222</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3942</v>
+        <v>0.5648</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.0411</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9228</v>
+        <v>1.3222</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2595</v>
+        <v>2.0064</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3367</v>
+        <v>-0.6842</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2595</v>
+        <v>2.0064</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2595</v>
+        <v>2.0889</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3367</v>
+        <v>-0.6842</v>
       </c>
       <c r="K21" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="L21" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9228000000000001</v>
+        <v>1.4047</v>
       </c>
       <c r="N21" t="n">
-        <v>125</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.888</v>
+        <v>1.2234</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3793</v>
+        <v>0.5226</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0901</v>
+        <v>-0.0857</v>
       </c>
       <c r="E22" t="n">
-        <v>0.888</v>
+        <v>1.2234</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5026</v>
+        <v>1.514</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6146</v>
+        <v>-0.2906</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5026</v>
+        <v>1.514</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0284</v>
+        <v>1.514</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.6146</v>
+        <v>-0.2906</v>
       </c>
       <c r="K22" t="n">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="L22" t="n">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4137999999999999</v>
+        <v>1.2234</v>
       </c>
       <c r="N22" t="n">
-        <v>204</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6284</v>
+        <v>1.0509</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2684</v>
+        <v>0.4489</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1936</v>
+        <v>-0.1636</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6284</v>
+        <v>1.0509</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.9525</v>
       </c>
       <c r="G23" t="n">
-        <v>0.022</v>
+        <v>0.0984</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.9525</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6115</v>
+        <v>0.9917</v>
       </c>
       <c r="J23" t="n">
-        <v>0.022</v>
+        <v>0.0984</v>
       </c>
       <c r="K23" t="n">
         <v>119</v>
@@ -1495,7 +1495,7 @@
         <v>72</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6335000000000001</v>
+        <v>1.0901</v>
       </c>
       <c r="N23" t="n">
         <v>191</v>
@@ -1504,277 +1504,277 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3456</v>
+        <v>0.9986</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1476</v>
+        <v>0.4266</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3062</v>
+        <v>-0.1872</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3456</v>
+        <v>0.9986</v>
       </c>
       <c r="F24" t="n">
-        <v>1.547</v>
+        <v>-0.4572</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2014</v>
+        <v>1.4558</v>
       </c>
       <c r="H24" t="n">
-        <v>1.547</v>
+        <v>-0.4572</v>
       </c>
       <c r="I24" t="n">
-        <v>1.547</v>
+        <v>-0.2377</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.2014</v>
+        <v>1.4558</v>
       </c>
       <c r="K24" t="n">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="L24" t="n">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3455999999999999</v>
+        <v>1.2181</v>
       </c>
       <c r="N24" t="n">
-        <v>217</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3308</v>
+        <v>0.9092</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1413</v>
+        <v>0.3884</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3121</v>
+        <v>-0.2276</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3308</v>
+        <v>0.9092</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4416</v>
+        <v>1.7608</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7724</v>
+        <v>-0.8516</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4416</v>
+        <v>1.7608</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4416</v>
+        <v>1.7608</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7724</v>
+        <v>-0.8516</v>
       </c>
       <c r="K25" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="L25" t="n">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3308</v>
+        <v>0.9091999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>167</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2058</v>
+        <v>0.6011</v>
       </c>
       <c r="C26" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.2568</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3619</v>
+        <v>-0.3666</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2058</v>
+        <v>0.6011</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2058</v>
+        <v>-0.2023</v>
       </c>
       <c r="G26" t="n">
-        <v>-1</v>
+        <v>0.8034</v>
       </c>
       <c r="H26" t="n">
-        <v>1.2058</v>
+        <v>-0.2023</v>
       </c>
       <c r="I26" t="n">
-        <v>1.2058</v>
+        <v>-0.2023</v>
       </c>
       <c r="J26" t="n">
-        <v>-1</v>
+        <v>0.8034</v>
       </c>
       <c r="K26" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L26" t="n">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2058</v>
+        <v>0.6011</v>
       </c>
       <c r="N26" t="n">
-        <v>125</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1048</v>
+        <v>0.3474</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0448</v>
+        <v>0.1484</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4857</v>
+        <v>-0.4812</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1048</v>
+        <v>0.3474</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1048</v>
+        <v>0.2453</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.1021</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1048</v>
+        <v>0.2453</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1048</v>
+        <v>0.2453</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.1021</v>
       </c>
       <c r="K27" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1048</v>
+        <v>0.3474</v>
       </c>
       <c r="N27" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1113</v>
+        <v>0.1826</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0475</v>
+        <v>0.078</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4883</v>
+        <v>-0.5556</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1113</v>
+        <v>0.1826</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.6912</v>
+        <v>0.1826</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5799</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6912</v>
+        <v>0.1826</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.697</v>
+        <v>0.1826</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5799</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L28" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1171</v>
+        <v>0.1826</v>
       </c>
       <c r="N28" t="n">
-        <v>191</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1531</v>
+        <v>0.1405</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0654</v>
+        <v>0.06</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5049</v>
+        <v>-0.5746</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1531</v>
+        <v>0.1405</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1458</v>
+        <v>-0.4934</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0073</v>
+        <v>0.6339</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1458</v>
+        <v>-0.4934</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1458</v>
+        <v>-0.5137</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0073</v>
+        <v>0.6339</v>
       </c>
       <c r="K29" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="L29" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1531</v>
+        <v>0.1202</v>
       </c>
       <c r="N29" t="n">
-        <v>125</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30">
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2782</v>
+        <v>-0.0538</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1188</v>
+        <v>-0.023</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5547</v>
+        <v>-0.6623</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2782</v>
+        <v>-0.0538</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.013</v>
+        <v>-0.0603</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.2652</v>
+        <v>0.0065</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.013</v>
+        <v>-0.0603</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0131</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.2652</v>
+        <v>0.0065</v>
       </c>
       <c r="K30" t="n">
         <v>119</v>
@@ -1817,7 +1817,7 @@
         <v>72</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2783</v>
+        <v>-0.0563</v>
       </c>
       <c r="N30" t="n">
         <v>191</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.343</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3607</v>
+        <v>-0.1465</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7803</v>
+        <v>-0.7929</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.343</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.343</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.343</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.343</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.343</v>
       </c>
       <c r="N31" t="n">
         <v>111</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8928</v>
+        <v>-0.3574</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3814</v>
+        <v>-0.1527</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7996</v>
+        <v>-0.7994</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8928</v>
+        <v>-0.3574</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5503</v>
+        <v>0.7523</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.4431</v>
+        <v>-1.1097</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5503</v>
+        <v>0.7523</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5503</v>
+        <v>0.7523</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.4431</v>
+        <v>-1.1097</v>
       </c>
       <c r="K32" t="n">
         <v>105</v>
@@ -1909,7 +1909,7 @@
         <v>112</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8928</v>
+        <v>-0.3573999999999999</v>
       </c>
       <c r="N32" t="n">
         <v>217</v>
@@ -1918,170 +1918,170 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9284</v>
+        <v>-0.4945</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3966</v>
+        <v>-0.2112</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8138</v>
+        <v>-0.8613</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9284</v>
+        <v>-0.4945</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0716</v>
+        <v>-0.4945</v>
       </c>
       <c r="G33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0716</v>
+        <v>-0.4945</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0716</v>
+        <v>-0.4945</v>
       </c>
       <c r="J33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L33" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.9284</v>
+        <v>-0.4945</v>
       </c>
       <c r="N33" t="n">
-        <v>125</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9552</v>
+        <v>-0.5006</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.408</v>
+        <v>-0.2138</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8245</v>
+        <v>-0.864</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9552</v>
+        <v>-0.5006</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9552</v>
+        <v>0.2393</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.7399</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9552</v>
+        <v>0.2393</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9552</v>
+        <v>0.2393</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.7399</v>
       </c>
       <c r="K34" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9552</v>
+        <v>-0.5005999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>84</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>dycha</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0554</v>
+        <v>-0.6179</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4508</v>
+        <v>-0.2639</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.917</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0554</v>
+        <v>-0.6179</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0554</v>
+        <v>-0.6179</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0554</v>
+        <v>-0.6179</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0554</v>
+        <v>-0.6179</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.0554</v>
+        <v>-0.6179</v>
       </c>
       <c r="N35" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>salazar</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0718</v>
+        <v>-0.7055</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4578</v>
+        <v>-0.3014</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8709</v>
+        <v>-0.9565</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0718</v>
+        <v>-0.7055</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.0718</v>
+        <v>-0.7055</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.0718</v>
+        <v>-0.7055</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0718</v>
+        <v>-0.7055</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0718</v>
+        <v>-0.7055</v>
       </c>
       <c r="N36" t="n">
         <v>84</v>
@@ -2102,32 +2102,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>salazar</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1718</v>
+        <v>-0.7138</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5006</v>
+        <v>-0.3049</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-0.9603</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1718</v>
+        <v>-0.7138</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1718</v>
+        <v>-0.7138</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1718</v>
+        <v>-0.7138</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1718</v>
+        <v>-0.7138</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1718</v>
+        <v>-0.7138</v>
       </c>
       <c r="N37" t="n">
         <v>84</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.193</v>
+        <v>-0.7201</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.3076</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9192</v>
+        <v>-0.9631</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.193</v>
+        <v>-0.7201</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.193</v>
+        <v>-0.7201</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.193</v>
+        <v>-0.7201</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.193</v>
+        <v>-0.7201</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.193</v>
+        <v>-0.7201</v>
       </c>
       <c r="N38" t="n">
         <v>111</v>
@@ -2194,47 +2194,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dycha</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2688</v>
+        <v>-0.7619</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.542</v>
+        <v>-0.3255</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9494</v>
+        <v>-0.982</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2688</v>
+        <v>-0.7619</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2688</v>
+        <v>-0.7619</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2688</v>
+        <v>-0.7619</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2688</v>
+        <v>-0.7619</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2688</v>
+        <v>-0.7619</v>
       </c>
       <c r="N39" t="n">
-        <v>111</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4141</v>
+        <v>-0.9527</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6041</v>
+        <v>-0.407</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0073</v>
+        <v>-1.0681</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4141</v>
+        <v>-0.9527</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.4141</v>
+        <v>-0.1549</v>
       </c>
       <c r="G40" t="n">
-        <v>-1</v>
+        <v>-0.7978</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.4141</v>
+        <v>-0.1549</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4141</v>
+        <v>-0.1549</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>-0.7978</v>
       </c>
       <c r="K40" t="n">
         <v>91</v>
@@ -2277,7 +2277,7 @@
         <v>34</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4141</v>
+        <v>-0.9527</v>
       </c>
       <c r="N40" t="n">
         <v>125</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8356</v>
+        <v>-1.2324</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7841</v>
+        <v>-0.5264</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1752</v>
+        <v>-1.1944</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8356</v>
+        <v>-1.2324</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.39</v>
+        <v>-0.9463</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.4456</v>
+        <v>-0.2861</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.39</v>
+        <v>-0.9463</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.39</v>
+        <v>-0.9463</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.4456</v>
+        <v>-0.2861</v>
       </c>
       <c r="K41" t="n">
         <v>105</v>
@@ -2323,7 +2323,7 @@
         <v>112</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8356</v>
+        <v>-1.2324</v>
       </c>
       <c r="N41" t="n">
         <v>217</v>
@@ -2429,10 +2429,10 @@
         <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6737</v>
+        <v>0.8339</v>
       </c>
       <c r="J2" t="n">
-        <v>12.1266</v>
+        <v>15.0102</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.76</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3896</v>
+        <v>-0.2567</v>
       </c>
       <c r="J3" t="n">
-        <v>-7.0128</v>
+        <v>-4.6206</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.7</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4786</v>
+        <v>-0.3142</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.614800000000001</v>
+        <v>-5.6556</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4927</v>
+        <v>-0.3237</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.868600000000001</v>
+        <v>-5.8266</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.61</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.601</v>
+        <v>-0.3991</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.818</v>
+        <v>-7.1838</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.67</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4891</v>
+        <v>1.3218</v>
       </c>
       <c r="J7" t="n">
-        <v>26.8038</v>
+        <v>23.7924</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.65</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4519</v>
+        <v>1.2978</v>
       </c>
       <c r="J8" t="n">
-        <v>26.1342</v>
+        <v>23.3604</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.45</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0561</v>
+        <v>1.0524</v>
       </c>
       <c r="J9" t="n">
-        <v>19.0098</v>
+        <v>18.9432</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1851</v>
+        <v>0.2726</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3318</v>
+        <v>4.9068</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.77</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8257</v>
+        <v>-0.7791</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.8626</v>
+        <v>-14.0238</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.54</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8224</v>
+        <v>1.0192</v>
       </c>
       <c r="J12" t="n">
-        <v>16.448</v>
+        <v>20.384</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.397</v>
+        <v>0.4517</v>
       </c>
       <c r="J13" t="n">
-        <v>7.94</v>
+        <v>9.034000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.77</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4174</v>
+        <v>-0.2643</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.348000000000001</v>
+        <v>-5.286</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.75</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4454</v>
+        <v>-0.2838</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.907999999999999</v>
+        <v>-5.676</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.55</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7005</v>
+        <v>-0.4708</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.01</v>
+        <v>-9.416</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>2.2</v>
       </c>
       <c r="I17" t="n">
-        <v>2.219</v>
+        <v>1.8681</v>
       </c>
       <c r="J17" t="n">
-        <v>44.38</v>
+        <v>37.362</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.113</v>
+        <v>0.1827</v>
       </c>
       <c r="J18" t="n">
-        <v>2.26</v>
+        <v>3.654</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.06</v>
       </c>
       <c r="I19" t="n">
-        <v>0.113</v>
+        <v>0.1827</v>
       </c>
       <c r="J19" t="n">
-        <v>2.26</v>
+        <v>3.654</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.9</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.478</v>
+        <v>-0.405</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.56</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7076</v>
+        <v>-0.6506</v>
       </c>
       <c r="J21" t="n">
-        <v>-14.152</v>
+        <v>-13.012</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.53</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2672</v>
+        <v>0.8986</v>
       </c>
       <c r="J22" t="n">
-        <v>22.8096</v>
+        <v>16.1748</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.46</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1262</v>
+        <v>0.8096</v>
       </c>
       <c r="J23" t="n">
-        <v>20.2716</v>
+        <v>14.5728</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3878</v>
+        <v>0.4062</v>
       </c>
       <c r="J24" t="n">
-        <v>6.9804</v>
+        <v>7.3116</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.14</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3336</v>
+        <v>0.3756</v>
       </c>
       <c r="J25" t="n">
-        <v>6.0048</v>
+        <v>6.7608</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5904</v>
+        <v>-0.5232</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.6272</v>
+        <v>-9.4176</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.03</v>
       </c>
       <c r="I27" t="n">
-        <v>0.155</v>
+        <v>0.1332</v>
       </c>
       <c r="J27" t="n">
-        <v>2.79</v>
+        <v>2.3976</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.97</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0329</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.1728</v>
+        <v>-0.5921999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.85</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2466</v>
+        <v>-0.1716</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.4388</v>
+        <v>-3.0888</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.77</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3845</v>
+        <v>-0.2503</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.921</v>
+        <v>-4.5054</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.64</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5679</v>
+        <v>-0.3745</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.2222</v>
+        <v>-6.741</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.38</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9882</v>
+        <v>0.718</v>
       </c>
       <c r="J32" t="n">
-        <v>21.7404</v>
+        <v>15.796</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.28</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7621</v>
+        <v>0.5824</v>
       </c>
       <c r="J33" t="n">
-        <v>16.7662</v>
+        <v>12.8128</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.22</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6128</v>
+        <v>0.4985</v>
       </c>
       <c r="J34" t="n">
-        <v>13.4816</v>
+        <v>10.967</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.15</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3994</v>
+        <v>0.3982</v>
       </c>
       <c r="J35" t="n">
-        <v>8.786799999999999</v>
+        <v>8.760400000000001</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.82</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6742</v>
+        <v>-0.6157</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.8324</v>
+        <v>-13.5454</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.32</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5343</v>
       </c>
       <c r="J37" t="n">
-        <v>12.408</v>
+        <v>11.7546</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.2</v>
       </c>
       <c r="I38" t="n">
-        <v>0.402</v>
+        <v>0.4065</v>
       </c>
       <c r="J38" t="n">
-        <v>8.843999999999999</v>
+        <v>8.943</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.88</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.244</v>
+        <v>-0.1503</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.368</v>
+        <v>-3.3066</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.82</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3404</v>
+        <v>-0.2127</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.4888</v>
+        <v>-4.6794</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.52</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7341</v>
+        <v>-0.4964</v>
       </c>
       <c r="J41" t="n">
-        <v>-16.1502</v>
+        <v>-10.9208</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.39</v>
       </c>
       <c r="I42" t="n">
-        <v>1.073</v>
+        <v>0.7627</v>
       </c>
       <c r="J42" t="n">
-        <v>25.752</v>
+        <v>18.3048</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.27</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8061</v>
+        <v>0.5936</v>
       </c>
       <c r="J43" t="n">
-        <v>19.3464</v>
+        <v>14.2464</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.99</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1124</v>
+        <v>-0.0653</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.6976</v>
+        <v>-1.5672</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3322</v>
+        <v>-0.2744</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.9728</v>
+        <v>-6.5856</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.68</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9649</v>
+        <v>-0.9373</v>
       </c>
       <c r="J46" t="n">
-        <v>-23.1576</v>
+        <v>-22.4952</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.26</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4706</v>
+        <v>0.4616</v>
       </c>
       <c r="J47" t="n">
-        <v>11.2944</v>
+        <v>11.0784</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.08</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1967</v>
+        <v>0.2073</v>
       </c>
       <c r="J48" t="n">
-        <v>4.7208</v>
+        <v>4.9752</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.92</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1892</v>
+        <v>-0.1106</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.5408</v>
+        <v>-2.6544</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2072</v>
+        <v>-0.122</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.9728</v>
+        <v>-2.928</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.78</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4098</v>
+        <v>-0.2577</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.8352</v>
+        <v>-6.1848</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.29</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8456</v>
+        <v>0.6192</v>
       </c>
       <c r="J52" t="n">
-        <v>20.2944</v>
+        <v>14.8608</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.28</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8225</v>
+        <v>0.6049</v>
       </c>
       <c r="J53" t="n">
-        <v>19.74</v>
+        <v>14.5176</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3503</v>
+        <v>0.3272</v>
       </c>
       <c r="J54" t="n">
-        <v>8.4072</v>
+        <v>7.8528</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.07</v>
       </c>
       <c r="I55" t="n">
-        <v>0.248</v>
+        <v>0.2441</v>
       </c>
       <c r="J55" t="n">
-        <v>5.952</v>
+        <v>5.8584</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.58</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.1799</v>
+        <v>-1.1787</v>
       </c>
       <c r="J56" t="n">
-        <v>-28.3176</v>
+        <v>-28.2888</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.45</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7103</v>
+        <v>0.6544</v>
       </c>
       <c r="J57" t="n">
-        <v>17.0472</v>
+        <v>15.7056</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.13</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2827</v>
+        <v>0.3098</v>
       </c>
       <c r="J58" t="n">
-        <v>6.7848</v>
+        <v>7.4352</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1877</v>
+        <v>-0.1102</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.5048</v>
+        <v>-2.6448</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.76</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4369</v>
+        <v>-0.2769</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.4856</v>
+        <v>-6.6456</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.67</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5565</v>
+        <v>-0.3629</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.356</v>
+        <v>-8.7096</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.18</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3708</v>
+        <v>0.318</v>
       </c>
       <c r="J62" t="n">
-        <v>10.7532</v>
+        <v>9.222</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>0.029</v>
+        <v>0.0056</v>
       </c>
       <c r="J63" t="n">
-        <v>0.841</v>
+        <v>0.1624</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.98</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0334</v>
+        <v>-0.0327</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.9686</v>
+        <v>-0.9483</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.91</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1932</v>
+        <v>-0.1181</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.6028</v>
+        <v>-3.4249</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.7</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5114</v>
+        <v>-0.3309</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.8306</v>
+        <v>-9.5961</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.41</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6216</v>
+        <v>0.4564</v>
       </c>
       <c r="J67" t="n">
-        <v>18.0264</v>
+        <v>13.2356</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.23</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3873</v>
+        <v>0.3261</v>
       </c>
       <c r="J68" t="n">
-        <v>11.2317</v>
+        <v>9.456899999999999</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.15</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2651</v>
+        <v>0.2274</v>
       </c>
       <c r="J69" t="n">
-        <v>7.6879</v>
+        <v>6.5946</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2068</v>
+        <v>-0.1122</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.9972</v>
+        <v>-3.2538</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.85</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3346</v>
+        <v>-0.2005</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.7034</v>
+        <v>-5.8145</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.85</v>
       </c>
       <c r="I72" t="n">
-        <v>1.8475</v>
+        <v>1.3671</v>
       </c>
       <c r="J72" t="n">
-        <v>44.34</v>
+        <v>32.8104</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.98</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1554</v>
+        <v>-0.1056</v>
       </c>
       <c r="J73" t="n">
-        <v>-3.7296</v>
+        <v>-2.5344</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.85</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.5591</v>
+        <v>-0.5032</v>
       </c>
       <c r="J74" t="n">
-        <v>-13.4184</v>
+        <v>-12.0768</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.6615</v>
+        <v>-0.6098</v>
       </c>
       <c r="J75" t="n">
-        <v>-15.876</v>
+        <v>-14.6352</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.76</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7825</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>-18.78</v>
+        <v>-17.7216</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.28</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4967</v>
+        <v>0.482</v>
       </c>
       <c r="J77" t="n">
-        <v>11.9208</v>
+        <v>11.568</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.16</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3273</v>
+        <v>0.3531</v>
       </c>
       <c r="J78" t="n">
-        <v>7.8552</v>
+        <v>8.474399999999999</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.96</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1109</v>
+        <v>-0.0625</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.6616</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.8</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3817</v>
+        <v>-0.2381</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.1608</v>
+        <v>-5.7144</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4382</v>
+        <v>-0.2776</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.5168</v>
+        <v>-6.6624</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.32</v>
       </c>
       <c r="I82" t="n">
-        <v>2.2006</v>
+        <v>1.8148</v>
       </c>
       <c r="J82" t="n">
-        <v>41.8114</v>
+        <v>34.4812</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.199</v>
+        <v>0.2818</v>
       </c>
       <c r="J83" t="n">
-        <v>3.781</v>
+        <v>5.3542</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.04</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0182</v>
+        <v>0.0979</v>
       </c>
       <c r="J84" t="n">
-        <v>0.3458</v>
+        <v>1.8601</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.01</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.0945</v>
+        <v>-0.0151</v>
       </c>
       <c r="J85" t="n">
-        <v>-1.7955</v>
+        <v>-0.2869</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2882</v>
+        <v>-0.2034</v>
       </c>
       <c r="J86" t="n">
-        <v>-5.4758</v>
+        <v>-3.8646</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.41</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6965</v>
+        <v>0.6446</v>
       </c>
       <c r="J87" t="n">
-        <v>13.2335</v>
+        <v>12.2474</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.86</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2544</v>
+        <v>-0.1652</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.8336</v>
+        <v>-3.1388</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.75</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.4273</v>
+        <v>-0.275</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.1187</v>
+        <v>-5.225</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.73</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4558</v>
+        <v>-0.2944</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.6602</v>
+        <v>-5.5936</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.71</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4836</v>
+        <v>-0.3136</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.1884</v>
+        <v>-5.9584</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.83</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.1441</v>
+        <v>-0.1407</v>
       </c>
       <c r="J92" t="n">
-        <v>-2.0174</v>
+        <v>-1.9698</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.66</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.4107</v>
+        <v>-0.3208</v>
       </c>
       <c r="J93" t="n">
-        <v>-5.7498</v>
+        <v>-4.4912</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.63</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.4613</v>
+        <v>-0.3488</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.4582</v>
+        <v>-4.8832</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.62</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4798</v>
+        <v>-0.3578</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.7172</v>
+        <v>-5.0092</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.31</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.9304</v>
+        <v>-0.6479</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.0256</v>
+        <v>-9.070600000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>2.01</v>
       </c>
       <c r="I97" t="n">
-        <v>1.8521</v>
+        <v>1.3734</v>
       </c>
       <c r="J97" t="n">
-        <v>25.9294</v>
+        <v>19.2276</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.72</v>
       </c>
       <c r="I98" t="n">
-        <v>1.4476</v>
+        <v>1.0564</v>
       </c>
       <c r="J98" t="n">
-        <v>20.2664</v>
+        <v>14.7896</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.61</v>
       </c>
       <c r="I99" t="n">
-        <v>1.2068</v>
+        <v>0.9356</v>
       </c>
       <c r="J99" t="n">
-        <v>16.8952</v>
+        <v>13.0984</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.46</v>
       </c>
       <c r="I100" t="n">
-        <v>0.9022</v>
+        <v>0.76</v>
       </c>
       <c r="J100" t="n">
-        <v>12.6308</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.38</v>
       </c>
       <c r="I101" t="n">
-        <v>0.7403</v>
+        <v>0.6601</v>
       </c>
       <c r="J101" t="n">
-        <v>10.3642</v>
+        <v>9.241400000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.22</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4725</v>
+        <v>0.4599</v>
       </c>
       <c r="J102" t="n">
-        <v>9.449999999999999</v>
+        <v>9.198</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.87</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1926</v>
+        <v>-0.1499</v>
       </c>
       <c r="J103" t="n">
-        <v>-3.852</v>
+        <v>-2.998</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.87</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1926</v>
+        <v>-0.1499</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.852</v>
+        <v>-2.998</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.63</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5772</v>
+        <v>-0.3817</v>
       </c>
       <c r="J105" t="n">
-        <v>-11.544</v>
+        <v>-7.634</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.59</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6292</v>
+        <v>-0.4191</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.584</v>
+        <v>-8.382</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.77</v>
       </c>
       <c r="I107" t="n">
-        <v>1.7036</v>
+        <v>1.1931</v>
       </c>
       <c r="J107" t="n">
-        <v>34.072</v>
+        <v>23.862</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.26</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6694</v>
+        <v>0.5457</v>
       </c>
       <c r="J108" t="n">
-        <v>13.388</v>
+        <v>10.914</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.26</v>
       </c>
       <c r="I109" t="n">
-        <v>0.6694</v>
+        <v>0.5457</v>
       </c>
       <c r="J109" t="n">
-        <v>13.388</v>
+        <v>10.914</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.97</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2728</v>
+        <v>-0.191</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.456</v>
+        <v>-3.82</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.92</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4303</v>
+        <v>-0.3533</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.606</v>
+        <v>-7.066</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2988</v>
+        <v>0.2414</v>
       </c>
       <c r="J112" t="n">
-        <v>5.976</v>
+        <v>4.828</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2304</v>
+        <v>0.1744</v>
       </c>
       <c r="J113" t="n">
-        <v>4.608</v>
+        <v>3.488</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.78</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3714</v>
+        <v>-0.2413</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.428</v>
+        <v>-4.826</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.72</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4601</v>
+        <v>-0.2995</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.202</v>
+        <v>-5.99</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.61</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6083</v>
+        <v>-0.4034</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.166</v>
+        <v>-8.068</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.47</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6857</v>
+        <v>0.6042</v>
       </c>
       <c r="J117" t="n">
-        <v>13.714</v>
+        <v>12.084</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.44</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6503</v>
+        <v>0.5704</v>
       </c>
       <c r="J118" t="n">
-        <v>13.006</v>
+        <v>11.408</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.08</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1207</v>
+        <v>0.1305</v>
       </c>
       <c r="J119" t="n">
-        <v>2.414</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.98</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1148</v>
+        <v>-0.0495</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.296</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.72</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5162</v>
+        <v>-0.3315</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.324</v>
+        <v>-6.63</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.81</v>
       </c>
       <c r="I122" t="n">
-        <v>1.8082</v>
+        <v>1.5329</v>
       </c>
       <c r="J122" t="n">
-        <v>41.5886</v>
+        <v>35.2567</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.24</v>
       </c>
       <c r="I123" t="n">
-        <v>0.655</v>
+        <v>0.6576</v>
       </c>
       <c r="J123" t="n">
-        <v>15.065</v>
+        <v>15.1248</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.24</v>
       </c>
       <c r="I124" t="n">
-        <v>0.655</v>
+        <v>0.6576</v>
       </c>
       <c r="J124" t="n">
-        <v>15.065</v>
+        <v>15.1248</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.85</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.6035</v>
+        <v>-0.5392</v>
       </c>
       <c r="J125" t="n">
-        <v>-13.8805</v>
+        <v>-12.4016</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7729</v>
+        <v>-0.7225</v>
       </c>
       <c r="J126" t="n">
-        <v>-17.7767</v>
+        <v>-16.6175</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>2.08</v>
       </c>
       <c r="I127" t="n">
-        <v>1.3376</v>
+        <v>1.4743</v>
       </c>
       <c r="J127" t="n">
-        <v>30.7648</v>
+        <v>33.9089</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.1</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1985</v>
+        <v>0.2319</v>
       </c>
       <c r="J128" t="n">
-        <v>4.5655</v>
+        <v>5.3337</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.92</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2135</v>
+        <v>-0.1192</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.9105</v>
+        <v>-2.7416</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.89</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2636</v>
+        <v>-0.153</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.0628</v>
+        <v>-3.519</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.36</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.9244</v>
+        <v>-0.6468</v>
       </c>
       <c r="J131" t="n">
-        <v>-21.2612</v>
+        <v>-14.8764</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.43</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1077</v>
+        <v>1.0643</v>
       </c>
       <c r="J132" t="n">
-        <v>32.1233</v>
+        <v>30.8647</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.12</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3296</v>
+        <v>0.3697</v>
       </c>
       <c r="J133" t="n">
-        <v>9.558400000000001</v>
+        <v>10.7213</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2374</v>
+        <v>0.287</v>
       </c>
       <c r="J134" t="n">
-        <v>6.8846</v>
+        <v>8.323</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.07</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1748</v>
+        <v>0.2284</v>
       </c>
       <c r="J135" t="n">
-        <v>5.0692</v>
+        <v>6.6236</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.01</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.0416</v>
+        <v>0.0205</v>
       </c>
       <c r="J136" t="n">
-        <v>-1.2064</v>
+        <v>0.5945</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.23</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4254</v>
+        <v>0.4926</v>
       </c>
       <c r="J137" t="n">
-        <v>12.3366</v>
+        <v>14.2854</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3829</v>
+        <v>0.4381</v>
       </c>
       <c r="J138" t="n">
-        <v>11.1041</v>
+        <v>12.7049</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1135</v>
+        <v>0.1157</v>
       </c>
       <c r="J139" t="n">
-        <v>3.2915</v>
+        <v>3.3553</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3096</v>
+        <v>-0.1882</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.978400000000001</v>
+        <v>-5.4578</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5336</v>
+        <v>-0.3459</v>
       </c>
       <c r="J141" t="n">
-        <v>-15.4744</v>
+        <v>-10.0311</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.43</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7175</v>
+        <v>0.891</v>
       </c>
       <c r="J142" t="n">
-        <v>14.35</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.83</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.3086</v>
+        <v>-0.1967</v>
       </c>
       <c r="J143" t="n">
-        <v>-6.172</v>
+        <v>-3.934</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3403</v>
+        <v>-0.2169</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.806</v>
+        <v>-4.338</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.79</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3709</v>
+        <v>-0.2368</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.418</v>
+        <v>-4.736</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.64</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5786</v>
+        <v>-0.3808</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.572</v>
+        <v>-7.616</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.5</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2124</v>
+        <v>1.1367</v>
       </c>
       <c r="J147" t="n">
-        <v>24.248</v>
+        <v>22.734</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.36</v>
       </c>
       <c r="I148" t="n">
-        <v>0.9179</v>
+        <v>0.923</v>
       </c>
       <c r="J148" t="n">
-        <v>18.358</v>
+        <v>18.46</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.25</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6554</v>
+        <v>0.6733</v>
       </c>
       <c r="J149" t="n">
-        <v>13.108</v>
+        <v>13.466</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.08</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1683</v>
+        <v>0.24</v>
       </c>
       <c r="J150" t="n">
-        <v>3.366</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.91</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4542</v>
+        <v>-0.3792</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.084</v>
+        <v>-7.584</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4157</v>
+        <v>0.4706</v>
       </c>
       <c r="J152" t="n">
-        <v>7.4826</v>
+        <v>8.470800000000001</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.92</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.119</v>
+        <v>-0.0994</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.142</v>
+        <v>-1.7892</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.83</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2966</v>
+        <v>-0.1935</v>
       </c>
       <c r="J154" t="n">
-        <v>-5.3388</v>
+        <v>-3.483</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3296</v>
+        <v>-0.2135</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.9328</v>
+        <v>-3.843</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6113</v>
+        <v>-0.4052</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.0034</v>
+        <v>-7.2936</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>2.06</v>
       </c>
       <c r="I157" t="n">
-        <v>2.0572</v>
+        <v>1.7778</v>
       </c>
       <c r="J157" t="n">
-        <v>37.0296</v>
+        <v>32.0004</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.86</v>
       </c>
       <c r="I158" t="n">
-        <v>1.8277</v>
+        <v>1.5468</v>
       </c>
       <c r="J158" t="n">
-        <v>32.8986</v>
+        <v>27.8424</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.4</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9472</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="J159" t="n">
-        <v>17.0496</v>
+        <v>17.5734</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.74</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.8922</v>
+        <v>-0.8534</v>
       </c>
       <c r="J160" t="n">
-        <v>-16.0596</v>
+        <v>-15.3612</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.58</v>
       </c>
       <c r="I161" t="n">
-        <v>-1.222</v>
+        <v>-1.2301</v>
       </c>
       <c r="J161" t="n">
-        <v>-21.996</v>
+        <v>-22.1418</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.32</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5647</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="J162" t="n">
-        <v>13.5528</v>
+        <v>16.1976</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.09</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2314</v>
+        <v>0.2405</v>
       </c>
       <c r="J163" t="n">
-        <v>5.5536</v>
+        <v>5.772</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.02</v>
       </c>
       <c r="I164" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="J164" t="n">
-        <v>2.2512</v>
+        <v>1.848</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.71</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4963</v>
+        <v>-0.3204</v>
       </c>
       <c r="J165" t="n">
-        <v>-11.9112</v>
+        <v>-7.6896</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.59</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6498</v>
+        <v>-0.4326</v>
       </c>
       <c r="J166" t="n">
-        <v>-15.5952</v>
+        <v>-10.3824</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.8</v>
       </c>
       <c r="I167" t="n">
-        <v>1.816</v>
+        <v>1.5398</v>
       </c>
       <c r="J167" t="n">
-        <v>43.584</v>
+        <v>36.9552</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.12</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3384</v>
+        <v>0.3715</v>
       </c>
       <c r="J168" t="n">
-        <v>8.121600000000001</v>
+        <v>8.916</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0058</v>
+        <v>0.0641</v>
       </c>
       <c r="J169" t="n">
-        <v>0.1392</v>
+        <v>1.5384</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.93</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3675</v>
+        <v>-0.2968</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.82</v>
+        <v>-7.1232</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7126</v>
+        <v>-0.6587</v>
       </c>
       <c r="J171" t="n">
-        <v>-17.1024</v>
+        <v>-15.8088</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.15</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3745</v>
+        <v>0.4142</v>
       </c>
       <c r="J172" t="n">
-        <v>7.8645</v>
+        <v>8.6982</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1184</v>
+        <v>0.0859</v>
       </c>
       <c r="J173" t="n">
-        <v>2.4864</v>
+        <v>1.8039</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.82</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2869</v>
+        <v>-0.1986</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.0249</v>
+        <v>-4.1706</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.58</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.6398</v>
+        <v>-0.427</v>
       </c>
       <c r="J175" t="n">
-        <v>-13.4358</v>
+        <v>-8.967000000000001</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.57</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6525</v>
+        <v>-0.4363</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.7025</v>
+        <v>-9.1623</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.64</v>
       </c>
       <c r="I177" t="n">
-        <v>1.4831</v>
+        <v>1.3125</v>
       </c>
       <c r="J177" t="n">
-        <v>31.1451</v>
+        <v>27.5625</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.47</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1516</v>
+        <v>1.0984</v>
       </c>
       <c r="J178" t="n">
-        <v>24.1836</v>
+        <v>23.0664</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.05</v>
       </c>
       <c r="I179" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.1474</v>
       </c>
       <c r="J179" t="n">
-        <v>1.5813</v>
+        <v>3.0954</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.98</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2305</v>
+        <v>-0.1497</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.8405</v>
+        <v>-3.1437</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3022</v>
+        <v>-0.222</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.3462</v>
+        <v>-4.662</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.19</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4629</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="J182" t="n">
-        <v>7.8693</v>
+        <v>9.1426</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.74</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.3871</v>
+        <v>-0.2672</v>
       </c>
       <c r="J183" t="n">
-        <v>-6.5807</v>
+        <v>-4.5424</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.73</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.4043</v>
+        <v>-0.2765</v>
       </c>
       <c r="J184" t="n">
-        <v>-6.8731</v>
+        <v>-4.7005</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.66</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.5122</v>
+        <v>-0.3422</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.7074</v>
+        <v>-5.8174</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.47</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7633</v>
+        <v>-0.5194</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.9761</v>
+        <v>-8.829800000000001</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.64</v>
       </c>
       <c r="I187" t="n">
-        <v>1.4038</v>
+        <v>1.2727</v>
       </c>
       <c r="J187" t="n">
-        <v>23.8646</v>
+        <v>21.6359</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.53</v>
       </c>
       <c r="I188" t="n">
-        <v>1.1889</v>
+        <v>1.1412</v>
       </c>
       <c r="J188" t="n">
-        <v>20.2113</v>
+        <v>19.4004</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.49</v>
       </c>
       <c r="I189" t="n">
-        <v>1.1063</v>
+        <v>1.0928</v>
       </c>
       <c r="J189" t="n">
-        <v>18.8071</v>
+        <v>18.5776</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.47</v>
       </c>
       <c r="I190" t="n">
-        <v>1.0638</v>
+        <v>1.0685</v>
       </c>
       <c r="J190" t="n">
-        <v>18.0846</v>
+        <v>18.1645</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.84</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6751</v>
+        <v>-0.6122</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.4767</v>
+        <v>-10.4074</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.35</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5481</v>
+        <v>0.4727</v>
       </c>
       <c r="J192" t="n">
-        <v>13.1544</v>
+        <v>11.3448</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.16</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2824</v>
+        <v>0.2405</v>
       </c>
       <c r="J193" t="n">
-        <v>6.7776</v>
+        <v>5.772</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.14</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2491</v>
+        <v>0.2146</v>
       </c>
       <c r="J194" t="n">
-        <v>5.9784</v>
+        <v>5.1504</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.12</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2128</v>
+        <v>0.1883</v>
       </c>
       <c r="J195" t="n">
-        <v>5.1072</v>
+        <v>4.5192</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.79</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4197</v>
+        <v>-0.2612</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.0728</v>
+        <v>-6.2688</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.15</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3141</v>
+        <v>0.2671</v>
       </c>
       <c r="J197" t="n">
-        <v>7.5384</v>
+        <v>6.4104</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0488</v>
+        <v>0.0305</v>
       </c>
       <c r="J198" t="n">
-        <v>1.1712</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.99</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0262</v>
+        <v>-0.0198</v>
       </c>
       <c r="J199" t="n">
-        <v>-0.6288</v>
+        <v>-0.4752</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.91</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2057</v>
+        <v>-0.1215</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.9368</v>
+        <v>-2.916</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.87</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2734</v>
+        <v>-0.1653</v>
       </c>
       <c r="J201" t="n">
-        <v>-6.5616</v>
+        <v>-3.9672</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.27</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4686</v>
+        <v>0.5522</v>
       </c>
       <c r="J202" t="n">
-        <v>11.2464</v>
+        <v>13.2528</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.21</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3855</v>
+        <v>0.4459</v>
       </c>
       <c r="J203" t="n">
-        <v>9.252000000000001</v>
+        <v>10.7016</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.97</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1071</v>
+        <v>-0.0535</v>
       </c>
       <c r="J204" t="n">
-        <v>-2.5704</v>
+        <v>-1.284</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.88</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2713</v>
+        <v>-0.1602</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.5112</v>
+        <v>-3.8448</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.85</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3181</v>
+        <v>-0.1921</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.6344</v>
+        <v>-4.6104</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.26</v>
       </c>
       <c r="I207" t="n">
-        <v>0.771</v>
+        <v>0.7417</v>
       </c>
       <c r="J207" t="n">
-        <v>18.504</v>
+        <v>17.8008</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.11</v>
       </c>
       <c r="I208" t="n">
-        <v>0.375</v>
+        <v>0.3556</v>
       </c>
       <c r="J208" t="n">
-        <v>9</v>
+        <v>8.5344</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.1</v>
       </c>
       <c r="I209" t="n">
-        <v>0.3436</v>
+        <v>0.3279</v>
       </c>
       <c r="J209" t="n">
-        <v>8.2464</v>
+        <v>7.8696</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.08</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2758</v>
+        <v>0.2716</v>
       </c>
       <c r="J210" t="n">
-        <v>6.6192</v>
+        <v>6.5184</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6691</v>
+        <v>-0.616</v>
       </c>
       <c r="J211" t="n">
-        <v>-16.0584</v>
+        <v>-14.784</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.36</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6313</v>
+        <v>0.7678</v>
       </c>
       <c r="J212" t="n">
-        <v>14.5199</v>
+        <v>17.6594</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.97</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0316</v>
+        <v>-0.0408</v>
       </c>
       <c r="J213" t="n">
-        <v>-0.7268</v>
+        <v>-0.9384</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.88</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2232</v>
+        <v>-0.1454</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.1336</v>
+        <v>-3.3442</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.75</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4302</v>
+        <v>-0.2763</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.894600000000001</v>
+        <v>-6.3549</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.55</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6915</v>
+        <v>-0.4642</v>
       </c>
       <c r="J216" t="n">
-        <v>-15.9045</v>
+        <v>-10.6766</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.52</v>
       </c>
       <c r="I217" t="n">
-        <v>1.3172</v>
+        <v>1.1985</v>
       </c>
       <c r="J217" t="n">
-        <v>30.2956</v>
+        <v>27.5655</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.17</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5327</v>
+        <v>0.5093</v>
       </c>
       <c r="J218" t="n">
-        <v>12.2521</v>
+        <v>11.7139</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.17</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5327</v>
+        <v>0.5093</v>
       </c>
       <c r="J219" t="n">
-        <v>12.2521</v>
+        <v>11.7139</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.89</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4674</v>
+        <v>-0.4038</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.7502</v>
+        <v>-9.2874</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.71</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.909</v>
+        <v>-0.8744</v>
       </c>
       <c r="J221" t="n">
-        <v>-20.907</v>
+        <v>-20.1112</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.15</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3382</v>
+        <v>0.3716</v>
       </c>
       <c r="J222" t="n">
-        <v>8.1168</v>
+        <v>8.9184</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1</v>
       </c>
       <c r="I223" t="n">
-        <v>0.0444</v>
+        <v>0.0153</v>
       </c>
       <c r="J223" t="n">
-        <v>1.0656</v>
+        <v>0.3672</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.89</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2142</v>
+        <v>-0.1366</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.1408</v>
+        <v>-3.2784</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.82</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3316</v>
+        <v>-0.2093</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.9584</v>
+        <v>-5.0232</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.74</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4492</v>
+        <v>-0.2883</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.7808</v>
+        <v>-6.9192</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.67</v>
       </c>
       <c r="I227" t="n">
-        <v>1.5898</v>
+        <v>1.383</v>
       </c>
       <c r="J227" t="n">
-        <v>38.1552</v>
+        <v>33.192</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.26</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7246</v>
       </c>
       <c r="J228" t="n">
-        <v>17.868</v>
+        <v>17.3904</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3303</v>
+        <v>-0.2613</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.9272</v>
+        <v>-6.2712</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.86</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5576</v>
+        <v>-0.4948</v>
       </c>
       <c r="J230" t="n">
-        <v>-13.3824</v>
+        <v>-11.8752</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.86</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5576</v>
+        <v>-0.4948</v>
       </c>
       <c r="J231" t="n">
-        <v>-13.3824</v>
+        <v>-11.8752</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.85</v>
       </c>
       <c r="I232" t="n">
-        <v>1.7337</v>
+        <v>1.4929</v>
       </c>
       <c r="J232" t="n">
-        <v>27.7392</v>
+        <v>23.8864</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.54</v>
       </c>
       <c r="I233" t="n">
-        <v>1.1448</v>
+        <v>1.1388</v>
       </c>
       <c r="J233" t="n">
-        <v>18.3168</v>
+        <v>18.2208</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.49</v>
       </c>
       <c r="I234" t="n">
-        <v>1.0183</v>
+        <v>1.0817</v>
       </c>
       <c r="J234" t="n">
-        <v>16.2928</v>
+        <v>17.3072</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.41</v>
       </c>
       <c r="I235" t="n">
-        <v>0.8439</v>
+        <v>0.9687</v>
       </c>
       <c r="J235" t="n">
-        <v>13.5024</v>
+        <v>15.4992</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.28</v>
       </c>
       <c r="I236" t="n">
-        <v>0.5636</v>
+        <v>0.6875</v>
       </c>
       <c r="J236" t="n">
-        <v>9.0176</v>
+        <v>11</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.65</v>
       </c>
       <c r="I237" t="n">
-        <v>0.9939</v>
+        <v>1.1861</v>
       </c>
       <c r="J237" t="n">
-        <v>15.9024</v>
+        <v>18.9776</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.99</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0451</v>
+        <v>0.0022</v>
       </c>
       <c r="J238" t="n">
-        <v>0.7216</v>
+        <v>0.0352</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.83</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.275</v>
+        <v>-0.1898</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.4</v>
+        <v>-3.0368</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.45</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.8007</v>
+        <v>-0.5476</v>
       </c>
       <c r="J240" t="n">
-        <v>-12.8112</v>
+        <v>-8.7616</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.26</v>
       </c>
       <c r="I241" t="n">
-        <v>-1.0152</v>
+        <v>-0.7181</v>
       </c>
       <c r="J241" t="n">
-        <v>-16.2432</v>
+        <v>-11.4896</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.31</v>
       </c>
       <c r="I242" t="n">
-        <v>0.8356</v>
+        <v>0.8275</v>
       </c>
       <c r="J242" t="n">
-        <v>25.068</v>
+        <v>24.825</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.31</v>
       </c>
       <c r="I243" t="n">
-        <v>0.8356</v>
+        <v>0.8275</v>
       </c>
       <c r="J243" t="n">
-        <v>25.068</v>
+        <v>24.825</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.25</v>
       </c>
       <c r="I244" t="n">
-        <v>0.6929</v>
+        <v>0.6865</v>
       </c>
       <c r="J244" t="n">
-        <v>20.787</v>
+        <v>20.595</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.03</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0301</v>
+        <v>0.0935</v>
       </c>
       <c r="J245" t="n">
-        <v>0.903</v>
+        <v>2.805</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.92</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.408</v>
+        <v>-0.3352</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.24</v>
+        <v>-10.056</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.32</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5488</v>
+        <v>0.655</v>
       </c>
       <c r="J247" t="n">
-        <v>16.464</v>
+        <v>19.65</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.15</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3119</v>
+        <v>0.3473</v>
       </c>
       <c r="J248" t="n">
-        <v>9.356999999999999</v>
+        <v>10.419</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.9</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2253</v>
+        <v>-0.1334</v>
       </c>
       <c r="J249" t="n">
-        <v>-6.759</v>
+        <v>-4.002</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.83</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3375</v>
+        <v>-0.2077</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.125</v>
+        <v>-6.231</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.76</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4382</v>
+        <v>-0.2776</v>
       </c>
       <c r="J251" t="n">
-        <v>-13.146</v>
+        <v>-8.327999999999999</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.39</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0641</v>
+        <v>1.0291</v>
       </c>
       <c r="J252" t="n">
-        <v>22.3461</v>
+        <v>21.6111</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.21</v>
       </c>
       <c r="I253" t="n">
-        <v>0.6516</v>
+        <v>0.619</v>
       </c>
       <c r="J253" t="n">
-        <v>13.6836</v>
+        <v>12.999</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.18</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5747</v>
+        <v>0.5426</v>
       </c>
       <c r="J254" t="n">
-        <v>12.0687</v>
+        <v>11.3946</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.89</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4578</v>
+        <v>-0.3971</v>
       </c>
       <c r="J255" t="n">
-        <v>-9.613799999999999</v>
+        <v>-8.3391</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.67</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.9909</v>
+        <v>-0.9657</v>
       </c>
       <c r="J256" t="n">
-        <v>-20.8089</v>
+        <v>-20.2797</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.33</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5483</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="J257" t="n">
-        <v>11.5143</v>
+        <v>13.7928</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.05</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1196</v>
+        <v>0.1337</v>
       </c>
       <c r="J258" t="n">
-        <v>2.5116</v>
+        <v>2.8077</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.03</v>
       </c>
       <c r="I259" t="n">
-        <v>0.0687</v>
+        <v>0.0876</v>
       </c>
       <c r="J259" t="n">
-        <v>1.4427</v>
+        <v>1.8396</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.95</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1472</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="J260" t="n">
-        <v>-3.0912</v>
+        <v>-1.6632</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.8</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3907</v>
+        <v>-0.2427</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.204700000000001</v>
+        <v>-5.0967</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.53</v>
       </c>
       <c r="I262" t="n">
-        <v>1.2242</v>
+        <v>1.1535</v>
       </c>
       <c r="J262" t="n">
-        <v>23.2598</v>
+        <v>21.9165</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.52</v>
       </c>
       <c r="I263" t="n">
-        <v>1.2042</v>
+        <v>1.1411</v>
       </c>
       <c r="J263" t="n">
-        <v>22.8798</v>
+        <v>21.6809</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.32</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7531</v>
+        <v>0.8136</v>
       </c>
       <c r="J264" t="n">
-        <v>14.3089</v>
+        <v>15.4584</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.32</v>
       </c>
       <c r="I265" t="n">
-        <v>0.7531</v>
+        <v>0.8136</v>
       </c>
       <c r="J265" t="n">
-        <v>14.3089</v>
+        <v>15.4584</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.91</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4802</v>
+        <v>-0.4024</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.123799999999999</v>
+        <v>-7.6456</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.17</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3834</v>
+        <v>0.4278</v>
       </c>
       <c r="J267" t="n">
-        <v>7.2846</v>
+        <v>8.1282</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0767</v>
       </c>
       <c r="J268" t="n">
-        <v>-1.596</v>
+        <v>-1.4573</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.84</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2834</v>
+        <v>-0.1843</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.3846</v>
+        <v>-3.5017</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.77</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3944</v>
+        <v>-0.254</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.4936</v>
+        <v>-4.826</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.68</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5214</v>
+        <v>-0.3406</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.906599999999999</v>
+        <v>-6.4714</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.16</v>
       </c>
       <c r="I272" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J272" t="n">
-        <v>35.0081</v>
+        <v>31.1746</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.58</v>
       </c>
       <c r="I273" t="n">
-        <v>1.2699</v>
+        <v>1.1951</v>
       </c>
       <c r="J273" t="n">
-        <v>21.5883</v>
+        <v>20.3167</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.27</v>
       </c>
       <c r="I274" t="n">
-        <v>0.5678</v>
+        <v>0.6805</v>
       </c>
       <c r="J274" t="n">
-        <v>9.6526</v>
+        <v>11.5685</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.14</v>
       </c>
       <c r="I275" t="n">
-        <v>0.2586</v>
+        <v>0.3592</v>
       </c>
       <c r="J275" t="n">
-        <v>4.3962</v>
+        <v>6.1064</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.02</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.0915</v>
+        <v>-0.0061</v>
       </c>
       <c r="J276" t="n">
-        <v>-1.5555</v>
+        <v>-0.1037</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.16</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4021</v>
+        <v>0.4516</v>
       </c>
       <c r="J277" t="n">
-        <v>6.8357</v>
+        <v>7.6772</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.01</v>
       </c>
       <c r="I278" t="n">
-        <v>0.131</v>
+        <v>0.0988</v>
       </c>
       <c r="J278" t="n">
-        <v>2.227</v>
+        <v>1.6796</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.71</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.4535</v>
+        <v>-0.3005</v>
       </c>
       <c r="J279" t="n">
-        <v>-7.7095</v>
+        <v>-5.1085</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.68</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4971</v>
+        <v>-0.3289</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.450699999999999</v>
+        <v>-5.5913</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.42</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.8300999999999999</v>
+        <v>-0.5702</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.1117</v>
+        <v>-9.6934</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.62</v>
       </c>
       <c r="I282" t="n">
-        <v>1.483</v>
+        <v>1.3105</v>
       </c>
       <c r="J282" t="n">
-        <v>43.007</v>
+        <v>38.0045</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.59</v>
       </c>
       <c r="I283" t="n">
-        <v>1.4261</v>
+        <v>1.2722</v>
       </c>
       <c r="J283" t="n">
-        <v>41.3569</v>
+        <v>36.8938</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.85</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.5918</v>
+        <v>-0.529</v>
       </c>
       <c r="J284" t="n">
-        <v>-17.1622</v>
+        <v>-15.341</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.84</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.6172</v>
+        <v>-0.556</v>
       </c>
       <c r="J285" t="n">
-        <v>-17.8988</v>
+        <v>-16.124</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.82</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6669</v>
+        <v>-0.6091</v>
       </c>
       <c r="J286" t="n">
-        <v>-19.3401</v>
+        <v>-17.6639</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.13</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2975</v>
+        <v>0.3226</v>
       </c>
       <c r="J287" t="n">
-        <v>8.6275</v>
+        <v>9.355399999999999</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.12</v>
       </c>
       <c r="I288" t="n">
-        <v>0.2815</v>
+        <v>0.3025</v>
       </c>
       <c r="J288" t="n">
-        <v>8.163500000000001</v>
+        <v>8.772500000000001</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.95</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1005</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.9145</v>
+        <v>-2.0735</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.86</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2767</v>
+        <v>-0.1712</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.0243</v>
+        <v>-4.9648</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.67</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5491</v>
+        <v>-0.3583</v>
       </c>
       <c r="J291" t="n">
-        <v>-15.9239</v>
+        <v>-10.3907</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6976/event_6976_evp_summary.xlsx
+++ b/database/event/6976/event_6976_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.1454</v>
+        <v>7.3046</v>
       </c>
       <c r="C2" t="n">
-        <v>3.0523</v>
+        <v>3.1203</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5878</v>
+        <v>2.701</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1454</v>
+        <v>7.3046</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3389</v>
+        <v>2.267</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8065</v>
+        <v>5.0376</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7545</v>
+        <v>2.5854</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4322</v>
+        <v>1.3961</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8065</v>
+        <v>5.0376</v>
       </c>
       <c r="K2" t="n">
         <v>85</v>
@@ -529,7 +529,7 @@
         <v>78</v>
       </c>
       <c r="M2" t="n">
-        <v>6.2387</v>
+        <v>6.4337</v>
       </c>
       <c r="N2" t="n">
         <v>163</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.3709</v>
+        <v>4.2607</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8671</v>
+        <v>1.82</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3352</v>
+        <v>1.3154</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3709</v>
+        <v>4.2607</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4966</v>
+        <v>3.4468</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8743</v>
+        <v>0.8139</v>
       </c>
       <c r="H3" t="n">
-        <v>6.8335</v>
+        <v>6.4781</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5531</v>
+        <v>3.4981</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8743</v>
+        <v>0.8139</v>
       </c>
       <c r="K3" t="n">
         <v>118</v>
@@ -575,7 +575,7 @@
         <v>86</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4274</v>
+        <v>4.312</v>
       </c>
       <c r="N3" t="n">
         <v>204</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.831</v>
+        <v>3.9638</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6365</v>
+        <v>1.6932</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0915</v>
+        <v>1.1802</v>
       </c>
       <c r="E4" t="n">
-        <v>3.831</v>
+        <v>3.9638</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4388</v>
+        <v>3.3849</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3922</v>
+        <v>0.5789</v>
       </c>
       <c r="H4" t="n">
-        <v>6.63</v>
+        <v>6.274</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4473</v>
+        <v>3.3879</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3922</v>
+        <v>0.5789</v>
       </c>
       <c r="K4" t="n">
         <v>85</v>
@@ -621,7 +621,7 @@
         <v>78</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8395</v>
+        <v>3.9668</v>
       </c>
       <c r="N4" t="n">
         <v>163</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4328</v>
+        <v>3.5907</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4664</v>
+        <v>1.5338</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9117</v>
+        <v>1.0104</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4328</v>
+        <v>3.5907</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8971</v>
+        <v>0.7968</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5357</v>
+        <v>2.7939</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8971</v>
+        <v>0.7968</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8971</v>
+        <v>0.7968</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5357</v>
+        <v>2.7939</v>
       </c>
       <c r="K5" t="n">
         <v>85</v>
@@ -667,7 +667,7 @@
         <v>82</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4328</v>
+        <v>3.5907</v>
       </c>
       <c r="N5" t="n">
         <v>167</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.2955</v>
+        <v>3.2965</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4077</v>
+        <v>1.4082</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8497</v>
+        <v>0.8764</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2955</v>
+        <v>3.2965</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4451</v>
+        <v>2.3133</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8504</v>
+        <v>0.9832</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4451</v>
+        <v>2.3382</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4451</v>
+        <v>2.3382</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8504</v>
+        <v>0.9832</v>
       </c>
       <c r="K6" t="n">
         <v>105</v>
@@ -713,7 +713,7 @@
         <v>112</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2955</v>
+        <v>3.3214</v>
       </c>
       <c r="N6" t="n">
         <v>217</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1616</v>
+        <v>3.2758</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3505</v>
+        <v>1.3993</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7893</v>
+        <v>0.867</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1616</v>
+        <v>3.2758</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1513</v>
+        <v>1.1012</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0103</v>
+        <v>2.1746</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1513</v>
+        <v>1.1012</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1513</v>
+        <v>1.1012</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0103</v>
+        <v>2.1746</v>
       </c>
       <c r="K7" t="n">
         <v>105</v>
@@ -759,7 +759,7 @@
         <v>112</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1616</v>
+        <v>3.2758</v>
       </c>
       <c r="N7" t="n">
         <v>217</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1303</v>
+        <v>3.1232</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3372</v>
+        <v>1.3341</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7752</v>
+        <v>0.7975</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1303</v>
+        <v>3.1232</v>
       </c>
       <c r="F8" t="n">
-        <v>2.723</v>
+        <v>2.6559</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4073</v>
+        <v>0.4673</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1077</v>
+        <v>3.8688</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1358</v>
+        <v>2.0891</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4073</v>
+        <v>0.4673</v>
       </c>
       <c r="K8" t="n">
         <v>85</v>
@@ -805,7 +805,7 @@
         <v>78</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5431</v>
+        <v>2.5564</v>
       </c>
       <c r="N8" t="n">
         <v>163</v>
@@ -814,35 +814,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0034</v>
+        <v>2.9782</v>
       </c>
       <c r="C9" t="n">
-        <v>1.283</v>
+        <v>1.2722</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7179</v>
+        <v>0.7315</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0034</v>
+        <v>2.9782</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7178</v>
+        <v>2.2893</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2856</v>
+        <v>0.6889</v>
       </c>
       <c r="H9" t="n">
-        <v>4.0894</v>
+        <v>2.6589</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1263</v>
+        <v>1.4358</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2856</v>
+        <v>0.6889</v>
       </c>
       <c r="K9" t="n">
         <v>118</v>
@@ -851,7 +851,7 @@
         <v>86</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4119</v>
+        <v>2.1247</v>
       </c>
       <c r="N9" t="n">
         <v>204</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9755</v>
+        <v>2.9034</v>
       </c>
       <c r="C10" t="n">
-        <v>1.271</v>
+        <v>1.2402</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7053</v>
+        <v>0.6975</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9755</v>
+        <v>2.9034</v>
       </c>
       <c r="F10" t="n">
-        <v>2.375</v>
+        <v>2.6826</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6005</v>
+        <v>0.2208</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8818</v>
+        <v>3.9565</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4984</v>
+        <v>2.1365</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6005</v>
+        <v>0.2208</v>
       </c>
       <c r="K10" t="n">
         <v>118</v>
@@ -897,7 +897,7 @@
         <v>86</v>
       </c>
       <c r="M10" t="n">
-        <v>2.0989</v>
+        <v>2.3573</v>
       </c>
       <c r="N10" t="n">
         <v>204</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9635</v>
+        <v>2.7423</v>
       </c>
       <c r="C11" t="n">
-        <v>1.2659</v>
+        <v>1.1714</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6999</v>
+        <v>0.6241</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9635</v>
+        <v>2.7423</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9679</v>
+        <v>2.673</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0044</v>
+        <v>0.0693</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1572</v>
+        <v>3.1254</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1572</v>
+        <v>3.1254</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0044</v>
+        <v>0.0693</v>
       </c>
       <c r="K11" t="n">
         <v>85</v>
@@ -943,7 +943,7 @@
         <v>82</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1528</v>
+        <v>3.1947</v>
       </c>
       <c r="N11" t="n">
         <v>167</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.524</v>
+        <v>2.6659</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0782</v>
+        <v>1.1388</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5014</v>
+        <v>0.5894</v>
       </c>
       <c r="E12" t="n">
-        <v>2.524</v>
+        <v>2.6659</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8055</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7185</v>
+        <v>1.6856</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8055</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9388</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7185</v>
+        <v>1.6856</v>
       </c>
       <c r="K12" t="n">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="L12" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6573</v>
+        <v>2.6659</v>
       </c>
       <c r="N12" t="n">
-        <v>204</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5092</v>
+        <v>2.5055</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0719</v>
+        <v>1.0703</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4948</v>
+        <v>0.5164</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5092</v>
+        <v>2.5055</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9902</v>
+        <v>1.6791</v>
       </c>
       <c r="G13" t="n">
-        <v>1.519</v>
+        <v>0.8264</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9902</v>
+        <v>1.6791</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9902</v>
+        <v>0.9067</v>
       </c>
       <c r="J13" t="n">
-        <v>1.519</v>
+        <v>0.8264</v>
       </c>
       <c r="K13" t="n">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="L13" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5092</v>
+        <v>1.7331</v>
       </c>
       <c r="N13" t="n">
-        <v>167</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3226</v>
+        <v>2.4169</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9921</v>
+        <v>1.0324</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4105</v>
+        <v>0.476</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3226</v>
+        <v>2.4169</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4928</v>
+        <v>1.4</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8298</v>
+        <v>1.0169</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4928</v>
+        <v>1.4</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7762</v>
+        <v>0.756</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8298</v>
+        <v>1.0169</v>
       </c>
       <c r="K14" t="n">
         <v>85</v>
@@ -1081,7 +1081,7 @@
         <v>78</v>
       </c>
       <c r="M14" t="n">
-        <v>1.606</v>
+        <v>1.7729</v>
       </c>
       <c r="N14" t="n">
         <v>163</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2625</v>
+        <v>2.3027</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9665</v>
+        <v>0.9836</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3834</v>
+        <v>0.424</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2625</v>
+        <v>2.3027</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7666</v>
+        <v>1.7475</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4959</v>
+        <v>0.5552</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7666</v>
+        <v>1.7475</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8393</v>
+        <v>1.7925</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4959</v>
+        <v>0.5552</v>
       </c>
       <c r="K15" t="n">
         <v>119</v>
@@ -1127,7 +1127,7 @@
         <v>72</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3352</v>
+        <v>2.3477</v>
       </c>
       <c r="N15" t="n">
         <v>191</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2109</v>
+        <v>2.1028</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9444</v>
+        <v>0.8983</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3601</v>
+        <v>0.333</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2109</v>
+        <v>2.1028</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2109</v>
+        <v>2.1028</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2109</v>
+        <v>2.1028</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2109</v>
+        <v>2.1028</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2109</v>
+        <v>2.1028</v>
       </c>
       <c r="N16" t="n">
         <v>84</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0542</v>
+        <v>1.7888</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.7641</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2894</v>
+        <v>0.1901</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0542</v>
+        <v>1.7888</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7847</v>
+        <v>-0.3877</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7305</v>
+        <v>2.1765</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7847</v>
+        <v>-0.3877</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7847</v>
+        <v>-0.3877</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7305</v>
+        <v>2.1765</v>
       </c>
       <c r="K17" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L17" t="n">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0542</v>
+        <v>1.7888</v>
       </c>
       <c r="N17" t="n">
-        <v>125</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5612</v>
+        <v>1.7518</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6669</v>
+        <v>0.7483</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0668</v>
+        <v>0.1733</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5612</v>
+        <v>1.7518</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4372</v>
+        <v>2.5166</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9984</v>
+        <v>-0.7648</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4372</v>
+        <v>2.7831</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4372</v>
+        <v>2.7831</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9984</v>
+        <v>-0.7648</v>
       </c>
       <c r="K18" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="L18" t="n">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5612</v>
+        <v>2.0183</v>
       </c>
       <c r="N18" t="n">
-        <v>167</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.519</v>
+        <v>1.4693</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6489</v>
+        <v>0.6276</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0477</v>
+        <v>0.0447</v>
       </c>
       <c r="E19" t="n">
-        <v>1.519</v>
+        <v>1.4693</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8566</v>
+        <v>2.7541</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3376</v>
+        <v>-1.2848</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5787</v>
+        <v>4.1927</v>
       </c>
       <c r="I19" t="n">
-        <v>2.3807</v>
+        <v>2.264</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3376</v>
+        <v>-1.2848</v>
       </c>
       <c r="K19" t="n">
         <v>118</v>
@@ -1311,7 +1311,7 @@
         <v>86</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0431</v>
+        <v>0.9791999999999998</v>
       </c>
       <c r="N19" t="n">
         <v>204</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.453</v>
+        <v>1.4043</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6207</v>
+        <v>0.5999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0179</v>
+        <v>0.0151</v>
       </c>
       <c r="E20" t="n">
-        <v>1.453</v>
+        <v>1.4043</v>
       </c>
       <c r="F20" t="n">
-        <v>1.453</v>
+        <v>1.4043</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.453</v>
+        <v>1.4043</v>
       </c>
       <c r="I20" t="n">
-        <v>1.453</v>
+        <v>1.4043</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.453</v>
+        <v>1.4043</v>
       </c>
       <c r="N20" t="n">
         <v>111</v>
@@ -1366,185 +1366,185 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3222</v>
+        <v>1.3219</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5648</v>
+        <v>0.5647</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0411</v>
+        <v>-0.0224</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3222</v>
+        <v>1.3219</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0064</v>
+        <v>-0.3137</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6842</v>
+        <v>1.6356</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0064</v>
+        <v>-0.3137</v>
       </c>
       <c r="I21" t="n">
-        <v>2.0889</v>
+        <v>-0.1694</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6842</v>
+        <v>1.6356</v>
       </c>
       <c r="K21" t="n">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="L21" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4047</v>
+        <v>1.4662</v>
       </c>
       <c r="N21" t="n">
-        <v>191</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2234</v>
+        <v>1.2813</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5226</v>
+        <v>0.5473</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0857</v>
+        <v>-0.0409</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2234</v>
+        <v>1.2813</v>
       </c>
       <c r="F22" t="n">
-        <v>1.514</v>
+        <v>2.0024</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2906</v>
+        <v>-0.7211</v>
       </c>
       <c r="H22" t="n">
-        <v>1.514</v>
+        <v>2.0024</v>
       </c>
       <c r="I22" t="n">
-        <v>1.514</v>
+        <v>2.054</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2906</v>
+        <v>-0.7211</v>
       </c>
       <c r="K22" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="L22" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2234</v>
+        <v>1.3329</v>
       </c>
       <c r="N22" t="n">
-        <v>125</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0509</v>
+        <v>1.1418</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4489</v>
+        <v>0.4877</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1636</v>
+        <v>-0.1044</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0509</v>
+        <v>1.1418</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9525</v>
+        <v>1.4784</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0984</v>
+        <v>-0.3366</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9525</v>
+        <v>1.4784</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9917</v>
+        <v>1.4784</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0984</v>
+        <v>-0.3366</v>
       </c>
       <c r="K23" t="n">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="L23" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0901</v>
+        <v>1.1418</v>
       </c>
       <c r="N23" t="n">
-        <v>191</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9986</v>
+        <v>1.089</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4266</v>
+        <v>0.4652</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1872</v>
+        <v>-0.1285</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9986</v>
+        <v>1.089</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4572</v>
+        <v>0.9999</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4558</v>
+        <v>0.0891</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4572</v>
+        <v>0.9999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2377</v>
+        <v>1.0257</v>
       </c>
       <c r="J24" t="n">
-        <v>1.4558</v>
+        <v>0.0891</v>
       </c>
       <c r="K24" t="n">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="L24" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="M24" t="n">
-        <v>1.2181</v>
+        <v>1.1148</v>
       </c>
       <c r="N24" t="n">
-        <v>163</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9092</v>
+        <v>0.9048</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3884</v>
+        <v>0.3865</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2276</v>
+        <v>-0.2123</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9092</v>
+        <v>0.9048</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7608</v>
+        <v>1.7439</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8516</v>
+        <v>-0.8391</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7608</v>
+        <v>1.7439</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7608</v>
+        <v>1.7439</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8516</v>
+        <v>-0.8391</v>
       </c>
       <c r="K25" t="n">
         <v>105</v>
@@ -1587,7 +1587,7 @@
         <v>112</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9091999999999999</v>
+        <v>0.9048</v>
       </c>
       <c r="N25" t="n">
         <v>217</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6011</v>
+        <v>0.7834</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2568</v>
+        <v>0.3346</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3666</v>
+        <v>-0.2676</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6011</v>
+        <v>0.7834</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2023</v>
+        <v>-0.1947</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8034</v>
+        <v>0.9781</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2023</v>
+        <v>-0.1947</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2023</v>
+        <v>-0.1947</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8034</v>
+        <v>0.9781</v>
       </c>
       <c r="K26" t="n">
         <v>85</v>
@@ -1633,7 +1633,7 @@
         <v>82</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6011</v>
+        <v>0.7834</v>
       </c>
       <c r="N26" t="n">
         <v>167</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3474</v>
+        <v>0.3493</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1484</v>
+        <v>0.1492</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4812</v>
+        <v>-0.4652</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3474</v>
+        <v>0.3493</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2453</v>
+        <v>0.2282</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1021</v>
+        <v>0.1211</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2453</v>
+        <v>0.2282</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2453</v>
+        <v>0.2282</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1021</v>
+        <v>0.1211</v>
       </c>
       <c r="K27" t="n">
         <v>91</v>
@@ -1679,7 +1679,7 @@
         <v>34</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3474</v>
+        <v>0.3493</v>
       </c>
       <c r="N27" t="n">
         <v>125</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1826</v>
+        <v>0.2834</v>
       </c>
       <c r="C28" t="n">
-        <v>0.078</v>
+        <v>0.1211</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5556</v>
+        <v>-0.4952</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1826</v>
+        <v>0.2834</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1826</v>
+        <v>-0.4203</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.7037</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1826</v>
+        <v>-0.4203</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1826</v>
+        <v>-0.4311</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.7037</v>
       </c>
       <c r="K28" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1826</v>
+        <v>0.2726</v>
       </c>
       <c r="N28" t="n">
-        <v>111</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1405</v>
+        <v>0.1579</v>
       </c>
       <c r="C29" t="n">
-        <v>0.06</v>
+        <v>0.0675</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5746</v>
+        <v>-0.5523</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1405</v>
+        <v>0.1579</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4934</v>
+        <v>0.1579</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6339</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4934</v>
+        <v>0.1579</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5137</v>
+        <v>0.1579</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6339</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L29" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1202</v>
+        <v>0.1579</v>
       </c>
       <c r="N29" t="n">
-        <v>191</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30">
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0538</v>
+        <v>-0.0588</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.023</v>
+        <v>-0.0251</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6623</v>
+        <v>-0.651</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0538</v>
+        <v>-0.0588</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0603</v>
+        <v>-0.091</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0065</v>
+        <v>0.0322</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0603</v>
+        <v>-0.091</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0065</v>
+        <v>0.0322</v>
       </c>
       <c r="K30" t="n">
         <v>119</v>
@@ -1817,7 +1817,7 @@
         <v>72</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0563</v>
+        <v>-0.06109999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>191</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.343</v>
+        <v>-0.3758</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1465</v>
+        <v>-0.1605</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7929</v>
+        <v>-0.7953</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.343</v>
+        <v>-0.3758</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.343</v>
+        <v>-0.3758</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.343</v>
+        <v>-0.3758</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.343</v>
+        <v>-0.3758</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.343</v>
+        <v>-0.3758</v>
       </c>
       <c r="N31" t="n">
         <v>111</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3574</v>
+        <v>-0.3935</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1527</v>
+        <v>-0.1681</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7994</v>
+        <v>-0.8033</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3574</v>
+        <v>-0.3935</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7523</v>
+        <v>0.7244</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.1097</v>
+        <v>-1.1179</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7523</v>
+        <v>0.7244</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7523</v>
+        <v>0.7244</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.1097</v>
+        <v>-1.1179</v>
       </c>
       <c r="K32" t="n">
         <v>105</v>
@@ -1909,7 +1909,7 @@
         <v>112</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3573999999999999</v>
+        <v>-0.3934999999999998</v>
       </c>
       <c r="N32" t="n">
         <v>217</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4945</v>
+        <v>-0.5351</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2112</v>
+        <v>-0.2286</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8613</v>
+        <v>-0.8678</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4945</v>
+        <v>-0.5351</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4945</v>
+        <v>0.2384</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.7735</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4945</v>
+        <v>0.2384</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4945</v>
+        <v>0.2384</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.7735</v>
       </c>
       <c r="K33" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4945</v>
+        <v>-0.5350999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>84</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5006</v>
+        <v>-0.5505</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2138</v>
+        <v>-0.2352</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.864</v>
+        <v>-0.8748</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5006</v>
+        <v>-0.5505</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2393</v>
+        <v>-0.5505</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.7399</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2393</v>
+        <v>-0.5505</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2393</v>
+        <v>-0.5505</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.7399</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L34" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5005999999999999</v>
+        <v>-0.5505</v>
       </c>
       <c r="N34" t="n">
-        <v>125</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6179</v>
+        <v>-0.6745</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2639</v>
+        <v>-0.2881</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.917</v>
+        <v>-0.9312</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6179</v>
+        <v>-0.6745</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6179</v>
+        <v>-0.6745</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6179</v>
+        <v>-0.6745</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6179</v>
+        <v>-0.6745</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6179</v>
+        <v>-0.6745</v>
       </c>
       <c r="N35" t="n">
         <v>111</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7055</v>
+        <v>-0.758</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3014</v>
+        <v>-0.3238</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9565</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7055</v>
+        <v>-0.758</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7055</v>
+        <v>-0.758</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7055</v>
+        <v>-0.758</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7055</v>
+        <v>-0.758</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7055</v>
+        <v>-0.758</v>
       </c>
       <c r="N36" t="n">
         <v>84</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>salazar</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7138</v>
+        <v>-0.7678</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3049</v>
+        <v>-0.328</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9603</v>
+        <v>-0.9737</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7138</v>
+        <v>-0.7678</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7138</v>
+        <v>-0.7678</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7138</v>
+        <v>-0.7678</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7138</v>
+        <v>-0.7678</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7138</v>
+        <v>-0.7678</v>
       </c>
       <c r="N37" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>salazar</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.7201</v>
+        <v>-0.7765</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3076</v>
+        <v>-0.3317</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9631</v>
+        <v>-0.9777</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.7201</v>
+        <v>-0.7765</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.7201</v>
+        <v>-0.7765</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.7201</v>
+        <v>-0.7765</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7201</v>
+        <v>-0.7765</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7201</v>
+        <v>-0.7765</v>
       </c>
       <c r="N38" t="n">
-        <v>111</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.7619</v>
+        <v>-0.7992</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3255</v>
+        <v>-0.3414</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.982</v>
+        <v>-0.988</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.7619</v>
+        <v>-0.7992</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.7619</v>
+        <v>-0.7992</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.7619</v>
+        <v>-0.7992</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7619</v>
+        <v>-0.7992</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.7619</v>
+        <v>-0.7992</v>
       </c>
       <c r="N39" t="n">
         <v>84</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.9527</v>
+        <v>-0.9372</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.407</v>
+        <v>-0.4003</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0681</v>
+        <v>-1.0508</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.9527</v>
+        <v>-0.9372</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.1549</v>
+        <v>-0.1211</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.7978</v>
+        <v>-0.8161</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.1549</v>
+        <v>-0.1211</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1549</v>
+        <v>-0.1211</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7978</v>
+        <v>-0.8161</v>
       </c>
       <c r="K40" t="n">
         <v>91</v>
@@ -2277,7 +2277,7 @@
         <v>34</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.9527</v>
+        <v>-0.9372</v>
       </c>
       <c r="N40" t="n">
         <v>125</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.2324</v>
+        <v>-1.1277</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5264</v>
+        <v>-0.4817</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1944</v>
+        <v>-1.1376</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.2324</v>
+        <v>-1.1277</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.9463</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.2861</v>
+        <v>-0.1897</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.9463</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9463</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.2861</v>
+        <v>-0.1897</v>
       </c>
       <c r="K41" t="n">
         <v>105</v>
@@ -2323,7 +2323,7 @@
         <v>112</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.2324</v>
+        <v>-1.1277</v>
       </c>
       <c r="N41" t="n">
         <v>217</v>
@@ -2429,10 +2429,10 @@
         <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8339</v>
+        <v>0.7775</v>
       </c>
       <c r="J2" t="n">
-        <v>15.0102</v>
+        <v>13.995</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.76</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2567</v>
+        <v>-0.2743</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.6206</v>
+        <v>-4.9374</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.7</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3142</v>
+        <v>-0.3304</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.6556</v>
+        <v>-5.9472</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3237</v>
+        <v>-0.3396</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.8266</v>
+        <v>-6.1128</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.61</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3991</v>
+        <v>-0.4119</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.1838</v>
+        <v>-7.4142</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.67</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3218</v>
+        <v>1.407</v>
       </c>
       <c r="J7" t="n">
-        <v>23.7924</v>
+        <v>25.326</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.65</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2978</v>
+        <v>1.3729</v>
       </c>
       <c r="J8" t="n">
-        <v>23.3604</v>
+        <v>24.7122</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.45</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0524</v>
+        <v>1.0172</v>
       </c>
       <c r="J9" t="n">
-        <v>18.9432</v>
+        <v>18.3096</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2726</v>
+        <v>0.2895</v>
       </c>
       <c r="J10" t="n">
-        <v>4.9068</v>
+        <v>5.211</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.77</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7791</v>
+        <v>-0.7126</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.0238</v>
+        <v>-12.8268</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.54</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0192</v>
+        <v>0.9716</v>
       </c>
       <c r="J12" t="n">
-        <v>20.384</v>
+        <v>19.432</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4517</v>
+        <v>0.4433</v>
       </c>
       <c r="J13" t="n">
-        <v>9.034000000000001</v>
+        <v>8.866</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.77</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2643</v>
+        <v>-0.2783</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.286</v>
+        <v>-5.566</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.75</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2838</v>
+        <v>-0.2974</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.676</v>
+        <v>-5.948</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.55</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4708</v>
+        <v>-0.4775</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.416</v>
+        <v>-9.550000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>2.2</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J17" t="n">
-        <v>37.362</v>
+        <v>36.906</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1827</v>
+        <v>0.1987</v>
       </c>
       <c r="J18" t="n">
-        <v>3.654</v>
+        <v>3.974</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.06</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1827</v>
+        <v>0.1987</v>
       </c>
       <c r="J19" t="n">
-        <v>3.654</v>
+        <v>3.974</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.9</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.405</v>
+        <v>-0.3812</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.1</v>
+        <v>-7.624</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6506</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.012</v>
+        <v>-12.066</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.53</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8986</v>
+        <v>0.9915</v>
       </c>
       <c r="J22" t="n">
-        <v>16.1748</v>
+        <v>17.847</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.46</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8096</v>
+        <v>0.8958</v>
       </c>
       <c r="J23" t="n">
-        <v>14.5728</v>
+        <v>16.1244</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4062</v>
+        <v>0.4476</v>
       </c>
       <c r="J24" t="n">
-        <v>7.3116</v>
+        <v>8.056800000000001</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.14</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3756</v>
+        <v>0.4051</v>
       </c>
       <c r="J25" t="n">
-        <v>6.7608</v>
+        <v>7.2918</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5232</v>
+        <v>-0.4878</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.4176</v>
+        <v>-8.7804</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.03</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1332</v>
+        <v>0.13</v>
       </c>
       <c r="J27" t="n">
-        <v>2.3976</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.97</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0329</v>
+        <v>-0.0451</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.8118</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.85</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1716</v>
+        <v>-0.1889</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.0888</v>
+        <v>-3.4002</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.77</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2503</v>
+        <v>-0.2674</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.5054</v>
+        <v>-4.8132</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.64</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3745</v>
+        <v>-0.3879</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.741</v>
+        <v>-6.9822</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.38</v>
       </c>
       <c r="I32" t="n">
-        <v>0.718</v>
+        <v>0.7938</v>
       </c>
       <c r="J32" t="n">
-        <v>15.796</v>
+        <v>17.4636</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.28</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5824</v>
+        <v>0.6452</v>
       </c>
       <c r="J33" t="n">
-        <v>12.8128</v>
+        <v>14.1944</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.22</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4985</v>
+        <v>0.5518</v>
       </c>
       <c r="J34" t="n">
-        <v>10.967</v>
+        <v>12.1396</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.15</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3982</v>
+        <v>0.4349</v>
       </c>
       <c r="J35" t="n">
-        <v>8.760400000000001</v>
+        <v>9.5678</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.82</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6157</v>
+        <v>-0.5738</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.5454</v>
+        <v>-12.6236</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.32</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5343</v>
+        <v>0.5914</v>
       </c>
       <c r="J37" t="n">
-        <v>11.7546</v>
+        <v>13.0108</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.2</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4065</v>
+        <v>0.4431</v>
       </c>
       <c r="J38" t="n">
-        <v>8.943</v>
+        <v>9.748200000000001</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.88</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1503</v>
+        <v>-0.1648</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.3066</v>
+        <v>-3.6256</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.82</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2127</v>
+        <v>-0.2276</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.6794</v>
+        <v>-5.0072</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.52</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4964</v>
+        <v>-0.502</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.9208</v>
+        <v>-11.044</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.39</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7627</v>
+        <v>0.836</v>
       </c>
       <c r="J42" t="n">
-        <v>18.3048</v>
+        <v>20.064</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.27</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5936</v>
+        <v>0.6518</v>
       </c>
       <c r="J43" t="n">
-        <v>14.2464</v>
+        <v>15.6432</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.99</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0653</v>
+        <v>-0.0668</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.5672</v>
+        <v>-1.6032</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2744</v>
+        <v>-0.2695</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.5856</v>
+        <v>-6.468</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.68</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9373</v>
+        <v>-0.8618</v>
       </c>
       <c r="J46" t="n">
-        <v>-22.4952</v>
+        <v>-20.6832</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.26</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4616</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>11.0784</v>
+        <v>12.2544</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.08</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2073</v>
+        <v>0.2141</v>
       </c>
       <c r="J48" t="n">
-        <v>4.9752</v>
+        <v>5.1384</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.92</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1106</v>
+        <v>-0.1228</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.6544</v>
+        <v>-2.9472</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.122</v>
+        <v>-0.1346</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.928</v>
+        <v>-3.2304</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.78</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2577</v>
+        <v>-0.2712</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.1848</v>
+        <v>-6.5088</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.29</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6192</v>
+        <v>0.6806</v>
       </c>
       <c r="J52" t="n">
-        <v>14.8608</v>
+        <v>16.3344</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.28</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6049</v>
+        <v>0.6649</v>
       </c>
       <c r="J53" t="n">
-        <v>14.5176</v>
+        <v>15.9576</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3272</v>
+        <v>0.3288</v>
       </c>
       <c r="J54" t="n">
-        <v>7.8528</v>
+        <v>7.8912</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.07</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2441</v>
+        <v>0.2487</v>
       </c>
       <c r="J55" t="n">
-        <v>5.8584</v>
+        <v>5.9688</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.58</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.1787</v>
+        <v>-1.0693</v>
       </c>
       <c r="J56" t="n">
-        <v>-28.2888</v>
+        <v>-25.6632</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.45</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6544</v>
+        <v>0.7284</v>
       </c>
       <c r="J57" t="n">
-        <v>15.7056</v>
+        <v>17.4816</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.13</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3098</v>
+        <v>0.3125</v>
       </c>
       <c r="J58" t="n">
-        <v>7.4352</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1102</v>
+        <v>-0.1225</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.6448</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.76</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2769</v>
+        <v>-0.2901</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.6456</v>
+        <v>-6.9624</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.67</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3629</v>
+        <v>-0.3738</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.7096</v>
+        <v>-8.9712</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.18</v>
       </c>
       <c r="I62" t="n">
-        <v>0.318</v>
+        <v>0.3216</v>
       </c>
       <c r="J62" t="n">
-        <v>9.222</v>
+        <v>9.3264</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0056</v>
+        <v>0.0041</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1624</v>
+        <v>0.1189</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.98</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0327</v>
+        <v>-0.0402</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.9483</v>
+        <v>-1.1658</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.91</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1181</v>
+        <v>-0.1316</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.4249</v>
+        <v>-3.8164</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.7</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3309</v>
+        <v>-0.3435</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.5961</v>
+        <v>-9.961499999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.41</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4564</v>
+        <v>0.5175</v>
       </c>
       <c r="J67" t="n">
-        <v>13.2356</v>
+        <v>15.0075</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.23</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3261</v>
+        <v>0.3424</v>
       </c>
       <c r="J68" t="n">
-        <v>9.456899999999999</v>
+        <v>9.929600000000001</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.15</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2274</v>
+        <v>0.2434</v>
       </c>
       <c r="J69" t="n">
-        <v>6.5946</v>
+        <v>7.0586</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1122</v>
+        <v>-0.1209</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.2538</v>
+        <v>-3.5061</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.85</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2005</v>
+        <v>-0.2113</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.8145</v>
+        <v>-6.1277</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.85</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3671</v>
+        <v>1.4745</v>
       </c>
       <c r="J72" t="n">
-        <v>32.8104</v>
+        <v>35.388</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.98</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1056</v>
+        <v>-0.1077</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.5344</v>
+        <v>-2.5848</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.85</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.5032</v>
+        <v>-0.4792</v>
       </c>
       <c r="J74" t="n">
-        <v>-12.0768</v>
+        <v>-11.5008</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.6098</v>
+        <v>-0.5746</v>
       </c>
       <c r="J75" t="n">
-        <v>-14.6352</v>
+        <v>-13.7904</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.76</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7383999999999999</v>
+        <v>-0.6884</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.7216</v>
+        <v>-16.5216</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.28</v>
       </c>
       <c r="I77" t="n">
-        <v>0.482</v>
+        <v>0.5341</v>
       </c>
       <c r="J77" t="n">
-        <v>11.568</v>
+        <v>12.8184</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.16</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3531</v>
+        <v>0.3658</v>
       </c>
       <c r="J78" t="n">
-        <v>8.474399999999999</v>
+        <v>8.779199999999999</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.96</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0625</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.5</v>
+        <v>-1.7256</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.8</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2381</v>
+        <v>-0.2517</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.7144</v>
+        <v>-6.0408</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2776</v>
+        <v>-0.2907</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.6624</v>
+        <v>-6.9768</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.32</v>
       </c>
       <c r="I82" t="n">
-        <v>1.8148</v>
+        <v>1.9517</v>
       </c>
       <c r="J82" t="n">
-        <v>34.4812</v>
+        <v>37.0823</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2818</v>
+        <v>0.2959</v>
       </c>
       <c r="J83" t="n">
-        <v>5.3542</v>
+        <v>5.6221</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.04</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0979</v>
+        <v>0.1229</v>
       </c>
       <c r="J84" t="n">
-        <v>1.8601</v>
+        <v>2.3351</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.01</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.0151</v>
+        <v>0.0113</v>
       </c>
       <c r="J85" t="n">
-        <v>-0.2869</v>
+        <v>0.2147</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2034</v>
+        <v>-0.1865</v>
       </c>
       <c r="J86" t="n">
-        <v>-3.8646</v>
+        <v>-3.5435</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.41</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6446</v>
+        <v>0.712</v>
       </c>
       <c r="J87" t="n">
-        <v>12.2474</v>
+        <v>13.528</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.86</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1652</v>
+        <v>-0.1814</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.1388</v>
+        <v>-3.4466</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.75</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.275</v>
+        <v>-0.2906</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.225</v>
+        <v>-5.5214</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.73</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2944</v>
+        <v>-0.3095</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.5936</v>
+        <v>-5.8805</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.71</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3136</v>
+        <v>-0.3281</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.9584</v>
+        <v>-6.2339</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.83</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.1407</v>
+        <v>-0.1694</v>
       </c>
       <c r="J92" t="n">
-        <v>-1.9698</v>
+        <v>-2.3716</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.66</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.3208</v>
+        <v>-0.3428</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.4912</v>
+        <v>-4.7992</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.63</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3488</v>
+        <v>-0.3697</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.8832</v>
+        <v>-5.1758</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.62</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3578</v>
+        <v>-0.3783</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.0092</v>
+        <v>-5.2962</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.31</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6479</v>
+        <v>-0.6489</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.070600000000001</v>
+        <v>-9.0846</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>2.01</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3734</v>
+        <v>1.5087</v>
       </c>
       <c r="J97" t="n">
-        <v>19.2276</v>
+        <v>21.1218</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.72</v>
       </c>
       <c r="I98" t="n">
-        <v>1.0564</v>
+        <v>1.1732</v>
       </c>
       <c r="J98" t="n">
-        <v>14.7896</v>
+        <v>16.4248</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.61</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9356</v>
+        <v>1.0432</v>
       </c>
       <c r="J99" t="n">
-        <v>13.0984</v>
+        <v>14.6048</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.46</v>
       </c>
       <c r="I100" t="n">
-        <v>0.76</v>
+        <v>0.8527</v>
       </c>
       <c r="J100" t="n">
-        <v>10.64</v>
+        <v>11.9378</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.38</v>
       </c>
       <c r="I101" t="n">
-        <v>0.6601</v>
+        <v>0.7437</v>
       </c>
       <c r="J101" t="n">
-        <v>9.241400000000001</v>
+        <v>10.4118</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.22</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4599</v>
+        <v>0.4994</v>
       </c>
       <c r="J102" t="n">
-        <v>9.198</v>
+        <v>9.988</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.87</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1499</v>
+        <v>-0.1672</v>
       </c>
       <c r="J103" t="n">
-        <v>-2.998</v>
+        <v>-3.344</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.87</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1499</v>
+        <v>-0.1672</v>
       </c>
       <c r="J104" t="n">
-        <v>-2.998</v>
+        <v>-3.344</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.63</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3817</v>
+        <v>-0.3951</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.634</v>
+        <v>-7.902</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.59</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4191</v>
+        <v>-0.4307</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.382</v>
+        <v>-8.614000000000001</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.77</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1931</v>
+        <v>1.304</v>
       </c>
       <c r="J107" t="n">
-        <v>23.862</v>
+        <v>26.08</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.26</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5457</v>
+        <v>0.6067</v>
       </c>
       <c r="J108" t="n">
-        <v>10.914</v>
+        <v>12.134</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.26</v>
       </c>
       <c r="I109" t="n">
-        <v>0.5457</v>
+        <v>0.6067</v>
       </c>
       <c r="J109" t="n">
-        <v>10.914</v>
+        <v>12.134</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.97</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.191</v>
+        <v>-0.1778</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.82</v>
+        <v>-3.556</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.92</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3533</v>
+        <v>-0.3318</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.066</v>
+        <v>-6.636</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2414</v>
+        <v>0.241</v>
       </c>
       <c r="J112" t="n">
-        <v>4.828</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1744</v>
+        <v>0.1754</v>
       </c>
       <c r="J113" t="n">
-        <v>3.488</v>
+        <v>3.508</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.78</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2413</v>
+        <v>-0.2584</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.826</v>
+        <v>-5.168</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.72</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2995</v>
+        <v>-0.3153</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.99</v>
+        <v>-6.306</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.61</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4034</v>
+        <v>-0.4153</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.068</v>
+        <v>-8.305999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.47</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6042</v>
+        <v>0.6047</v>
       </c>
       <c r="J117" t="n">
-        <v>12.084</v>
+        <v>12.094</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.44</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5704</v>
+        <v>0.5732</v>
       </c>
       <c r="J118" t="n">
-        <v>11.408</v>
+        <v>11.464</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.08</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1305</v>
+        <v>0.1463</v>
       </c>
       <c r="J119" t="n">
-        <v>2.61</v>
+        <v>2.926</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.98</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0495</v>
+        <v>-0.0532</v>
       </c>
       <c r="J120" t="n">
-        <v>-0.99</v>
+        <v>-1.064</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.72</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3315</v>
+        <v>-0.3404</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.63</v>
+        <v>-6.808</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.81</v>
       </c>
       <c r="I122" t="n">
-        <v>1.5329</v>
+        <v>1.5179</v>
       </c>
       <c r="J122" t="n">
-        <v>35.2567</v>
+        <v>34.9117</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.24</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6576</v>
+        <v>0.632</v>
       </c>
       <c r="J123" t="n">
-        <v>15.1248</v>
+        <v>14.536</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.24</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6576</v>
+        <v>0.632</v>
       </c>
       <c r="J124" t="n">
-        <v>15.1248</v>
+        <v>14.536</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.85</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5392</v>
+        <v>-0.5044</v>
       </c>
       <c r="J125" t="n">
-        <v>-12.4016</v>
+        <v>-11.6012</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7225</v>
+        <v>-0.6681</v>
       </c>
       <c r="J126" t="n">
-        <v>-16.6175</v>
+        <v>-15.3663</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>2.08</v>
       </c>
       <c r="I127" t="n">
-        <v>1.4743</v>
+        <v>1.4771</v>
       </c>
       <c r="J127" t="n">
-        <v>33.9089</v>
+        <v>33.9733</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.1</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2319</v>
+        <v>0.2421</v>
       </c>
       <c r="J128" t="n">
-        <v>5.3337</v>
+        <v>5.5683</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.92</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1192</v>
+        <v>-0.1295</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.7416</v>
+        <v>-2.9785</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.89</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.153</v>
+        <v>-0.1643</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.519</v>
+        <v>-3.7789</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.36</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6468</v>
+        <v>-0.642</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.8764</v>
+        <v>-14.766</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.43</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0643</v>
+        <v>1.0145</v>
       </c>
       <c r="J132" t="n">
-        <v>30.8647</v>
+        <v>29.4205</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.12</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3697</v>
+        <v>0.3693</v>
       </c>
       <c r="J133" t="n">
-        <v>10.7213</v>
+        <v>10.7097</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.287</v>
+        <v>0.2928</v>
       </c>
       <c r="J134" t="n">
-        <v>8.323</v>
+        <v>8.491199999999999</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.07</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2284</v>
+        <v>0.238</v>
       </c>
       <c r="J135" t="n">
-        <v>6.6236</v>
+        <v>6.902</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.01</v>
       </c>
       <c r="I136" t="n">
-        <v>0.0205</v>
+        <v>0.0362</v>
       </c>
       <c r="J136" t="n">
-        <v>0.5945</v>
+        <v>1.0498</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.23</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4926</v>
+        <v>0.4837</v>
       </c>
       <c r="J137" t="n">
-        <v>14.2854</v>
+        <v>14.0273</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4381</v>
+        <v>0.4333</v>
       </c>
       <c r="J138" t="n">
-        <v>12.7049</v>
+        <v>12.5657</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1157</v>
+        <v>0.1243</v>
       </c>
       <c r="J139" t="n">
-        <v>3.3553</v>
+        <v>3.6047</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1882</v>
+        <v>-0.2017</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.4578</v>
+        <v>-5.8493</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3459</v>
+        <v>-0.357</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.0311</v>
+        <v>-10.353</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.43</v>
       </c>
       <c r="I142" t="n">
-        <v>0.891</v>
+        <v>0.8354</v>
       </c>
       <c r="J142" t="n">
-        <v>17.82</v>
+        <v>16.708</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.83</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1967</v>
+        <v>-0.213</v>
       </c>
       <c r="J143" t="n">
-        <v>-3.934</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2169</v>
+        <v>-0.233</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.338</v>
+        <v>-4.66</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.79</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2368</v>
+        <v>-0.2528</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.736</v>
+        <v>-5.056</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.64</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3808</v>
+        <v>-0.3928</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.616</v>
+        <v>-7.856</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.5</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1367</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
-        <v>22.734</v>
+        <v>22</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.36</v>
       </c>
       <c r="I148" t="n">
-        <v>0.923</v>
+        <v>0.8681</v>
       </c>
       <c r="J148" t="n">
-        <v>18.46</v>
+        <v>17.362</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.25</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6733</v>
+        <v>0.6475</v>
       </c>
       <c r="J149" t="n">
-        <v>13.466</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.08</v>
       </c>
       <c r="I150" t="n">
-        <v>0.24</v>
+        <v>0.2533</v>
       </c>
       <c r="J150" t="n">
-        <v>4.8</v>
+        <v>5.066</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.91</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3792</v>
+        <v>-0.3566</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.584</v>
+        <v>-7.132</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4706</v>
+        <v>0.4536</v>
       </c>
       <c r="J152" t="n">
-        <v>8.470800000000001</v>
+        <v>8.1648</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.92</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0994</v>
+        <v>-0.1143</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.7892</v>
+        <v>-2.0574</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.83</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1935</v>
+        <v>-0.2105</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.483</v>
+        <v>-3.789</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2135</v>
+        <v>-0.2304</v>
       </c>
       <c r="J155" t="n">
-        <v>-3.843</v>
+        <v>-4.1472</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4052</v>
+        <v>-0.4167</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.2936</v>
+        <v>-7.5006</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>2.06</v>
       </c>
       <c r="I157" t="n">
-        <v>1.7778</v>
+        <v>1.7806</v>
       </c>
       <c r="J157" t="n">
-        <v>32.0004</v>
+        <v>32.0508</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.86</v>
       </c>
       <c r="I158" t="n">
-        <v>1.5468</v>
+        <v>1.5396</v>
       </c>
       <c r="J158" t="n">
-        <v>27.8424</v>
+        <v>27.7128</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.4</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9245</v>
       </c>
       <c r="J159" t="n">
-        <v>17.5734</v>
+        <v>16.641</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.74</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.8534</v>
+        <v>-0.7782</v>
       </c>
       <c r="J160" t="n">
-        <v>-15.3612</v>
+        <v>-14.0076</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.58</v>
       </c>
       <c r="I161" t="n">
-        <v>-1.2301</v>
+        <v>-1.1057</v>
       </c>
       <c r="J161" t="n">
-        <v>-22.1418</v>
+        <v>-19.9026</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.32</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.6459</v>
       </c>
       <c r="J162" t="n">
-        <v>16.1976</v>
+        <v>15.5016</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.09</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2405</v>
+        <v>0.2434</v>
       </c>
       <c r="J163" t="n">
-        <v>5.772</v>
+        <v>5.8416</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.02</v>
       </c>
       <c r="I164" t="n">
-        <v>0.077</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="J164" t="n">
-        <v>1.848</v>
+        <v>1.9488</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.71</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3204</v>
+        <v>-0.3335</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.6896</v>
+        <v>-8.004</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.59</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4326</v>
+        <v>-0.4414</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.3824</v>
+        <v>-10.5936</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.8</v>
       </c>
       <c r="I167" t="n">
-        <v>1.5398</v>
+        <v>1.5221</v>
       </c>
       <c r="J167" t="n">
-        <v>36.9552</v>
+        <v>36.5304</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.12</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3715</v>
+        <v>0.3705</v>
       </c>
       <c r="J168" t="n">
-        <v>8.916</v>
+        <v>8.891999999999999</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0641</v>
+        <v>0.0793</v>
       </c>
       <c r="J169" t="n">
-        <v>1.5384</v>
+        <v>1.9032</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.93</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2968</v>
+        <v>-0.2851</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.1232</v>
+        <v>-6.8424</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6587</v>
+        <v>-0.6138</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.8088</v>
+        <v>-14.7312</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.15</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4142</v>
+        <v>0.3971</v>
       </c>
       <c r="J172" t="n">
-        <v>8.6982</v>
+        <v>8.3391</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0859</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="J173" t="n">
-        <v>1.8039</v>
+        <v>1.6443</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.82</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1986</v>
+        <v>-0.2168</v>
       </c>
       <c r="J174" t="n">
-        <v>-4.1706</v>
+        <v>-4.5528</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.58</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.427</v>
+        <v>-0.4385</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.967000000000001</v>
+        <v>-9.208500000000001</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.57</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4363</v>
+        <v>-0.4473</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.1623</v>
+        <v>-9.3933</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.64</v>
       </c>
       <c r="I177" t="n">
-        <v>1.3125</v>
+        <v>1.2876</v>
       </c>
       <c r="J177" t="n">
-        <v>27.5625</v>
+        <v>27.0396</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.47</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0984</v>
+        <v>1.0582</v>
       </c>
       <c r="J178" t="n">
-        <v>23.0664</v>
+        <v>22.2222</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.05</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1474</v>
+        <v>0.1661</v>
       </c>
       <c r="J179" t="n">
-        <v>3.0954</v>
+        <v>3.4881</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.98</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1497</v>
+        <v>-0.1384</v>
       </c>
       <c r="J180" t="n">
-        <v>-3.1437</v>
+        <v>-2.9064</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.222</v>
+        <v>-0.2089</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.662</v>
+        <v>-4.3869</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.19</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5034</v>
       </c>
       <c r="J182" t="n">
-        <v>9.1426</v>
+        <v>8.5578</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.74</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2672</v>
+        <v>-0.2865</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.5424</v>
+        <v>-4.8705</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.73</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2765</v>
+        <v>-0.2956</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.7005</v>
+        <v>-5.0252</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.66</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3422</v>
+        <v>-0.3592</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.8174</v>
+        <v>-6.1064</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.47</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5194</v>
+        <v>-0.527</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.829800000000001</v>
+        <v>-8.959</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.64</v>
       </c>
       <c r="I187" t="n">
-        <v>1.2727</v>
+        <v>1.2525</v>
       </c>
       <c r="J187" t="n">
-        <v>21.6359</v>
+        <v>21.2925</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.53</v>
       </c>
       <c r="I188" t="n">
-        <v>1.1412</v>
+        <v>1.1114</v>
       </c>
       <c r="J188" t="n">
-        <v>19.4004</v>
+        <v>18.8938</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.49</v>
       </c>
       <c r="I189" t="n">
-        <v>1.0928</v>
+        <v>1.0585</v>
       </c>
       <c r="J189" t="n">
-        <v>18.5776</v>
+        <v>17.9945</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.47</v>
       </c>
       <c r="I190" t="n">
-        <v>1.0685</v>
+        <v>1.0303</v>
       </c>
       <c r="J190" t="n">
-        <v>18.1645</v>
+        <v>17.5151</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.84</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6122</v>
+        <v>-0.5612</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.4074</v>
+        <v>-9.5404</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.35</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4727</v>
+        <v>0.4802</v>
       </c>
       <c r="J192" t="n">
-        <v>11.3448</v>
+        <v>11.5248</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.16</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2405</v>
+        <v>0.2564</v>
       </c>
       <c r="J193" t="n">
-        <v>5.772</v>
+        <v>6.1536</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.14</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2146</v>
+        <v>0.2307</v>
       </c>
       <c r="J194" t="n">
-        <v>5.1504</v>
+        <v>5.5368</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.12</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1883</v>
+        <v>0.2043</v>
       </c>
       <c r="J195" t="n">
-        <v>4.5192</v>
+        <v>4.9032</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.79</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2612</v>
+        <v>-0.2719</v>
       </c>
       <c r="J196" t="n">
-        <v>-6.2688</v>
+        <v>-6.5256</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.15</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2671</v>
+        <v>0.2735</v>
       </c>
       <c r="J197" t="n">
-        <v>6.4104</v>
+        <v>6.564</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0305</v>
+        <v>0.0351</v>
       </c>
       <c r="J198" t="n">
-        <v>0.732</v>
+        <v>0.8424</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.99</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0198</v>
+        <v>-0.0247</v>
       </c>
       <c r="J199" t="n">
-        <v>-0.4752</v>
+        <v>-0.5928</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.91</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1215</v>
+        <v>-0.1342</v>
       </c>
       <c r="J200" t="n">
-        <v>-2.916</v>
+        <v>-3.2208</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.87</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1653</v>
+        <v>-0.1789</v>
       </c>
       <c r="J201" t="n">
-        <v>-3.9672</v>
+        <v>-4.2936</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.27</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5522</v>
+        <v>0.5404</v>
       </c>
       <c r="J202" t="n">
-        <v>13.2528</v>
+        <v>12.9696</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.21</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4459</v>
+        <v>0.4426</v>
       </c>
       <c r="J203" t="n">
-        <v>10.7016</v>
+        <v>10.6224</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.97</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.0535</v>
+        <v>-0.0608</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.284</v>
+        <v>-1.4592</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.88</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1602</v>
+        <v>-0.1725</v>
       </c>
       <c r="J205" t="n">
-        <v>-3.8448</v>
+        <v>-4.14</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.85</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1921</v>
+        <v>-0.2047</v>
       </c>
       <c r="J206" t="n">
-        <v>-4.6104</v>
+        <v>-4.9128</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.26</v>
       </c>
       <c r="I207" t="n">
-        <v>0.7417</v>
+        <v>0.6995</v>
       </c>
       <c r="J207" t="n">
-        <v>17.8008</v>
+        <v>16.788</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.11</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3556</v>
+        <v>0.3531</v>
       </c>
       <c r="J208" t="n">
-        <v>8.5344</v>
+        <v>8.474399999999999</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.1</v>
       </c>
       <c r="I209" t="n">
-        <v>0.3279</v>
+        <v>0.3276</v>
       </c>
       <c r="J209" t="n">
-        <v>7.8696</v>
+        <v>7.8624</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.08</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2716</v>
+        <v>0.275</v>
       </c>
       <c r="J210" t="n">
-        <v>6.5184</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.616</v>
+        <v>-0.5789</v>
       </c>
       <c r="J211" t="n">
-        <v>-14.784</v>
+        <v>-13.8936</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.36</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7678</v>
+        <v>0.7258</v>
       </c>
       <c r="J212" t="n">
-        <v>17.6594</v>
+        <v>16.6934</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.97</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0408</v>
+        <v>-0.0512</v>
       </c>
       <c r="J213" t="n">
-        <v>-0.9384</v>
+        <v>-1.1776</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.88</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1454</v>
+        <v>-0.161</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.3442</v>
+        <v>-3.703</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.75</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2763</v>
+        <v>-0.2916</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.3549</v>
+        <v>-6.7068</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.55</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4642</v>
+        <v>-0.4723</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.6766</v>
+        <v>-10.8629</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.52</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1985</v>
+        <v>1.1595</v>
       </c>
       <c r="J217" t="n">
-        <v>27.5655</v>
+        <v>26.6685</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.17</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5093</v>
+        <v>0.4943</v>
       </c>
       <c r="J218" t="n">
-        <v>11.7139</v>
+        <v>11.3689</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.17</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5093</v>
+        <v>0.4943</v>
       </c>
       <c r="J219" t="n">
-        <v>11.7139</v>
+        <v>11.3689</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.89</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4038</v>
+        <v>-0.3866</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.2874</v>
+        <v>-8.8918</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.71</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.8744</v>
+        <v>-0.8055</v>
       </c>
       <c r="J221" t="n">
-        <v>-20.1112</v>
+        <v>-18.5265</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.15</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3716</v>
+        <v>0.3657</v>
       </c>
       <c r="J222" t="n">
-        <v>8.9184</v>
+        <v>8.7768</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1</v>
       </c>
       <c r="I223" t="n">
-        <v>0.0153</v>
+        <v>0.0109</v>
       </c>
       <c r="J223" t="n">
-        <v>0.3672</v>
+        <v>0.2616</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.89</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1366</v>
+        <v>-0.1515</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.2784</v>
+        <v>-3.636</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.82</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2093</v>
+        <v>-0.2249</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.0232</v>
+        <v>-5.3976</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.74</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2883</v>
+        <v>-0.3029</v>
       </c>
       <c r="J226" t="n">
-        <v>-6.9192</v>
+        <v>-7.2696</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.67</v>
       </c>
       <c r="I227" t="n">
-        <v>1.383</v>
+        <v>1.3566</v>
       </c>
       <c r="J227" t="n">
-        <v>33.192</v>
+        <v>32.5584</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.26</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7246</v>
+        <v>0.6876</v>
       </c>
       <c r="J228" t="n">
-        <v>17.3904</v>
+        <v>16.5024</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2613</v>
+        <v>-0.2528</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.2712</v>
+        <v>-6.0672</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.86</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4948</v>
+        <v>-0.4678</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.8752</v>
+        <v>-11.2272</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.86</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4948</v>
+        <v>-0.4678</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.8752</v>
+        <v>-11.2272</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.85</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4929</v>
+        <v>1.49</v>
       </c>
       <c r="J232" t="n">
-        <v>23.8864</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.54</v>
       </c>
       <c r="I233" t="n">
-        <v>1.1388</v>
+        <v>1.112</v>
       </c>
       <c r="J233" t="n">
-        <v>18.2208</v>
+        <v>17.792</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.49</v>
       </c>
       <c r="I234" t="n">
-        <v>1.0817</v>
+        <v>1.0485</v>
       </c>
       <c r="J234" t="n">
-        <v>17.3072</v>
+        <v>16.776</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.41</v>
       </c>
       <c r="I235" t="n">
-        <v>0.9687</v>
+        <v>0.9224</v>
       </c>
       <c r="J235" t="n">
-        <v>15.4992</v>
+        <v>14.7584</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.28</v>
       </c>
       <c r="I236" t="n">
-        <v>0.6875</v>
+        <v>0.6711</v>
       </c>
       <c r="J236" t="n">
-        <v>11</v>
+        <v>10.7376</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.65</v>
       </c>
       <c r="I237" t="n">
-        <v>1.1861</v>
+        <v>1.1499</v>
       </c>
       <c r="J237" t="n">
-        <v>18.9776</v>
+        <v>18.3984</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.99</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0022</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="J238" t="n">
-        <v>0.0352</v>
+        <v>-0.1344</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.83</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1898</v>
+        <v>-0.2077</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.0368</v>
+        <v>-3.3232</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.45</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5476</v>
+        <v>-0.552</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.7616</v>
+        <v>-8.832000000000001</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.26</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7181</v>
+        <v>-0.7104</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.4896</v>
+        <v>-11.3664</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.31</v>
       </c>
       <c r="I242" t="n">
-        <v>0.8275</v>
+        <v>0.7808</v>
       </c>
       <c r="J242" t="n">
-        <v>24.825</v>
+        <v>23.424</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.31</v>
       </c>
       <c r="I243" t="n">
-        <v>0.8275</v>
+        <v>0.7808</v>
       </c>
       <c r="J243" t="n">
-        <v>24.825</v>
+        <v>23.424</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.25</v>
       </c>
       <c r="I244" t="n">
-        <v>0.6865</v>
+        <v>0.6566</v>
       </c>
       <c r="J244" t="n">
-        <v>20.595</v>
+        <v>19.698</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.03</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0935</v>
+        <v>0.1104</v>
       </c>
       <c r="J245" t="n">
-        <v>2.805</v>
+        <v>3.312</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.92</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3352</v>
+        <v>-0.3191</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.056</v>
+        <v>-9.573</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.32</v>
       </c>
       <c r="I247" t="n">
-        <v>0.655</v>
+        <v>0.6312</v>
       </c>
       <c r="J247" t="n">
-        <v>19.65</v>
+        <v>18.936</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.15</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3473</v>
+        <v>0.3479</v>
       </c>
       <c r="J248" t="n">
-        <v>10.419</v>
+        <v>10.437</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.9</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1334</v>
+        <v>-0.1463</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.002</v>
+        <v>-4.389</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.83</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2077</v>
+        <v>-0.2215</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.231</v>
+        <v>-6.645</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.76</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2776</v>
+        <v>-0.2907</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.327999999999999</v>
+        <v>-8.721</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.39</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0291</v>
+        <v>0.9674</v>
       </c>
       <c r="J252" t="n">
-        <v>21.6111</v>
+        <v>20.3154</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.21</v>
       </c>
       <c r="I253" t="n">
-        <v>0.619</v>
+        <v>0.5908</v>
       </c>
       <c r="J253" t="n">
-        <v>12.999</v>
+        <v>12.4068</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.18</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5426</v>
+        <v>0.5226</v>
       </c>
       <c r="J254" t="n">
-        <v>11.3946</v>
+        <v>10.9746</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.89</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3971</v>
+        <v>-0.3819</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.3391</v>
+        <v>-8.0199</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.67</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.9657</v>
+        <v>-0.8858</v>
       </c>
       <c r="J256" t="n">
-        <v>-20.2797</v>
+        <v>-18.6018</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.33</v>
       </c>
       <c r="I257" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6354</v>
       </c>
       <c r="J257" t="n">
-        <v>13.7928</v>
+        <v>13.3434</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.05</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1337</v>
+        <v>0.1439</v>
       </c>
       <c r="J258" t="n">
-        <v>2.8077</v>
+        <v>3.0219</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.03</v>
       </c>
       <c r="I259" t="n">
-        <v>0.0876</v>
+        <v>0.097</v>
       </c>
       <c r="J259" t="n">
-        <v>1.8396</v>
+        <v>2.037</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.95</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.0886</v>
       </c>
       <c r="J260" t="n">
-        <v>-1.6632</v>
+        <v>-1.8606</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.8</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2427</v>
+        <v>-0.2553</v>
       </c>
       <c r="J261" t="n">
-        <v>-5.0967</v>
+        <v>-5.3613</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.53</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1535</v>
+        <v>1.1221</v>
       </c>
       <c r="J262" t="n">
-        <v>21.9165</v>
+        <v>21.3199</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.52</v>
       </c>
       <c r="I263" t="n">
-        <v>1.1411</v>
+        <v>1.1089</v>
       </c>
       <c r="J263" t="n">
-        <v>21.6809</v>
+        <v>21.0691</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.32</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8136</v>
+        <v>0.7755</v>
       </c>
       <c r="J264" t="n">
-        <v>15.4584</v>
+        <v>14.7345</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.32</v>
       </c>
       <c r="I265" t="n">
-        <v>0.8136</v>
+        <v>0.7755</v>
       </c>
       <c r="J265" t="n">
-        <v>15.4584</v>
+        <v>14.7345</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.91</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4024</v>
+        <v>-0.373</v>
       </c>
       <c r="J266" t="n">
-        <v>-7.6456</v>
+        <v>-7.087</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.17</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4278</v>
+        <v>0.4147</v>
       </c>
       <c r="J267" t="n">
-        <v>8.1282</v>
+        <v>7.8793</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0767</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J268" t="n">
-        <v>-1.4573</v>
+        <v>-1.7157</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.84</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1843</v>
+        <v>-0.201</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.5017</v>
+        <v>-3.819</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.77</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.254</v>
+        <v>-0.2702</v>
       </c>
       <c r="J270" t="n">
-        <v>-4.826</v>
+        <v>-5.1338</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.68</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3406</v>
+        <v>-0.3545</v>
       </c>
       <c r="J271" t="n">
-        <v>-6.4714</v>
+        <v>-6.7355</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.16</v>
       </c>
       <c r="I272" t="n">
-        <v>1.8338</v>
+        <v>1.8677</v>
       </c>
       <c r="J272" t="n">
-        <v>31.1746</v>
+        <v>31.7509</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.58</v>
       </c>
       <c r="I273" t="n">
-        <v>1.1951</v>
+        <v>1.1706</v>
       </c>
       <c r="J273" t="n">
-        <v>20.3167</v>
+        <v>19.9002</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.27</v>
       </c>
       <c r="I274" t="n">
-        <v>0.6805</v>
+        <v>0.6619</v>
       </c>
       <c r="J274" t="n">
-        <v>11.5685</v>
+        <v>11.2523</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.14</v>
       </c>
       <c r="I275" t="n">
-        <v>0.3592</v>
+        <v>0.3738</v>
       </c>
       <c r="J275" t="n">
-        <v>6.1064</v>
+        <v>6.3546</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.02</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.0061</v>
+        <v>0.0301</v>
       </c>
       <c r="J276" t="n">
-        <v>-0.1037</v>
+        <v>0.5117</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.16</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4516</v>
+        <v>0.4285</v>
       </c>
       <c r="J277" t="n">
-        <v>7.6772</v>
+        <v>7.2845</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.01</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0988</v>
+        <v>0.0878</v>
       </c>
       <c r="J278" t="n">
-        <v>1.6796</v>
+        <v>1.4926</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.71</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3005</v>
+        <v>-0.3179</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.1085</v>
+        <v>-5.4043</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.68</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3289</v>
+        <v>-0.3454</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.5913</v>
+        <v>-5.8718</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.42</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5702</v>
+        <v>-0.5738</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.6934</v>
+        <v>-9.7546</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.62</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3105</v>
+        <v>1.2815</v>
       </c>
       <c r="J282" t="n">
-        <v>38.0045</v>
+        <v>37.1635</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.59</v>
       </c>
       <c r="I283" t="n">
-        <v>1.2722</v>
+        <v>1.2409</v>
       </c>
       <c r="J283" t="n">
-        <v>36.8938</v>
+        <v>35.9861</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.85</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.529</v>
+        <v>-0.4973</v>
       </c>
       <c r="J284" t="n">
-        <v>-15.341</v>
+        <v>-14.4217</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.84</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.556</v>
+        <v>-0.5215</v>
       </c>
       <c r="J285" t="n">
-        <v>-16.124</v>
+        <v>-15.1235</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.82</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6091</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="J286" t="n">
-        <v>-17.6639</v>
+        <v>-16.5039</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.13</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3226</v>
+        <v>0.3216</v>
       </c>
       <c r="J287" t="n">
-        <v>9.355399999999999</v>
+        <v>9.3264</v>
       </c>
     </row>
     <row r="288">
@@ -13909,10 +13909,10 @@
         <v>0.95</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.0827</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.0735</v>
+        <v>-2.3983</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.86</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1712</v>
+        <v>-0.1861</v>
       </c>
       <c r="J290" t="n">
-        <v>-4.9648</v>
+        <v>-5.3969</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.67</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3583</v>
+        <v>-0.3702</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.3907</v>
+        <v>-10.7358</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6976/event_6976_evp_summary.xlsx
+++ b/database/event/6976/event_6976_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.3046</v>
+        <v>7.6714</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1203</v>
+        <v>3.277</v>
       </c>
       <c r="D2" t="n">
-        <v>2.701</v>
+        <v>2.8128</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3046</v>
+        <v>7.6714</v>
       </c>
       <c r="F2" t="n">
         <v>2.267</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.2607</v>
+        <v>4.3016</v>
       </c>
       <c r="C3" t="n">
-        <v>1.82</v>
+        <v>1.8375</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3154</v>
+        <v>1.3076</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2607</v>
+        <v>4.3016</v>
       </c>
       <c r="F3" t="n">
         <v>3.4468</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.9638</v>
+        <v>3.8431</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6932</v>
+        <v>1.6417</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1802</v>
+        <v>1.1028</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9638</v>
+        <v>3.8431</v>
       </c>
       <c r="F4" t="n">
         <v>3.3849</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.5907</v>
+        <v>3.6983</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5338</v>
+        <v>1.5798</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0104</v>
+        <v>1.0381</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5907</v>
+        <v>3.6983</v>
       </c>
       <c r="F5" t="n">
         <v>0.7968</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.2965</v>
+        <v>3.4892</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4082</v>
+        <v>1.4905</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8764</v>
+        <v>0.9447</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2965</v>
+        <v>3.4892</v>
       </c>
       <c r="F6" t="n">
         <v>2.3133</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2758</v>
+        <v>3.393</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3993</v>
+        <v>1.4494</v>
       </c>
       <c r="D7" t="n">
-        <v>0.867</v>
+        <v>0.9018</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2758</v>
+        <v>3.393</v>
       </c>
       <c r="F7" t="n">
         <v>1.1012</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1232</v>
+        <v>3.0815</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3341</v>
+        <v>1.3163</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7975</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1232</v>
+        <v>3.0815</v>
       </c>
       <c r="F8" t="n">
         <v>2.6559</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9782</v>
+        <v>3.0037</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2722</v>
+        <v>1.2831</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7315</v>
+        <v>0.7279</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9782</v>
+        <v>3.0037</v>
       </c>
       <c r="F9" t="n">
         <v>2.2893</v>
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9034</v>
+        <v>2.9899</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2402</v>
+        <v>1.2772</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6975</v>
+        <v>0.7217</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9034</v>
+        <v>2.9899</v>
       </c>
       <c r="F10" t="n">
         <v>2.6826</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7423</v>
+        <v>2.7492</v>
       </c>
       <c r="C11" t="n">
-        <v>1.1714</v>
+        <v>1.1744</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6241</v>
+        <v>0.6142</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7423</v>
+        <v>2.7492</v>
       </c>
       <c r="F11" t="n">
         <v>2.673</v>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6659</v>
+        <v>2.7414</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1388</v>
+        <v>1.171</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5894</v>
+        <v>0.6107</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6659</v>
+        <v>2.7414</v>
       </c>
       <c r="F12" t="n">
         <v>0.9802999999999999</v>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5055</v>
+        <v>2.5848</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0703</v>
+        <v>1.1041</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5164</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5055</v>
+        <v>2.5848</v>
       </c>
       <c r="F13" t="n">
         <v>1.6791</v>
@@ -1044,323 +1044,323 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4169</v>
+        <v>2.5483</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0324</v>
+        <v>1.0886</v>
       </c>
       <c r="D14" t="n">
-        <v>0.476</v>
+        <v>0.5244</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4169</v>
+        <v>2.5483</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4</v>
+        <v>1.7475</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0169</v>
+        <v>0.5552</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4</v>
+        <v>1.7475</v>
       </c>
       <c r="I14" t="n">
-        <v>0.756</v>
+        <v>1.7925</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0169</v>
+        <v>0.5552</v>
       </c>
       <c r="K14" t="n">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="L14" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7729</v>
+        <v>2.3477</v>
       </c>
       <c r="N14" t="n">
-        <v>163</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>Zyphon</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3027</v>
+        <v>2.5409</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9836</v>
+        <v>1.0854</v>
       </c>
       <c r="D15" t="n">
-        <v>0.424</v>
+        <v>0.5211</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3027</v>
+        <v>2.5409</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7475</v>
+        <v>2.1028</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5552</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7475</v>
+        <v>2.1028</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7925</v>
+        <v>2.1028</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5552</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="L15" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3477</v>
+        <v>2.1028</v>
       </c>
       <c r="N15" t="n">
-        <v>191</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Zyphon</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1028</v>
+        <v>2.3599</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8983</v>
+        <v>1.0081</v>
       </c>
       <c r="D16" t="n">
-        <v>0.333</v>
+        <v>0.4403</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1028</v>
+        <v>2.3599</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1028</v>
+        <v>1.4</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.0169</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1028</v>
+        <v>1.4</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1028</v>
+        <v>0.756</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.0169</v>
       </c>
       <c r="K16" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1028</v>
+        <v>1.7729</v>
       </c>
       <c r="N16" t="n">
-        <v>84</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7888</v>
+        <v>1.992</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7641</v>
+        <v>0.8509</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1901</v>
+        <v>0.276</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7888</v>
+        <v>1.992</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3877</v>
+        <v>2.5166</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1765</v>
+        <v>-0.7648</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3877</v>
+        <v>2.7831</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3877</v>
+        <v>2.7831</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1765</v>
+        <v>-0.7648</v>
       </c>
       <c r="K17" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="L17" t="n">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7888</v>
+        <v>2.0183</v>
       </c>
       <c r="N17" t="n">
-        <v>167</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7518</v>
+        <v>1.9487</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7483</v>
+        <v>0.8324</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1733</v>
+        <v>0.2566</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7518</v>
+        <v>1.9487</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5166</v>
+        <v>-0.3877</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7648</v>
+        <v>2.1765</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7831</v>
+        <v>-0.3877</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7831</v>
+        <v>-0.3877</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7648</v>
+        <v>2.1765</v>
       </c>
       <c r="K18" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L18" t="n">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0183</v>
+        <v>1.7888</v>
       </c>
       <c r="N18" t="n">
-        <v>125</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4693</v>
+        <v>1.5122</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6276</v>
+        <v>0.646</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0447</v>
+        <v>0.0616</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4693</v>
+        <v>1.5122</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7541</v>
+        <v>1.4043</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2848</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1927</v>
+        <v>1.4043</v>
       </c>
       <c r="I19" t="n">
-        <v>2.264</v>
+        <v>1.4043</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2848</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L19" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9791999999999998</v>
+        <v>1.4043</v>
       </c>
       <c r="N19" t="n">
-        <v>204</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4043</v>
+        <v>1.377</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5999</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0151</v>
+        <v>0.0013</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4043</v>
+        <v>1.377</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4043</v>
+        <v>2.7541</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-1.2848</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4043</v>
+        <v>4.1927</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4043</v>
+        <v>2.264</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-1.2848</v>
       </c>
       <c r="K20" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4043</v>
+        <v>0.9791999999999998</v>
       </c>
       <c r="N20" t="n">
-        <v>111</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21">
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3219</v>
+        <v>1.1944</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5647</v>
+        <v>0.5102</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0224</v>
+        <v>-0.0803</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3219</v>
+        <v>1.1944</v>
       </c>
       <c r="F21" t="n">
         <v>-0.3137</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2813</v>
+        <v>1.1523</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5473</v>
+        <v>0.4922</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0409</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2813</v>
+        <v>1.1523</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0024</v>
+        <v>1.4784</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7211</v>
+        <v>-0.3366</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0024</v>
+        <v>1.4784</v>
       </c>
       <c r="I22" t="n">
-        <v>2.054</v>
+        <v>1.4784</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7211</v>
+        <v>-0.3366</v>
       </c>
       <c r="K22" t="n">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="L22" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3329</v>
+        <v>1.1418</v>
       </c>
       <c r="N22" t="n">
-        <v>191</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1418</v>
+        <v>1.1033</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4877</v>
+        <v>0.4713</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1044</v>
+        <v>-0.121</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1418</v>
+        <v>1.1033</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4784</v>
+        <v>2.0024</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3366</v>
+        <v>-0.7211</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4784</v>
+        <v>2.0024</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4784</v>
+        <v>2.054</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3366</v>
+        <v>-0.7211</v>
       </c>
       <c r="K23" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="L23" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1418</v>
+        <v>1.3329</v>
       </c>
       <c r="N23" t="n">
-        <v>125</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.089</v>
+        <v>1.0695</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4652</v>
+        <v>0.4569</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1285</v>
+        <v>-0.1361</v>
       </c>
       <c r="E24" t="n">
-        <v>1.089</v>
+        <v>1.0695</v>
       </c>
       <c r="F24" t="n">
         <v>0.9999</v>
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9048</v>
+        <v>0.836</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3865</v>
+        <v>0.3571</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2123</v>
+        <v>-0.2404</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9048</v>
+        <v>0.836</v>
       </c>
       <c r="F25" t="n">
         <v>1.7439</v>
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7834</v>
+        <v>0.6681</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3346</v>
+        <v>0.2854</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2676</v>
+        <v>-0.3154</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7834</v>
+        <v>0.6681</v>
       </c>
       <c r="F26" t="n">
         <v>-0.1947</v>
@@ -1642,139 +1642,139 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3493</v>
+        <v>0.3033</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1492</v>
+        <v>0.1296</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4652</v>
+        <v>-0.4783</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3493</v>
+        <v>0.3033</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2282</v>
+        <v>-0.4203</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1211</v>
+        <v>0.7037</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2282</v>
+        <v>-0.4203</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2282</v>
+        <v>-0.4311</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1211</v>
+        <v>0.7037</v>
       </c>
       <c r="K27" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="L27" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3493</v>
+        <v>0.2726</v>
       </c>
       <c r="N27" t="n">
-        <v>125</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2834</v>
+        <v>0.2504</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1211</v>
+        <v>0.107</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4952</v>
+        <v>-0.502</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2834</v>
+        <v>0.2504</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4203</v>
+        <v>0.1579</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7037</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4203</v>
+        <v>0.1579</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4311</v>
+        <v>0.1579</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7037</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L28" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2726</v>
+        <v>0.1579</v>
       </c>
       <c r="N28" t="n">
-        <v>191</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1579</v>
+        <v>0.052</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0675</v>
+        <v>0.0222</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5523</v>
+        <v>-0.5906</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1579</v>
+        <v>0.052</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1579</v>
+        <v>0.2282</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.1211</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1579</v>
+        <v>0.2282</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1579</v>
+        <v>0.2282</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.1211</v>
       </c>
       <c r="K29" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1579</v>
+        <v>0.3493</v>
       </c>
       <c r="N29" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30">
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0588</v>
+        <v>-0.3213</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0251</v>
+        <v>-0.1372</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.651</v>
+        <v>-0.7573</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0588</v>
+        <v>-0.3213</v>
       </c>
       <c r="F30" t="n">
         <v>-0.091</v>
@@ -1826,277 +1826,277 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3758</v>
+        <v>-0.4708</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1605</v>
+        <v>-0.2011</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7953</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3758</v>
+        <v>-0.4708</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3758</v>
+        <v>0.7244</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-1.1179</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3758</v>
+        <v>0.7244</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3758</v>
+        <v>0.7244</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-1.1179</v>
       </c>
       <c r="K31" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3758</v>
+        <v>-0.3934999999999998</v>
       </c>
       <c r="N31" t="n">
-        <v>111</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3935</v>
+        <v>-0.521</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1681</v>
+        <v>-0.2226</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8033</v>
+        <v>-0.8465</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3935</v>
+        <v>-0.521</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7244</v>
+        <v>-0.5505</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.1179</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7244</v>
+        <v>-0.5505</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7244</v>
+        <v>-0.5505</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.1179</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L32" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3934999999999998</v>
+        <v>-0.5505</v>
       </c>
       <c r="N32" t="n">
-        <v>217</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5351</v>
+        <v>-0.5331</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2286</v>
+        <v>-0.2277</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8678</v>
+        <v>-0.8519</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5351</v>
+        <v>-0.5331</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2384</v>
+        <v>-0.7992</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.7735</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2384</v>
+        <v>-0.7992</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2384</v>
+        <v>-0.7992</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.7735</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L33" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5350999999999999</v>
+        <v>-0.7992</v>
       </c>
       <c r="N33" t="n">
-        <v>125</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5505</v>
+        <v>-0.5986</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2352</v>
+        <v>-0.2557</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8748</v>
+        <v>-0.8812</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5505</v>
+        <v>-0.5986</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5505</v>
+        <v>-0.3758</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5505</v>
+        <v>-0.3758</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5505</v>
+        <v>-0.3758</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5505</v>
+        <v>-0.3758</v>
       </c>
       <c r="N34" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dycha</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6745</v>
+        <v>-0.7006</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2881</v>
+        <v>-0.2993</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9312</v>
+        <v>-0.9268</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6745</v>
+        <v>-0.7006</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6745</v>
+        <v>0.2384</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.7735</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6745</v>
+        <v>0.2384</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6745</v>
+        <v>0.2384</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.7735</v>
       </c>
       <c r="K35" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6745</v>
+        <v>-0.5350999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>dycha</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.758</v>
+        <v>-0.7339</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3238</v>
+        <v>-0.3135</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9693000000000001</v>
+        <v>-0.9416</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.758</v>
+        <v>-0.7339</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.758</v>
+        <v>-0.6745</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.758</v>
+        <v>-0.6745</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.758</v>
+        <v>-0.6745</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.758</v>
+        <v>-0.6745</v>
       </c>
       <c r="N36" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37">
@@ -2106,16 +2106,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7678</v>
+        <v>-0.8348</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.328</v>
+        <v>-0.3566</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9737</v>
+        <v>-0.9867</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7678</v>
+        <v>-0.8348</v>
       </c>
       <c r="F37" t="n">
         <v>-0.7678</v>
@@ -2148,78 +2148,78 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>salazar</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.7765</v>
+        <v>-0.8676</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3317</v>
+        <v>-0.3706</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9777</v>
+        <v>-1.0014</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.7765</v>
+        <v>-0.8676</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.7765</v>
+        <v>-0.1211</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.8161</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.7765</v>
+        <v>-0.1211</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7765</v>
+        <v>-0.1211</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.8161</v>
       </c>
       <c r="K38" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7765</v>
+        <v>-0.9372</v>
       </c>
       <c r="N38" t="n">
-        <v>84</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.7992</v>
+        <v>-0.8851</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3414</v>
+        <v>-0.3781</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.988</v>
+        <v>-1.0092</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.7992</v>
+        <v>-0.8851</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.7992</v>
+        <v>-0.758</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.7992</v>
+        <v>-0.758</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7992</v>
+        <v>-0.758</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.7992</v>
+        <v>-0.758</v>
       </c>
       <c r="N39" t="n">
         <v>84</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.9372</v>
+        <v>-1.1834</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4003</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0508</v>
+        <v>-1.1424</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.9372</v>
+        <v>-1.1834</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.1211</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.8161</v>
+        <v>-0.1897</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.1211</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1211</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.8161</v>
+        <v>-0.1897</v>
       </c>
       <c r="K40" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="L40" t="n">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.9372</v>
+        <v>-1.1277</v>
       </c>
       <c r="N40" t="n">
-        <v>125</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>salazar</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.1277</v>
+        <v>-1.3998</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4817</v>
+        <v>-0.598</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1376</v>
+        <v>-1.2391</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.1277</v>
+        <v>-1.3998</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-0.7765</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.1897</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-0.7765</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-0.7765</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.1897</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="L41" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.1277</v>
+        <v>-0.7765</v>
       </c>
       <c r="N41" t="n">
-        <v>217</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6976/event_6976_evp_summary.xlsx
+++ b/database/event/6976/event_6976_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.6714</v>
+        <v>7.9654</v>
       </c>
       <c r="C2" t="n">
-        <v>3.277</v>
+        <v>3.4026</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8128</v>
+        <v>3.0228</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6714</v>
+        <v>7.9654</v>
       </c>
       <c r="F2" t="n">
-        <v>2.267</v>
+        <v>2.4174</v>
       </c>
       <c r="G2" t="n">
-        <v>5.0376</v>
+        <v>5.1812</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5854</v>
+        <v>2.6335</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3961</v>
+        <v>1.4786</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0376</v>
+        <v>5.1812</v>
       </c>
       <c r="K2" t="n">
         <v>85</v>
@@ -529,7 +529,7 @@
         <v>78</v>
       </c>
       <c r="M2" t="n">
-        <v>6.4337</v>
+        <v>6.6598</v>
       </c>
       <c r="N2" t="n">
         <v>163</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.3016</v>
+        <v>4.1936</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8375</v>
+        <v>1.7914</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3076</v>
+        <v>1.3046</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3016</v>
+        <v>4.1936</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4468</v>
+        <v>3.3744</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8139</v>
+        <v>0.7783</v>
       </c>
       <c r="H3" t="n">
-        <v>6.4781</v>
+        <v>6.2263</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4981</v>
+        <v>3.4959</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8139</v>
+        <v>0.7783</v>
       </c>
       <c r="K3" t="n">
         <v>118</v>
@@ -575,7 +575,7 @@
         <v>86</v>
       </c>
       <c r="M3" t="n">
-        <v>4.312</v>
+        <v>4.2742</v>
       </c>
       <c r="N3" t="n">
         <v>204</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.8431</v>
+        <v>3.7314</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6417</v>
+        <v>1.5939</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1028</v>
+        <v>1.094</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8431</v>
+        <v>3.7314</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3849</v>
+        <v>3.3185</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5789</v>
+        <v>0.5336</v>
       </c>
       <c r="H4" t="n">
-        <v>6.274</v>
+        <v>6.0164</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3879</v>
+        <v>3.378</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5789</v>
+        <v>0.5336</v>
       </c>
       <c r="K4" t="n">
         <v>85</v>
@@ -621,7 +621,7 @@
         <v>78</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9668</v>
+        <v>3.9116</v>
       </c>
       <c r="N4" t="n">
         <v>163</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6983</v>
+        <v>3.6779</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5798</v>
+        <v>1.5711</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0381</v>
+        <v>1.0697</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6983</v>
+        <v>3.6779</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7968</v>
+        <v>0.7775</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7939</v>
+        <v>2.7928</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7968</v>
+        <v>0.7775</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7968</v>
+        <v>0.7775</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7939</v>
+        <v>2.7928</v>
       </c>
       <c r="K5" t="n">
         <v>85</v>
@@ -667,7 +667,7 @@
         <v>82</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5907</v>
+        <v>3.5703</v>
       </c>
       <c r="N5" t="n">
         <v>167</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.4892</v>
+        <v>3.604</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4905</v>
+        <v>1.5395</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9447</v>
+        <v>1.036</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4892</v>
+        <v>3.604</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3133</v>
+        <v>2.2581</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9832</v>
+        <v>1.1532</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3382</v>
+        <v>2.2581</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3382</v>
+        <v>2.2581</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9832</v>
+        <v>1.1532</v>
       </c>
       <c r="K6" t="n">
         <v>105</v>
@@ -713,7 +713,7 @@
         <v>112</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3214</v>
+        <v>3.4113</v>
       </c>
       <c r="N6" t="n">
         <v>217</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.393</v>
+        <v>3.2818</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4494</v>
+        <v>1.4019</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9018</v>
+        <v>0.8892</v>
       </c>
       <c r="E7" t="n">
-        <v>3.393</v>
+        <v>3.2818</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1012</v>
+        <v>1.0661</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1746</v>
+        <v>2.0985</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1012</v>
+        <v>1.0661</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1012</v>
+        <v>1.0661</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1746</v>
+        <v>2.0985</v>
       </c>
       <c r="K7" t="n">
         <v>105</v>
@@ -759,7 +759,7 @@
         <v>112</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2758</v>
+        <v>3.1646</v>
       </c>
       <c r="N7" t="n">
         <v>217</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0815</v>
+        <v>3.1824</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3163</v>
+        <v>1.3594</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7625999999999999</v>
+        <v>0.8439</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0815</v>
+        <v>3.1824</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6559</v>
+        <v>2.7144</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4673</v>
+        <v>0.5097</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8688</v>
+        <v>3.7484</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0891</v>
+        <v>2.1046</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4673</v>
+        <v>0.5097</v>
       </c>
       <c r="K8" t="n">
         <v>85</v>
@@ -805,7 +805,7 @@
         <v>78</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5564</v>
+        <v>2.6143</v>
       </c>
       <c r="N8" t="n">
         <v>163</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0037</v>
+        <v>3.1212</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2831</v>
+        <v>1.3333</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7279</v>
+        <v>0.8161</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0037</v>
+        <v>3.1212</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2893</v>
+        <v>2.4019</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6889</v>
+        <v>0.6938</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6589</v>
+        <v>2.575</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4358</v>
+        <v>1.4458</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6889</v>
+        <v>0.6938</v>
       </c>
       <c r="K9" t="n">
         <v>118</v>
@@ -851,7 +851,7 @@
         <v>86</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1247</v>
+        <v>2.1396</v>
       </c>
       <c r="N9" t="n">
         <v>204</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9899</v>
+        <v>2.9374</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2772</v>
+        <v>1.2548</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7217</v>
+        <v>0.7323</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9899</v>
+        <v>2.9374</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6826</v>
+        <v>2.7242</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2208</v>
+        <v>0.1267</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9565</v>
+        <v>3.7851</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1365</v>
+        <v>2.1252</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2208</v>
+        <v>0.1267</v>
       </c>
       <c r="K10" t="n">
         <v>118</v>
@@ -897,7 +897,7 @@
         <v>86</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3573</v>
+        <v>2.2519</v>
       </c>
       <c r="N10" t="n">
         <v>204</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7492</v>
+        <v>2.8966</v>
       </c>
       <c r="C11" t="n">
-        <v>1.1744</v>
+        <v>1.2373</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6142</v>
+        <v>0.7138</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7492</v>
+        <v>2.8966</v>
       </c>
       <c r="F11" t="n">
-        <v>2.673</v>
+        <v>1.0848</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0693</v>
+        <v>1.7363</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1254</v>
+        <v>1.0848</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1254</v>
+        <v>1.0848</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0693</v>
+        <v>1.7363</v>
       </c>
       <c r="K11" t="n">
         <v>85</v>
@@ -943,7 +943,7 @@
         <v>82</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1947</v>
+        <v>2.8211</v>
       </c>
       <c r="N11" t="n">
         <v>167</v>
@@ -952,35 +952,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7414</v>
+        <v>2.7505</v>
       </c>
       <c r="C12" t="n">
-        <v>1.171</v>
+        <v>1.1749</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6107</v>
+        <v>0.6472</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7414</v>
+        <v>2.7505</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9802999999999999</v>
+        <v>2.6163</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6856</v>
+        <v>0.1273</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9802999999999999</v>
+        <v>3.0456</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9802999999999999</v>
+        <v>3.0456</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6856</v>
+        <v>0.1273</v>
       </c>
       <c r="K12" t="n">
         <v>85</v>
@@ -989,7 +989,7 @@
         <v>82</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6659</v>
+        <v>3.1729</v>
       </c>
       <c r="N12" t="n">
         <v>167</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5848</v>
+        <v>2.4735</v>
       </c>
       <c r="C13" t="n">
-        <v>1.1041</v>
+        <v>1.0566</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.521</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5848</v>
+        <v>2.4735</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6791</v>
+        <v>1.5684</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8264</v>
+        <v>0.8258</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6791</v>
+        <v>1.5684</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9067</v>
+        <v>0.8806</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8264</v>
+        <v>0.8258</v>
       </c>
       <c r="K13" t="n">
         <v>118</v>
@@ -1035,7 +1035,7 @@
         <v>86</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7331</v>
+        <v>1.7064</v>
       </c>
       <c r="N13" t="n">
         <v>204</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>Zyphon</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5483</v>
+        <v>2.4649</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0886</v>
+        <v>1.0529</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5244</v>
+        <v>0.5171</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5483</v>
+        <v>2.4649</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7475</v>
+        <v>2.0268</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5552</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7475</v>
+        <v>2.0268</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7925</v>
+        <v>2.0268</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5552</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="L14" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3477</v>
+        <v>2.0268</v>
       </c>
       <c r="N14" t="n">
-        <v>191</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Zyphon</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5409</v>
+        <v>2.4517</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0854</v>
+        <v>1.0473</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5211</v>
+        <v>0.5111</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5409</v>
+        <v>2.4517</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1028</v>
+        <v>1.7345</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.4715</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1028</v>
+        <v>1.7345</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1028</v>
+        <v>1.7809</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.4715</v>
       </c>
       <c r="K15" t="n">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1028</v>
+        <v>2.2524</v>
       </c>
       <c r="N15" t="n">
-        <v>84</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3599</v>
+        <v>2.3091</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0081</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4403</v>
+        <v>0.4461</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3599</v>
+        <v>2.3091</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4</v>
+        <v>1.3942</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0169</v>
+        <v>0.9719</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4</v>
+        <v>1.3942</v>
       </c>
       <c r="I16" t="n">
-        <v>0.756</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0169</v>
+        <v>0.9719</v>
       </c>
       <c r="K16" t="n">
         <v>85</v>
@@ -1173,7 +1173,7 @@
         <v>78</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7729</v>
+        <v>1.7547</v>
       </c>
       <c r="N16" t="n">
         <v>163</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.992</v>
+        <v>2.0292</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8509</v>
+        <v>0.8668</v>
       </c>
       <c r="D17" t="n">
-        <v>0.276</v>
+        <v>0.3186</v>
       </c>
       <c r="E17" t="n">
-        <v>1.992</v>
+        <v>2.0292</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5166</v>
+        <v>2.5329</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7648</v>
+        <v>-0.7439</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7831</v>
+        <v>2.8544</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7831</v>
+        <v>2.8544</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7648</v>
+        <v>-0.7439</v>
       </c>
       <c r="K17" t="n">
         <v>91</v>
@@ -1219,7 +1219,7 @@
         <v>34</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0183</v>
+        <v>2.1105</v>
       </c>
       <c r="N17" t="n">
         <v>125</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9487</v>
+        <v>1.8155</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8324</v>
+        <v>0.7755</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2566</v>
+        <v>0.2213</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9487</v>
+        <v>1.8155</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3877</v>
+        <v>-0.4122</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1765</v>
+        <v>2.0678</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3877</v>
+        <v>-0.4122</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3877</v>
+        <v>-0.4122</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1765</v>
+        <v>2.0678</v>
       </c>
       <c r="K18" t="n">
         <v>85</v>
@@ -1265,7 +1265,7 @@
         <v>82</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7888</v>
+        <v>1.6556</v>
       </c>
       <c r="N18" t="n">
         <v>167</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5122</v>
+        <v>1.3904</v>
       </c>
       <c r="C19" t="n">
-        <v>0.646</v>
+        <v>0.5939</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0616</v>
+        <v>0.0276</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5122</v>
+        <v>1.3904</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4043</v>
+        <v>2.7683</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-1.2856</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4043</v>
+        <v>3.9507</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4043</v>
+        <v>2.2182</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-1.2856</v>
       </c>
       <c r="K19" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4043</v>
+        <v>0.9325999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>111</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.377</v>
+        <v>1.3295</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.5679</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0013</v>
+        <v>-0.0001</v>
       </c>
       <c r="E20" t="n">
-        <v>1.377</v>
+        <v>1.3295</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7541</v>
+        <v>1.2216</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2848</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1927</v>
+        <v>1.2216</v>
       </c>
       <c r="I20" t="n">
-        <v>2.264</v>
+        <v>1.2216</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2848</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L20" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9791999999999998</v>
+        <v>1.2216</v>
       </c>
       <c r="N20" t="n">
-        <v>204</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1944</v>
+        <v>1.2531</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5102</v>
+        <v>0.5353</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0803</v>
+        <v>-0.0349</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1944</v>
+        <v>1.2531</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3137</v>
+        <v>-0.2919</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6356</v>
+        <v>1.6725</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3137</v>
+        <v>-0.2919</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1694</v>
+        <v>-0.1639</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6356</v>
+        <v>1.6725</v>
       </c>
       <c r="K21" t="n">
         <v>85</v>
@@ -1403,7 +1403,7 @@
         <v>78</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4662</v>
+        <v>1.5086</v>
       </c>
       <c r="N21" t="n">
         <v>163</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1523</v>
+        <v>1.1377</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4922</v>
+        <v>0.486</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1523</v>
+        <v>1.1377</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4784</v>
+        <v>1.4284</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3366</v>
+        <v>-0.3012</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4784</v>
+        <v>1.4284</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4784</v>
+        <v>1.4284</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3366</v>
+        <v>-0.3012</v>
       </c>
       <c r="K22" t="n">
         <v>91</v>
@@ -1449,7 +1449,7 @@
         <v>34</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1418</v>
+        <v>1.1272</v>
       </c>
       <c r="N22" t="n">
         <v>125</v>
@@ -1458,35 +1458,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1033</v>
+        <v>1.0734</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4713</v>
+        <v>0.4585</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.121</v>
+        <v>-0.1168</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1033</v>
+        <v>1.0734</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0024</v>
+        <v>1.0299</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7211</v>
+        <v>0.0631</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0024</v>
+        <v>1.0299</v>
       </c>
       <c r="I23" t="n">
-        <v>2.054</v>
+        <v>1.0574</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7211</v>
+        <v>0.0631</v>
       </c>
       <c r="K23" t="n">
         <v>119</v>
@@ -1495,7 +1495,7 @@
         <v>72</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3329</v>
+        <v>1.1205</v>
       </c>
       <c r="N23" t="n">
         <v>191</v>
@@ -1504,35 +1504,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0695</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4569</v>
+        <v>0.4046</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1361</v>
+        <v>-0.1743</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0695</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9999</v>
+        <v>1.7916</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0891</v>
+        <v>-0.6665</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9999</v>
+        <v>1.7916</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0257</v>
+        <v>1.8395</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0891</v>
+        <v>-0.6665</v>
       </c>
       <c r="K24" t="n">
         <v>119</v>
@@ -1541,7 +1541,7 @@
         <v>72</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1148</v>
+        <v>1.173</v>
       </c>
       <c r="N24" t="n">
         <v>191</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.836</v>
+        <v>0.8918</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3571</v>
+        <v>0.3809</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2404</v>
+        <v>-0.1995</v>
       </c>
       <c r="E25" t="n">
-        <v>0.836</v>
+        <v>0.8918</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7439</v>
+        <v>1.6984</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8391</v>
+        <v>-0.7378</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7439</v>
+        <v>1.6984</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7439</v>
+        <v>1.6984</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8391</v>
+        <v>-0.7378</v>
       </c>
       <c r="K25" t="n">
         <v>105</v>
@@ -1587,7 +1587,7 @@
         <v>112</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9048</v>
+        <v>0.9605999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>217</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6681</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2854</v>
+        <v>0.3227</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3154</v>
+        <v>-0.2616</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6681</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1947</v>
+        <v>-0.1265</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9781</v>
+        <v>0.9973</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1947</v>
+        <v>-0.1265</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1947</v>
+        <v>-0.1265</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9781</v>
+        <v>0.9973</v>
       </c>
       <c r="K26" t="n">
         <v>85</v>
@@ -1633,7 +1633,7 @@
         <v>82</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7834</v>
+        <v>0.8708</v>
       </c>
       <c r="N26" t="n">
         <v>167</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3033</v>
+        <v>0.1971</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1296</v>
+        <v>0.0842</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4783</v>
+        <v>-0.516</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3033</v>
+        <v>0.1971</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4203</v>
+        <v>-0.4669</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7037</v>
+        <v>0.6441</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4203</v>
+        <v>-0.4669</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.4311</v>
+        <v>-0.4794</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7037</v>
+        <v>0.6441</v>
       </c>
       <c r="K27" t="n">
         <v>119</v>
@@ -1679,7 +1679,7 @@
         <v>72</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2726</v>
+        <v>0.1647</v>
       </c>
       <c r="N27" t="n">
         <v>191</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2504</v>
+        <v>0.1278</v>
       </c>
       <c r="C28" t="n">
-        <v>0.107</v>
+        <v>0.0546</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.502</v>
+        <v>-0.5476</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2504</v>
+        <v>0.1278</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1579</v>
+        <v>0.0353</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1579</v>
+        <v>0.0353</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1579</v>
+        <v>0.0353</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1579</v>
+        <v>0.0353</v>
       </c>
       <c r="N28" t="n">
         <v>111</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.052</v>
+        <v>0.0151</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0222</v>
+        <v>0.0065</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5906</v>
+        <v>-0.5989</v>
       </c>
       <c r="E29" t="n">
-        <v>0.052</v>
+        <v>0.0151</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2282</v>
+        <v>0.2131</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1211</v>
+        <v>0.0993</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2282</v>
+        <v>0.2131</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2282</v>
+        <v>0.2131</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1211</v>
+        <v>0.0993</v>
       </c>
       <c r="K29" t="n">
         <v>91</v>
@@ -1771,7 +1771,7 @@
         <v>34</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3493</v>
+        <v>0.3124</v>
       </c>
       <c r="N29" t="n">
         <v>125</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3213</v>
+        <v>-0.2579</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1372</v>
+        <v>-0.1102</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7573</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3213</v>
+        <v>-0.2579</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.091</v>
+        <v>-0.0378</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0322</v>
+        <v>0.0424</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.091</v>
+        <v>-0.0378</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.0388</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0322</v>
+        <v>0.0424</v>
       </c>
       <c r="K30" t="n">
         <v>119</v>
@@ -1817,7 +1817,7 @@
         <v>72</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.06109999999999999</v>
+        <v>0.003599999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>191</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4708</v>
+        <v>-0.3937</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2011</v>
+        <v>-0.1682</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.7851</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4708</v>
+        <v>-0.3937</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7244</v>
+        <v>0.7571</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.1179</v>
+        <v>-1.0735</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7244</v>
+        <v>0.7571</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7244</v>
+        <v>0.7571</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.1179</v>
+        <v>-1.0735</v>
       </c>
       <c r="K31" t="n">
         <v>105</v>
@@ -1863,7 +1863,7 @@
         <v>112</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3934999999999998</v>
+        <v>-0.3163999999999999</v>
       </c>
       <c r="N31" t="n">
         <v>217</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.521</v>
+        <v>-0.5567</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2226</v>
+        <v>-0.2378</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8465</v>
+        <v>-0.8594000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.521</v>
+        <v>-0.5567</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5505</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5505</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5505</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5505</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="N32" t="n">
         <v>84</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5331</v>
+        <v>-0.5687</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2277</v>
+        <v>-0.2429</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8519</v>
+        <v>-0.8649</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5331</v>
+        <v>-0.5687</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7992</v>
+        <v>-0.8348</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7992</v>
+        <v>-0.8348</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7992</v>
+        <v>-0.8348</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7992</v>
+        <v>-0.8348</v>
       </c>
       <c r="N33" t="n">
         <v>84</v>
@@ -1964,93 +1964,93 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5986</v>
+        <v>-0.6407</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2557</v>
+        <v>-0.2737</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8812</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5986</v>
+        <v>-0.6407</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3758</v>
+        <v>0.28</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.7552</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3758</v>
+        <v>0.28</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3758</v>
+        <v>0.28</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.7552</v>
       </c>
       <c r="K34" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3758</v>
+        <v>-0.4752</v>
       </c>
       <c r="N34" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7006</v>
+        <v>-0.6652</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2993</v>
+        <v>-0.2842</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9268</v>
+        <v>-0.9088000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7006</v>
+        <v>-0.6652</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2384</v>
+        <v>-0.4424</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.7735</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2384</v>
+        <v>-0.4424</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2384</v>
+        <v>-0.4424</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.7735</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="L35" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5350999999999999</v>
+        <v>-0.4424</v>
       </c>
       <c r="N35" t="n">
-        <v>125</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7339</v>
+        <v>-0.7543</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3135</v>
+        <v>-0.3222</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9416</v>
+        <v>-0.9494</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7339</v>
+        <v>-0.7543</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6745</v>
+        <v>-0.6949</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6745</v>
+        <v>-0.6949</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6745</v>
+        <v>-0.6949</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6745</v>
+        <v>-0.6949</v>
       </c>
       <c r="N36" t="n">
         <v>111</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8348</v>
+        <v>-0.8045</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3566</v>
+        <v>-0.3437</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9867</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8348</v>
+        <v>-0.8045</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7678</v>
+        <v>-0.7375</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7678</v>
+        <v>-0.7375</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7678</v>
+        <v>-0.7375</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7678</v>
+        <v>-0.7375</v>
       </c>
       <c r="N37" t="n">
         <v>111</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8676</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3706</v>
+        <v>-0.3546</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0014</v>
+        <v>-0.9839</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8676</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.1211</v>
+        <v>-0.703</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.8161</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.1211</v>
+        <v>-0.703</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1211</v>
+        <v>-0.703</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.8161</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L38" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9372</v>
+        <v>-0.703</v>
       </c>
       <c r="N38" t="n">
-        <v>125</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.8851</v>
+        <v>-0.891</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3781</v>
+        <v>-0.3806</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0092</v>
+        <v>-1.0117</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.8851</v>
+        <v>-0.891</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.758</v>
+        <v>-0.1414</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.8192</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.758</v>
+        <v>-0.1414</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.758</v>
+        <v>-0.1414</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.8192</v>
       </c>
       <c r="K39" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.758</v>
+        <v>-0.9606</v>
       </c>
       <c r="N39" t="n">
-        <v>84</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1834</v>
+        <v>-1.1346</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-0.4847</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1424</v>
+        <v>-1.1227</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1834</v>
+        <v>-1.1346</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-0.8862</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.1897</v>
+        <v>-0.1927</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-0.8862</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-0.8862</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1897</v>
+        <v>-0.1927</v>
       </c>
       <c r="K40" t="n">
         <v>105</v>
@@ -2277,7 +2277,7 @@
         <v>112</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.1277</v>
+        <v>-1.0789</v>
       </c>
       <c r="N40" t="n">
         <v>217</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.3998</v>
+        <v>-1.3261</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.598</v>
+        <v>-0.5665</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2391</v>
+        <v>-1.2099</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.3998</v>
+        <v>-1.3261</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.7765</v>
+        <v>-0.7028</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.7765</v>
+        <v>-0.7028</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7765</v>
+        <v>-0.7028</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.7765</v>
+        <v>-0.7028</v>
       </c>
       <c r="N41" t="n">
         <v>84</v>
@@ -2429,10 +2429,10 @@
         <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7775</v>
+        <v>0.7408</v>
       </c>
       <c r="J2" t="n">
-        <v>13.995</v>
+        <v>13.3344</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.76</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2743</v>
+        <v>-0.2562</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.9374</v>
+        <v>-4.6116</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.7</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3304</v>
+        <v>-0.3142</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.9472</v>
+        <v>-5.6556</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3396</v>
+        <v>-0.3239</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.1128</v>
+        <v>-5.8302</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.61</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4119</v>
+        <v>-0.4015</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.4142</v>
+        <v>-7.227</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.67</v>
       </c>
       <c r="I7" t="n">
-        <v>1.407</v>
+        <v>1.4424</v>
       </c>
       <c r="J7" t="n">
-        <v>25.326</v>
+        <v>25.9632</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.65</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3729</v>
+        <v>1.4073</v>
       </c>
       <c r="J8" t="n">
-        <v>24.7122</v>
+        <v>25.3314</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.45</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0172</v>
+        <v>1.0145</v>
       </c>
       <c r="J9" t="n">
-        <v>18.3096</v>
+        <v>18.261</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2895</v>
+        <v>0.2579</v>
       </c>
       <c r="J10" t="n">
-        <v>5.211</v>
+        <v>4.6422</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.77</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7126</v>
+        <v>-0.6885</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.8268</v>
+        <v>-12.393</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.54</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9716</v>
+        <v>0.9366</v>
       </c>
       <c r="J12" t="n">
-        <v>19.432</v>
+        <v>18.732</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4433</v>
+        <v>0.3859</v>
       </c>
       <c r="J13" t="n">
-        <v>8.866</v>
+        <v>7.718</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.77</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2783</v>
+        <v>-0.2592</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.566</v>
+        <v>-5.184</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.75</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2974</v>
+        <v>-0.2792</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.948</v>
+        <v>-5.584</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.55</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4775</v>
+        <v>-0.4756</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.550000000000001</v>
+        <v>-9.512</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>2.2</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J17" t="n">
-        <v>36.906</v>
+        <v>39.644</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1987</v>
+        <v>0.1706</v>
       </c>
       <c r="J18" t="n">
-        <v>3.974</v>
+        <v>3.412</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.06</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1987</v>
+        <v>0.1706</v>
       </c>
       <c r="J19" t="n">
-        <v>3.974</v>
+        <v>3.412</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.9</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3812</v>
+        <v>-0.3403</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.624</v>
+        <v>-6.806</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6032999999999999</v>
+        <v>-0.5684</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.066</v>
+        <v>-11.368</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.53</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9915</v>
+        <v>0.9786</v>
       </c>
       <c r="J22" t="n">
-        <v>17.847</v>
+        <v>17.6148</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.46</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8958</v>
+        <v>0.8809</v>
       </c>
       <c r="J23" t="n">
-        <v>16.1244</v>
+        <v>15.8562</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4476</v>
+        <v>0.4191</v>
       </c>
       <c r="J24" t="n">
-        <v>8.056800000000001</v>
+        <v>7.5438</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.14</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4051</v>
+        <v>0.3719</v>
       </c>
       <c r="J25" t="n">
-        <v>7.2918</v>
+        <v>6.6942</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4878</v>
+        <v>-0.4487</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.7804</v>
+        <v>-8.076599999999999</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.03</v>
       </c>
       <c r="I27" t="n">
-        <v>0.13</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>2.34</v>
+        <v>1.791</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.97</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0451</v>
+        <v>-0.0358</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.8118</v>
+        <v>-0.6444</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.85</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1889</v>
+        <v>-0.1707</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.4002</v>
+        <v>-3.0726</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.77</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2674</v>
+        <v>-0.2487</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.8132</v>
+        <v>-4.4766</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.64</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3879</v>
+        <v>-0.3754</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.9822</v>
+        <v>-6.7572</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.38</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7938</v>
+        <v>0.778</v>
       </c>
       <c r="J32" t="n">
-        <v>17.4636</v>
+        <v>17.116</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.28</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6452</v>
+        <v>0.6324</v>
       </c>
       <c r="J33" t="n">
-        <v>14.1944</v>
+        <v>13.9128</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.22</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5518</v>
+        <v>0.5433</v>
       </c>
       <c r="J34" t="n">
-        <v>12.1396</v>
+        <v>11.9526</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.15</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4349</v>
+        <v>0.4015</v>
       </c>
       <c r="J35" t="n">
-        <v>9.5678</v>
+        <v>8.833</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.82</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5738</v>
+        <v>-0.5364</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.6236</v>
+        <v>-11.8008</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.32</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5914</v>
+        <v>0.5657</v>
       </c>
       <c r="J37" t="n">
-        <v>13.0108</v>
+        <v>12.4454</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.2</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4431</v>
+        <v>0.3899</v>
       </c>
       <c r="J38" t="n">
-        <v>9.748200000000001</v>
+        <v>8.5778</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.88</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1648</v>
+        <v>-0.1451</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.6256</v>
+        <v>-3.1922</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.82</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2276</v>
+        <v>-0.2073</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.0072</v>
+        <v>-4.5606</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.52</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.502</v>
+        <v>-0.5033</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.044</v>
+        <v>-11.0726</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.39</v>
       </c>
       <c r="I42" t="n">
-        <v>0.836</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>20.064</v>
+        <v>19.7064</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.27</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6518</v>
+        <v>0.6372</v>
       </c>
       <c r="J43" t="n">
-        <v>15.6432</v>
+        <v>15.2928</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.99</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0668</v>
+        <v>-0.0481</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.6032</v>
+        <v>-1.1544</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2695</v>
+        <v>-0.2296</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.468</v>
+        <v>-5.5104</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.68</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8618</v>
+        <v>-0.8435</v>
       </c>
       <c r="J46" t="n">
-        <v>-20.6832</v>
+        <v>-20.244</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.26</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.4766</v>
       </c>
       <c r="J47" t="n">
-        <v>12.2544</v>
+        <v>11.4384</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.08</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2141</v>
+        <v>0.1714</v>
       </c>
       <c r="J48" t="n">
-        <v>5.1384</v>
+        <v>4.1136</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.92</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1228</v>
+        <v>-0.1044</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.9472</v>
+        <v>-2.5056</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.91</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1346</v>
+        <v>-0.1156</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.2304</v>
+        <v>-2.7744</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.78</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2712</v>
+        <v>-0.2519</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.5088</v>
+        <v>-6.0456</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.29</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6806</v>
+        <v>0.6654</v>
       </c>
       <c r="J52" t="n">
-        <v>16.3344</v>
+        <v>15.9696</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.28</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6649</v>
+        <v>0.65</v>
       </c>
       <c r="J53" t="n">
-        <v>15.9576</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3288</v>
+        <v>0.2897</v>
       </c>
       <c r="J54" t="n">
-        <v>7.8912</v>
+        <v>6.9528</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.07</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2487</v>
+        <v>0.2137</v>
       </c>
       <c r="J55" t="n">
-        <v>5.9688</v>
+        <v>5.1288</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.58</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0693</v>
+        <v>-1.0763</v>
       </c>
       <c r="J56" t="n">
-        <v>-25.6632</v>
+        <v>-25.8312</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.45</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7284</v>
+        <v>0.696</v>
       </c>
       <c r="J57" t="n">
-        <v>17.4816</v>
+        <v>16.704</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.13</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3125</v>
+        <v>0.2609</v>
       </c>
       <c r="J58" t="n">
-        <v>7.5</v>
+        <v>6.2616</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1225</v>
+        <v>-0.1042</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.94</v>
+        <v>-2.5008</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.76</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2901</v>
+        <v>-0.2717</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.9624</v>
+        <v>-6.5208</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.67</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3738</v>
+        <v>-0.361</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.9712</v>
+        <v>-8.664</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.18</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3216</v>
+        <v>0.3114</v>
       </c>
       <c r="J62" t="n">
-        <v>9.3264</v>
+        <v>9.0306</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0041</v>
+        <v>0.0026</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1189</v>
+        <v>0.07539999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.98</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0402</v>
+        <v>-0.0312</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.1658</v>
+        <v>-0.9048</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.91</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1316</v>
+        <v>-0.1133</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.8164</v>
+        <v>-3.2857</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.7</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3435</v>
+        <v>-0.328</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.961499999999999</v>
+        <v>-9.512</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.41</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5175</v>
+        <v>0.4752</v>
       </c>
       <c r="J67" t="n">
-        <v>15.0075</v>
+        <v>13.7808</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.23</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3424</v>
+        <v>0.2837</v>
       </c>
       <c r="J68" t="n">
-        <v>9.929600000000001</v>
+        <v>8.2273</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.15</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2434</v>
+        <v>0.1953</v>
       </c>
       <c r="J69" t="n">
-        <v>7.0586</v>
+        <v>5.6637</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1209</v>
+        <v>-0.1023</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.5061</v>
+        <v>-2.9667</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.85</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2113</v>
+        <v>-0.191</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.1277</v>
+        <v>-5.539</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.85</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4745</v>
+        <v>1.5107</v>
       </c>
       <c r="J72" t="n">
-        <v>35.388</v>
+        <v>36.2568</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.98</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1077</v>
+        <v>-0.0823</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.5848</v>
+        <v>-1.9752</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.85</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.4792</v>
+        <v>-0.4367</v>
       </c>
       <c r="J74" t="n">
-        <v>-11.5008</v>
+        <v>-10.4808</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5746</v>
+        <v>-0.535</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.7904</v>
+        <v>-12.84</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.76</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6884</v>
+        <v>-0.6552</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.5216</v>
+        <v>-15.7248</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.28</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5341</v>
+        <v>0.5058</v>
       </c>
       <c r="J77" t="n">
-        <v>12.8184</v>
+        <v>12.1392</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.16</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3658</v>
+        <v>0.3111</v>
       </c>
       <c r="J78" t="n">
-        <v>8.779199999999999</v>
+        <v>7.4664</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.96</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.0579</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.7256</v>
+        <v>-1.3896</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.8</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2517</v>
+        <v>-0.2318</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.0408</v>
+        <v>-5.5632</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2907</v>
+        <v>-0.2723</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.9768</v>
+        <v>-6.5352</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.32</v>
       </c>
       <c r="I82" t="n">
-        <v>1.9517</v>
+        <v>2.0352</v>
       </c>
       <c r="J82" t="n">
-        <v>37.0823</v>
+        <v>38.6688</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2959</v>
+        <v>0.2643</v>
       </c>
       <c r="J83" t="n">
-        <v>5.6221</v>
+        <v>5.0217</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.04</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1229</v>
+        <v>0.0992</v>
       </c>
       <c r="J84" t="n">
-        <v>2.3351</v>
+        <v>1.8848</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.01</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0113</v>
+        <v>0.0008</v>
       </c>
       <c r="J85" t="n">
-        <v>0.2147</v>
+        <v>0.0152</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.97</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1865</v>
+        <v>-0.1565</v>
       </c>
       <c r="J86" t="n">
-        <v>-3.5435</v>
+        <v>-2.9735</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.41</v>
       </c>
       <c r="I87" t="n">
-        <v>0.712</v>
+        <v>0.6851</v>
       </c>
       <c r="J87" t="n">
-        <v>13.528</v>
+        <v>13.0169</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.86</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1814</v>
+        <v>-0.1623</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.4466</v>
+        <v>-3.0837</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.75</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2906</v>
+        <v>-0.2721</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.5214</v>
+        <v>-5.1699</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.73</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3095</v>
+        <v>-0.2919</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.8805</v>
+        <v>-5.5461</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.71</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3281</v>
+        <v>-0.3115</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.2339</v>
+        <v>-5.9185</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.83</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.1694</v>
+        <v>-0.151</v>
       </c>
       <c r="J92" t="n">
-        <v>-2.3716</v>
+        <v>-2.114</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.66</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.3428</v>
+        <v>-0.3331</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.7992</v>
+        <v>-4.6634</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.63</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3697</v>
+        <v>-0.3607</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.1758</v>
+        <v>-5.0498</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.62</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3783</v>
+        <v>-0.3695</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.2962</v>
+        <v>-5.173</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.31</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6489</v>
+        <v>-0.669</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.0846</v>
+        <v>-9.366</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>2.01</v>
       </c>
       <c r="I97" t="n">
-        <v>1.5087</v>
+        <v>1.5274</v>
       </c>
       <c r="J97" t="n">
-        <v>21.1218</v>
+        <v>21.3836</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.72</v>
       </c>
       <c r="I98" t="n">
-        <v>1.1732</v>
+        <v>1.1736</v>
       </c>
       <c r="J98" t="n">
-        <v>16.4248</v>
+        <v>16.4304</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.61</v>
       </c>
       <c r="I99" t="n">
-        <v>1.0432</v>
+        <v>1.0407</v>
       </c>
       <c r="J99" t="n">
-        <v>14.6048</v>
+        <v>14.5698</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.46</v>
       </c>
       <c r="I100" t="n">
-        <v>0.8527</v>
+        <v>0.8486</v>
       </c>
       <c r="J100" t="n">
-        <v>11.9378</v>
+        <v>11.8804</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.38</v>
       </c>
       <c r="I101" t="n">
-        <v>0.7437</v>
+        <v>0.7395</v>
       </c>
       <c r="J101" t="n">
-        <v>10.4118</v>
+        <v>10.353</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.22</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4994</v>
+        <v>0.4695</v>
       </c>
       <c r="J102" t="n">
-        <v>9.988</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.87</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1672</v>
+        <v>-0.1502</v>
       </c>
       <c r="J103" t="n">
-        <v>-3.344</v>
+        <v>-3.004</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.87</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1672</v>
+        <v>-0.1502</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.344</v>
+        <v>-3.004</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.63</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3951</v>
+        <v>-0.3832</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.902</v>
+        <v>-7.664</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.59</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4307</v>
+        <v>-0.4221</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.614000000000001</v>
+        <v>-8.442</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.77</v>
       </c>
       <c r="I107" t="n">
-        <v>1.304</v>
+        <v>1.3089</v>
       </c>
       <c r="J107" t="n">
-        <v>26.08</v>
+        <v>26.178</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.26</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6067</v>
+        <v>0.5978</v>
       </c>
       <c r="J108" t="n">
-        <v>12.134</v>
+        <v>11.956</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.26</v>
       </c>
       <c r="I109" t="n">
-        <v>0.6067</v>
+        <v>0.5978</v>
       </c>
       <c r="J109" t="n">
-        <v>12.134</v>
+        <v>11.956</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.97</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1778</v>
+        <v>-0.1468</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.556</v>
+        <v>-2.936</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.92</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3318</v>
+        <v>-0.2923</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.636</v>
+        <v>-5.846</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.11</v>
       </c>
       <c r="I112" t="n">
-        <v>0.241</v>
+        <v>0.2276</v>
       </c>
       <c r="J112" t="n">
-        <v>4.82</v>
+        <v>4.552</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1754</v>
+        <v>0.1596</v>
       </c>
       <c r="J113" t="n">
-        <v>3.508</v>
+        <v>3.192</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.78</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2584</v>
+        <v>-0.2395</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.168</v>
+        <v>-4.79</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.72</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3153</v>
+        <v>-0.2981</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.306</v>
+        <v>-5.962</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.61</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4153</v>
+        <v>-0.4053</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.305999999999999</v>
+        <v>-8.106</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.47</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6047</v>
+        <v>0.5336</v>
       </c>
       <c r="J117" t="n">
-        <v>12.094</v>
+        <v>10.672</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.44</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5732</v>
+        <v>0.5026</v>
       </c>
       <c r="J118" t="n">
-        <v>11.464</v>
+        <v>10.052</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.08</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1463</v>
+        <v>0.1129</v>
       </c>
       <c r="J119" t="n">
-        <v>2.926</v>
+        <v>2.258</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.98</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0532</v>
+        <v>-0.041</v>
       </c>
       <c r="J120" t="n">
-        <v>-1.064</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.72</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3404</v>
+        <v>-0.3264</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.808</v>
+        <v>-6.528</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.81</v>
       </c>
       <c r="I122" t="n">
-        <v>1.5179</v>
+        <v>1.5565</v>
       </c>
       <c r="J122" t="n">
-        <v>34.9117</v>
+        <v>35.7995</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.24</v>
       </c>
       <c r="I123" t="n">
-        <v>0.632</v>
+        <v>0.5989</v>
       </c>
       <c r="J123" t="n">
-        <v>14.536</v>
+        <v>13.7747</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.24</v>
       </c>
       <c r="I124" t="n">
-        <v>0.632</v>
+        <v>0.5989</v>
       </c>
       <c r="J124" t="n">
-        <v>14.536</v>
+        <v>13.7747</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.85</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5044</v>
+        <v>-0.4647</v>
       </c>
       <c r="J125" t="n">
-        <v>-11.6012</v>
+        <v>-10.6881</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6681</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.3663</v>
+        <v>-14.6418</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>2.08</v>
       </c>
       <c r="I127" t="n">
-        <v>1.4771</v>
+        <v>1.4871</v>
       </c>
       <c r="J127" t="n">
-        <v>33.9733</v>
+        <v>34.2033</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.1</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2421</v>
+        <v>0.1984</v>
       </c>
       <c r="J128" t="n">
-        <v>5.5683</v>
+        <v>4.5632</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.92</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1295</v>
+        <v>-0.1103</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.9785</v>
+        <v>-2.5369</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.89</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1643</v>
+        <v>-0.144</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.7789</v>
+        <v>-3.312</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.36</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.642</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.766</v>
+        <v>-15.3594</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.43</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0145</v>
+        <v>1.0138</v>
       </c>
       <c r="J132" t="n">
-        <v>29.4205</v>
+        <v>29.4002</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.12</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3693</v>
+        <v>0.333</v>
       </c>
       <c r="J133" t="n">
-        <v>10.7097</v>
+        <v>9.657</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2928</v>
+        <v>0.259</v>
       </c>
       <c r="J134" t="n">
-        <v>8.491199999999999</v>
+        <v>7.511</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.07</v>
       </c>
       <c r="I135" t="n">
-        <v>0.238</v>
+        <v>0.2069</v>
       </c>
       <c r="J135" t="n">
-        <v>6.902</v>
+        <v>6.0001</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.01</v>
       </c>
       <c r="I136" t="n">
-        <v>0.0362</v>
+        <v>0.026</v>
       </c>
       <c r="J136" t="n">
-        <v>1.0498</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.23</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4837</v>
+        <v>0.4249</v>
       </c>
       <c r="J137" t="n">
-        <v>14.0273</v>
+        <v>12.3221</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4333</v>
+        <v>0.3757</v>
       </c>
       <c r="J138" t="n">
-        <v>12.5657</v>
+        <v>10.8953</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1243</v>
+        <v>0.094</v>
       </c>
       <c r="J139" t="n">
-        <v>3.6047</v>
+        <v>2.726</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2017</v>
+        <v>-0.181</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.8493</v>
+        <v>-5.249</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.357</v>
+        <v>-0.343</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.353</v>
+        <v>-9.946999999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.43</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8354</v>
+        <v>0.7943</v>
       </c>
       <c r="J142" t="n">
-        <v>16.708</v>
+        <v>15.886</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.83</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.213</v>
+        <v>-0.1932</v>
       </c>
       <c r="J143" t="n">
-        <v>-4.26</v>
+        <v>-3.864</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.233</v>
+        <v>-0.2133</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.66</v>
+        <v>-4.266</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.79</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2528</v>
+        <v>-0.2332</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.056</v>
+        <v>-4.664</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.64</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3928</v>
+        <v>-0.381</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.856</v>
+        <v>-7.62</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.5</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1</v>
+        <v>1.1112</v>
       </c>
       <c r="J147" t="n">
-        <v>22</v>
+        <v>22.224</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.36</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8681</v>
+        <v>0.8491</v>
       </c>
       <c r="J148" t="n">
-        <v>17.362</v>
+        <v>16.982</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.25</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6475</v>
+        <v>0.6168</v>
       </c>
       <c r="J149" t="n">
-        <v>12.95</v>
+        <v>12.336</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.08</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2533</v>
+        <v>0.2227</v>
       </c>
       <c r="J150" t="n">
-        <v>5.066</v>
+        <v>4.454</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.91</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3566</v>
+        <v>-0.3163</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.132</v>
+        <v>-6.326</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.19</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4536</v>
+        <v>0.3995</v>
       </c>
       <c r="J152" t="n">
-        <v>8.1648</v>
+        <v>7.191</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.92</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1143</v>
+        <v>-0.099</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.0574</v>
+        <v>-1.782</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.83</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2105</v>
+        <v>-0.1912</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.789</v>
+        <v>-3.4416</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2304</v>
+        <v>-0.211</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.1472</v>
+        <v>-3.798</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4167</v>
+        <v>-0.407</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.5006</v>
+        <v>-7.326</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>2.06</v>
       </c>
       <c r="I157" t="n">
-        <v>1.7806</v>
+        <v>1.8412</v>
       </c>
       <c r="J157" t="n">
-        <v>32.0508</v>
+        <v>33.1416</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.86</v>
       </c>
       <c r="I158" t="n">
-        <v>1.5396</v>
+        <v>1.5752</v>
       </c>
       <c r="J158" t="n">
-        <v>27.7128</v>
+        <v>28.3536</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.4</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9245</v>
+        <v>0.9146</v>
       </c>
       <c r="J159" t="n">
-        <v>16.641</v>
+        <v>16.4628</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.74</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.7782</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="J160" t="n">
-        <v>-14.0076</v>
+        <v>-13.6728</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.58</v>
       </c>
       <c r="I161" t="n">
-        <v>-1.1057</v>
+        <v>-1.126</v>
       </c>
       <c r="J161" t="n">
-        <v>-19.9026</v>
+        <v>-20.268</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.32</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6459</v>
+        <v>0.5901</v>
       </c>
       <c r="J162" t="n">
-        <v>15.5016</v>
+        <v>14.1624</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.09</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2434</v>
+        <v>0.1973</v>
       </c>
       <c r="J163" t="n">
-        <v>5.8416</v>
+        <v>4.7352</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.02</v>
       </c>
       <c r="I164" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0578</v>
       </c>
       <c r="J164" t="n">
-        <v>1.9488</v>
+        <v>1.3872</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.71</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3335</v>
+        <v>-0.3173</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.004</v>
+        <v>-7.6152</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.59</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4414</v>
+        <v>-0.435</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.5936</v>
+        <v>-10.44</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.8</v>
       </c>
       <c r="I167" t="n">
-        <v>1.5221</v>
+        <v>1.5642</v>
       </c>
       <c r="J167" t="n">
-        <v>36.5304</v>
+        <v>37.5408</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.12</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3705</v>
+        <v>0.3337</v>
       </c>
       <c r="J168" t="n">
-        <v>8.891999999999999</v>
+        <v>8.008800000000001</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0793</v>
+        <v>0.0624</v>
       </c>
       <c r="J169" t="n">
-        <v>1.9032</v>
+        <v>1.4976</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.93</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2851</v>
+        <v>-0.2449</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.8424</v>
+        <v>-5.8776</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6138</v>
+        <v>-0.5777</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.7312</v>
+        <v>-13.8648</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.15</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3971</v>
+        <v>0.3469</v>
       </c>
       <c r="J172" t="n">
-        <v>8.3391</v>
+        <v>7.2849</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0589</v>
       </c>
       <c r="J173" t="n">
-        <v>1.6443</v>
+        <v>1.2369</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.82</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2168</v>
+        <v>-0.1988</v>
       </c>
       <c r="J174" t="n">
-        <v>-4.5528</v>
+        <v>-4.1748</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.58</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4385</v>
+        <v>-0.4306</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.208500000000001</v>
+        <v>-9.0426</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.57</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4473</v>
+        <v>-0.4404</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.3933</v>
+        <v>-9.2484</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.64</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2876</v>
+        <v>1.3069</v>
       </c>
       <c r="J177" t="n">
-        <v>27.0396</v>
+        <v>27.4449</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.47</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0582</v>
+        <v>1.0649</v>
       </c>
       <c r="J178" t="n">
-        <v>22.2222</v>
+        <v>22.3629</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.05</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1661</v>
+        <v>0.1401</v>
       </c>
       <c r="J179" t="n">
-        <v>3.4881</v>
+        <v>2.9421</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.98</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1384</v>
+        <v>-0.1114</v>
       </c>
       <c r="J180" t="n">
-        <v>-2.9064</v>
+        <v>-2.3394</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2089</v>
+        <v>-0.1748</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.3869</v>
+        <v>-3.6708</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.19</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5034</v>
+        <v>0.4611</v>
       </c>
       <c r="J182" t="n">
-        <v>8.5578</v>
+        <v>7.8387</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.74</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2865</v>
+        <v>-0.2703</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.8705</v>
+        <v>-4.5951</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.73</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2956</v>
+        <v>-0.2795</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.0252</v>
+        <v>-4.7515</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.66</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3592</v>
+        <v>-0.3452</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.1064</v>
+        <v>-5.8684</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.47</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.527</v>
+        <v>-0.5293</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.959</v>
+        <v>-8.998100000000001</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.64</v>
       </c>
       <c r="I187" t="n">
-        <v>1.2525</v>
+        <v>1.2704</v>
       </c>
       <c r="J187" t="n">
-        <v>21.2925</v>
+        <v>21.5968</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.53</v>
       </c>
       <c r="I188" t="n">
-        <v>1.1114</v>
+        <v>1.1259</v>
       </c>
       <c r="J188" t="n">
-        <v>18.8938</v>
+        <v>19.1403</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.49</v>
       </c>
       <c r="I189" t="n">
-        <v>1.0585</v>
+        <v>1.0694</v>
       </c>
       <c r="J189" t="n">
-        <v>17.9945</v>
+        <v>18.1798</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.47</v>
       </c>
       <c r="I190" t="n">
-        <v>1.0303</v>
+        <v>1.0377</v>
       </c>
       <c r="J190" t="n">
-        <v>17.5151</v>
+        <v>17.6409</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.84</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5612</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.5404</v>
+        <v>-9.004899999999999</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.35</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4802</v>
+        <v>0.4126</v>
       </c>
       <c r="J192" t="n">
-        <v>11.5248</v>
+        <v>9.9024</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.16</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2564</v>
+        <v>0.2066</v>
       </c>
       <c r="J193" t="n">
-        <v>6.1536</v>
+        <v>4.9584</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.14</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2307</v>
+        <v>0.1841</v>
       </c>
       <c r="J194" t="n">
-        <v>5.5368</v>
+        <v>4.4184</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.12</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2043</v>
+        <v>0.1614</v>
       </c>
       <c r="J195" t="n">
-        <v>4.9032</v>
+        <v>3.8736</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.79</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2719</v>
+        <v>-0.2534</v>
       </c>
       <c r="J196" t="n">
-        <v>-6.5256</v>
+        <v>-6.0816</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.15</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2735</v>
+        <v>0.2596</v>
       </c>
       <c r="J197" t="n">
-        <v>6.564</v>
+        <v>6.2304</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0351</v>
+        <v>0.0264</v>
       </c>
       <c r="J198" t="n">
-        <v>0.8424</v>
+        <v>0.6336000000000001</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.99</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0247</v>
+        <v>-0.0179</v>
       </c>
       <c r="J199" t="n">
-        <v>-0.5928</v>
+        <v>-0.4296</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.91</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1342</v>
+        <v>-0.1153</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.2208</v>
+        <v>-2.7672</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.87</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1789</v>
+        <v>-0.1586</v>
       </c>
       <c r="J201" t="n">
-        <v>-4.2936</v>
+        <v>-3.8064</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.27</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5404</v>
+        <v>0.4808</v>
       </c>
       <c r="J202" t="n">
-        <v>12.9696</v>
+        <v>11.5392</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.21</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4426</v>
+        <v>0.3848</v>
       </c>
       <c r="J203" t="n">
-        <v>10.6224</v>
+        <v>9.235200000000001</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.97</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.0608</v>
+        <v>-0.0475</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.4592</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.88</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1725</v>
+        <v>-0.152</v>
       </c>
       <c r="J205" t="n">
-        <v>-4.14</v>
+        <v>-3.648</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.85</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2047</v>
+        <v>-0.184</v>
       </c>
       <c r="J206" t="n">
-        <v>-4.9128</v>
+        <v>-4.416</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.26</v>
       </c>
       <c r="I207" t="n">
-        <v>0.6995</v>
+        <v>0.666</v>
       </c>
       <c r="J207" t="n">
-        <v>16.788</v>
+        <v>15.984</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.11</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3531</v>
+        <v>0.3135</v>
       </c>
       <c r="J208" t="n">
-        <v>8.474399999999999</v>
+        <v>7.524</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.1</v>
       </c>
       <c r="I209" t="n">
-        <v>0.3276</v>
+        <v>0.2889</v>
       </c>
       <c r="J209" t="n">
-        <v>7.8624</v>
+        <v>6.9336</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.08</v>
       </c>
       <c r="I210" t="n">
-        <v>0.275</v>
+        <v>0.2388</v>
       </c>
       <c r="J210" t="n">
-        <v>6.6</v>
+        <v>5.7312</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5789</v>
+        <v>-0.5399</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.8936</v>
+        <v>-12.9576</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.36</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7258</v>
+        <v>0.6767</v>
       </c>
       <c r="J212" t="n">
-        <v>16.6934</v>
+        <v>15.5641</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.97</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0512</v>
+        <v>-0.0412</v>
       </c>
       <c r="J213" t="n">
-        <v>-1.1776</v>
+        <v>-0.9476</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.88</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.161</v>
+        <v>-0.1424</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.703</v>
+        <v>-3.2752</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.75</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2916</v>
+        <v>-0.2732</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.7068</v>
+        <v>-6.2836</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.55</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4723</v>
+        <v>-0.469</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.8629</v>
+        <v>-10.787</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.52</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1595</v>
+        <v>1.1751</v>
       </c>
       <c r="J217" t="n">
-        <v>26.6685</v>
+        <v>27.0273</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.17</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4943</v>
+        <v>0.4542</v>
       </c>
       <c r="J218" t="n">
-        <v>11.3689</v>
+        <v>10.4466</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.17</v>
       </c>
       <c r="I219" t="n">
-        <v>0.4943</v>
+        <v>0.4542</v>
       </c>
       <c r="J219" t="n">
-        <v>11.3689</v>
+        <v>10.4466</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.89</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3866</v>
+        <v>-0.3437</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.8918</v>
+        <v>-7.9051</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.71</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.8055</v>
+        <v>-0.7827</v>
       </c>
       <c r="J221" t="n">
-        <v>-18.5265</v>
+        <v>-18.0021</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.15</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3657</v>
+        <v>0.3118</v>
       </c>
       <c r="J222" t="n">
-        <v>8.7768</v>
+        <v>7.4832</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1</v>
       </c>
       <c r="I223" t="n">
-        <v>0.0109</v>
+        <v>0.0071</v>
       </c>
       <c r="J223" t="n">
-        <v>0.2616</v>
+        <v>0.1704</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.89</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1515</v>
+        <v>-0.1329</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.636</v>
+        <v>-3.1896</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.82</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2249</v>
+        <v>-0.2049</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.3976</v>
+        <v>-4.9176</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.74</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3029</v>
+        <v>-0.2849</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.2696</v>
+        <v>-6.8376</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.67</v>
       </c>
       <c r="I227" t="n">
-        <v>1.3566</v>
+        <v>1.384</v>
       </c>
       <c r="J227" t="n">
-        <v>32.5584</v>
+        <v>33.216</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.26</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6876</v>
+        <v>0.6542</v>
       </c>
       <c r="J228" t="n">
-        <v>16.5024</v>
+        <v>15.7008</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2528</v>
+        <v>-0.2139</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.0672</v>
+        <v>-5.1336</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.86</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4678</v>
+        <v>-0.4259</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.2272</v>
+        <v>-10.2216</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.86</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4678</v>
+        <v>-0.4259</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.2272</v>
+        <v>-10.2216</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.85</v>
       </c>
       <c r="I232" t="n">
-        <v>1.49</v>
+        <v>1.5212</v>
       </c>
       <c r="J232" t="n">
-        <v>23.84</v>
+        <v>24.3392</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.54</v>
       </c>
       <c r="I233" t="n">
-        <v>1.112</v>
+        <v>1.1304</v>
       </c>
       <c r="J233" t="n">
-        <v>17.792</v>
+        <v>18.0864</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.49</v>
       </c>
       <c r="I234" t="n">
-        <v>1.0485</v>
+        <v>1.063</v>
       </c>
       <c r="J234" t="n">
-        <v>16.776</v>
+        <v>17.008</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.41</v>
       </c>
       <c r="I235" t="n">
-        <v>0.9224</v>
+        <v>0.9212</v>
       </c>
       <c r="J235" t="n">
-        <v>14.7584</v>
+        <v>14.7392</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>1.28</v>
       </c>
       <c r="I236" t="n">
-        <v>0.6711</v>
+        <v>0.6512</v>
       </c>
       <c r="J236" t="n">
-        <v>10.7376</v>
+        <v>10.4192</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.65</v>
       </c>
       <c r="I237" t="n">
-        <v>1.1499</v>
+        <v>1.1635</v>
       </c>
       <c r="J237" t="n">
-        <v>18.3984</v>
+        <v>18.616</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.99</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0041</v>
       </c>
       <c r="J238" t="n">
-        <v>-0.1344</v>
+        <v>-0.06560000000000001</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.83</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2077</v>
+        <v>-0.1895</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.3232</v>
+        <v>-3.032</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.45</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.552</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.832000000000001</v>
+        <v>-8.944000000000001</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.26</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7104</v>
+        <v>-0.7467</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.3664</v>
+        <v>-11.9472</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.31</v>
       </c>
       <c r="I242" t="n">
-        <v>0.7808</v>
+        <v>0.754</v>
       </c>
       <c r="J242" t="n">
-        <v>23.424</v>
+        <v>22.62</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.31</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7808</v>
+        <v>0.754</v>
       </c>
       <c r="J243" t="n">
-        <v>23.424</v>
+        <v>22.62</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.25</v>
       </c>
       <c r="I244" t="n">
-        <v>0.6566</v>
+        <v>0.6234</v>
       </c>
       <c r="J244" t="n">
-        <v>19.698</v>
+        <v>18.702</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.03</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1104</v>
+        <v>0.0896</v>
       </c>
       <c r="J245" t="n">
-        <v>3.312</v>
+        <v>2.688</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.92</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3191</v>
+        <v>-0.2783</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.573</v>
+        <v>-8.349</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.32</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6312</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="J247" t="n">
-        <v>18.936</v>
+        <v>17.193</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.15</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3479</v>
+        <v>0.2941</v>
       </c>
       <c r="J248" t="n">
-        <v>10.437</v>
+        <v>8.823</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.9</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1463</v>
+        <v>-0.1267</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.389</v>
+        <v>-3.801</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.83</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2215</v>
+        <v>-0.201</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.645</v>
+        <v>-6.03</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.76</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2907</v>
+        <v>-0.2723</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.721</v>
+        <v>-8.169</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.39</v>
       </c>
       <c r="I252" t="n">
-        <v>0.9674</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="J252" t="n">
-        <v>20.3154</v>
+        <v>20.1432</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.21</v>
       </c>
       <c r="I253" t="n">
-        <v>0.5908</v>
+        <v>0.5521</v>
       </c>
       <c r="J253" t="n">
-        <v>12.4068</v>
+        <v>11.5941</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.18</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5226</v>
+        <v>0.4821</v>
       </c>
       <c r="J254" t="n">
-        <v>10.9746</v>
+        <v>10.1241</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.89</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3819</v>
+        <v>-0.3389</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.0199</v>
+        <v>-7.1169</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.67</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.8858</v>
+        <v>-0.8704</v>
       </c>
       <c r="J256" t="n">
-        <v>-18.6018</v>
+        <v>-18.2784</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.33</v>
       </c>
       <c r="I257" t="n">
-        <v>0.6354</v>
+        <v>0.5764</v>
       </c>
       <c r="J257" t="n">
-        <v>13.3434</v>
+        <v>12.1044</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.05</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1439</v>
+        <v>0.1114</v>
       </c>
       <c r="J258" t="n">
-        <v>3.0219</v>
+        <v>2.3394</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.03</v>
       </c>
       <c r="I259" t="n">
-        <v>0.097</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="J259" t="n">
-        <v>2.037</v>
+        <v>1.5204</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.95</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.0886</v>
+        <v>-0.0723</v>
       </c>
       <c r="J260" t="n">
-        <v>-1.8606</v>
+        <v>-1.5183</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.8</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2553</v>
+        <v>-0.2356</v>
       </c>
       <c r="J261" t="n">
-        <v>-5.3613</v>
+        <v>-4.9476</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.53</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1221</v>
+        <v>1.1353</v>
       </c>
       <c r="J262" t="n">
-        <v>21.3199</v>
+        <v>21.5707</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.52</v>
       </c>
       <c r="I263" t="n">
-        <v>1.1089</v>
+        <v>1.1216</v>
       </c>
       <c r="J263" t="n">
-        <v>21.0691</v>
+        <v>21.3104</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.32</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7755</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="J264" t="n">
-        <v>14.7345</v>
+        <v>14.3545</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.32</v>
       </c>
       <c r="I265" t="n">
-        <v>0.7755</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="J265" t="n">
-        <v>14.7345</v>
+        <v>14.3545</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.91</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.373</v>
+        <v>-0.3353</v>
       </c>
       <c r="J266" t="n">
-        <v>-7.087</v>
+        <v>-6.3707</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.17</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4147</v>
+        <v>0.3607</v>
       </c>
       <c r="J267" t="n">
-        <v>7.8793</v>
+        <v>6.8533</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.0766</v>
       </c>
       <c r="J268" t="n">
-        <v>-1.7157</v>
+        <v>-1.4554</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.84</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.201</v>
+        <v>-0.1818</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.819</v>
+        <v>-3.4542</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.77</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2702</v>
+        <v>-0.2512</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.1338</v>
+        <v>-4.7728</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.68</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3545</v>
+        <v>-0.3396</v>
       </c>
       <c r="J271" t="n">
-        <v>-6.7355</v>
+        <v>-6.4524</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.16</v>
       </c>
       <c r="I272" t="n">
-        <v>1.8677</v>
+        <v>1.9347</v>
       </c>
       <c r="J272" t="n">
-        <v>31.7509</v>
+        <v>32.8899</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.58</v>
       </c>
       <c r="I273" t="n">
-        <v>1.1706</v>
+        <v>1.1871</v>
       </c>
       <c r="J273" t="n">
-        <v>19.9002</v>
+        <v>20.1807</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.27</v>
       </c>
       <c r="I274" t="n">
-        <v>0.6619</v>
+        <v>0.6402</v>
       </c>
       <c r="J274" t="n">
-        <v>11.2523</v>
+        <v>10.8834</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.14</v>
       </c>
       <c r="I275" t="n">
-        <v>0.3738</v>
+        <v>0.3416</v>
       </c>
       <c r="J275" t="n">
-        <v>6.3546</v>
+        <v>5.8072</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.02</v>
       </c>
       <c r="I276" t="n">
-        <v>0.0301</v>
+        <v>0.0107</v>
       </c>
       <c r="J276" t="n">
-        <v>0.5117</v>
+        <v>0.1819</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.16</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4285</v>
+        <v>0.3807</v>
       </c>
       <c r="J277" t="n">
-        <v>7.2845</v>
+        <v>6.4719</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.01</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0878</v>
+        <v>0.0688</v>
       </c>
       <c r="J278" t="n">
-        <v>1.4926</v>
+        <v>1.1696</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.71</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3179</v>
+        <v>-0.3015</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.4043</v>
+        <v>-5.1255</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.68</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3454</v>
+        <v>-0.3302</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.8718</v>
+        <v>-5.6134</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.42</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5738</v>
+        <v>-0.5836</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.7546</v>
+        <v>-9.921200000000001</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.62</v>
       </c>
       <c r="I282" t="n">
-        <v>1.2815</v>
+        <v>1.3023</v>
       </c>
       <c r="J282" t="n">
-        <v>37.1635</v>
+        <v>37.7667</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.59</v>
       </c>
       <c r="I283" t="n">
-        <v>1.2409</v>
+        <v>1.2593</v>
       </c>
       <c r="J283" t="n">
-        <v>35.9861</v>
+        <v>36.5197</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.85</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.4973</v>
+        <v>-0.4565</v>
       </c>
       <c r="J284" t="n">
-        <v>-14.4217</v>
+        <v>-13.2385</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.84</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.5215</v>
+        <v>-0.4815</v>
       </c>
       <c r="J285" t="n">
-        <v>-15.1235</v>
+        <v>-13.9635</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.82</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.531</v>
       </c>
       <c r="J286" t="n">
-        <v>-16.5039</v>
+        <v>-15.399</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.13</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3216</v>
+        <v>0.2695</v>
       </c>
       <c r="J287" t="n">
-        <v>9.3264</v>
+        <v>7.8155</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.12</v>
       </c>
       <c r="I288" t="n">
-        <v>0.3025</v>
+        <v>0.2517</v>
       </c>
       <c r="J288" t="n">
-        <v>8.772500000000001</v>
+        <v>7.2993</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.95</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0827</v>
+        <v>-0.0684</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.3983</v>
+        <v>-1.9836</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.86</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1861</v>
+        <v>-0.1659</v>
       </c>
       <c r="J290" t="n">
-        <v>-5.3969</v>
+        <v>-4.8111</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.67</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3702</v>
+        <v>-0.3567</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.7358</v>
+        <v>-10.3443</v>
       </c>
     </row>
   </sheetData>
